--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1BD8F37-6A9A-4829-854E-087E0C201F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0C4ED8-891A-4361-B3AE-706A189CA14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="07-05" sheetId="9" r:id="rId5"/>
     <sheet name="08-05" sheetId="10" r:id="rId6"/>
     <sheet name="09-05" sheetId="11" r:id="rId7"/>
+    <sheet name="11-05" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2280" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="965">
   <si>
     <t>THU 6</t>
   </si>
@@ -2213,12 +2214,30 @@
     <t>NGAY 9-5</t>
   </si>
   <si>
+    <t>KIỀU HOANH</t>
+  </si>
+  <si>
+    <t>277 âu dương lân p2</t>
+  </si>
+  <si>
     <t>AT 09-05</t>
   </si>
   <si>
     <t>09-05-2026</t>
   </si>
   <si>
+    <t>Isabella</t>
+  </si>
+  <si>
+    <t>494/1/12 Le Quang Dinh, P1</t>
+  </si>
+  <si>
+    <t>THƯƠNG</t>
+  </si>
+  <si>
+    <t>49 TX22, phường Thới An</t>
+  </si>
+  <si>
     <t>TUYẾT NHI</t>
   </si>
   <si>
@@ -2234,6 +2253,15 @@
     <t>NOTE GỬI CHO SU ANH</t>
   </si>
   <si>
+    <t>22/40 Yên Thế, P2, Tân Bình</t>
+  </si>
+  <si>
+    <t>NGUYỄN MINH DUY</t>
+  </si>
+  <si>
+    <t>90/35 Trần Văn Ơn, Phường Tân Sơn Nhì</t>
+  </si>
+  <si>
     <t>Thanh Thao</t>
   </si>
   <si>
@@ -2249,18 +2277,27 @@
     <t>HD019513</t>
   </si>
   <si>
+    <t>162/25, Đường Nguyễn Văn Khối, Phường 8</t>
+  </si>
+  <si>
     <t>Phạm Dung</t>
   </si>
   <si>
     <t>HD019531</t>
   </si>
   <si>
+    <t>208 nguyễn hữu cảnh phường 22 chung cư vinhome toà lanmark 5</t>
+  </si>
+  <si>
     <t>Nguyễn Hà</t>
   </si>
   <si>
     <t>HD019502</t>
   </si>
   <si>
+    <t>007 Lô B chung cư Tây Thạnh phường Tân Thạnh</t>
+  </si>
+  <si>
     <t>mai anh</t>
   </si>
   <si>
@@ -2276,12 +2313,18 @@
     <t>HD015540</t>
   </si>
   <si>
+    <t>100/2A Trần Hưng Đạo</t>
+  </si>
+  <si>
     <t>Kimchou Try</t>
   </si>
   <si>
     <t>HD019523</t>
   </si>
   <si>
+    <t>301 Pham Ngu Lao Street</t>
+  </si>
+  <si>
     <t>HD019300</t>
   </si>
   <si>
@@ -2300,12 +2343,24 @@
     <t>HD019522</t>
   </si>
   <si>
+    <t>154/4/7, Nguyễn Phúc Chu Phường 15</t>
+  </si>
+  <si>
+    <t>Hạnh Trần</t>
+  </si>
+  <si>
     <t>HD019306</t>
   </si>
   <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phủ, phường Tân Tạo</t>
+  </si>
+  <si>
     <t>HD019430</t>
   </si>
   <si>
+    <t>702/45/31 điện biên phủ phường 10</t>
+  </si>
+  <si>
     <t>Huyền Nhung</t>
   </si>
   <si>
@@ -2318,6 +2373,9 @@
     <t>HD019413</t>
   </si>
   <si>
+    <t>32B đường số 8 thông tây hội</t>
+  </si>
+  <si>
     <t>Minh Ngọc</t>
   </si>
   <si>
@@ -2330,6 +2388,15 @@
     <t>HD019503</t>
   </si>
   <si>
+    <t>Lê Nguyễn Nhật Ánh</t>
+  </si>
+  <si>
+    <t>HD019357</t>
+  </si>
+  <si>
+    <t>orchid 1, Hà Đô Centrosa, 118 3/2, phường Hòa Hưng</t>
+  </si>
+  <si>
     <t>Thu Hà</t>
   </si>
   <si>
@@ -2339,18 +2406,33 @@
     <t>số 201/12 mã văn lò, p, bình trị đông a</t>
   </si>
   <si>
+    <t>Thuý Heri</t>
+  </si>
+  <si>
     <t>HD019180</t>
   </si>
   <si>
+    <t>184/17/35 bãi sậy, phường bình tiên</t>
+  </si>
+  <si>
     <t>Kim Mese Phan</t>
   </si>
   <si>
     <t>HD019317</t>
   </si>
   <si>
+    <t>72 bùi hữu nghĩa p7</t>
+  </si>
+  <si>
     <t>Thy Mai</t>
   </si>
   <si>
+    <t>HD019514</t>
+  </si>
+  <si>
+    <t>2 nguyễn văn tưởng, phường tân phú</t>
+  </si>
+  <si>
     <t>HD018297</t>
   </si>
   <si>
@@ -2360,88 +2442,502 @@
     <t>HDO19455</t>
   </si>
   <si>
-    <t>32B đường số 8 thông tây hội</t>
-  </si>
-  <si>
-    <t>154/4/7, Nguyễn Phúc Chu Phường 15</t>
-  </si>
-  <si>
-    <t>90/35 Trần Văn Ơn, Phường Tân Sơn Nhì</t>
-  </si>
-  <si>
-    <t>NGUYỄN MINH DUY</t>
-  </si>
-  <si>
-    <t>Isabella</t>
-  </si>
-  <si>
-    <t>494/1/12 Le Quang Dinh, P1</t>
-  </si>
-  <si>
-    <t>162/25, Đường Nguyễn Văn Khối, Phường 8</t>
-  </si>
-  <si>
-    <t>208 nguyễn hữu cảnh phường 22 chung cư vinhome toà lanmark 5</t>
-  </si>
-  <si>
-    <t>22/40 Yên Thế, P2, Tân Bình</t>
-  </si>
-  <si>
-    <t>Lê Nguyễn Nhật Ánh</t>
-  </si>
-  <si>
-    <t>HD019357</t>
-  </si>
-  <si>
-    <t>orchid 1, Hà Đô Centrosa, 118 3/2, phường Hòa Hưng</t>
-  </si>
-  <si>
-    <t>301 Pham Ngu Lao Street</t>
-  </si>
-  <si>
-    <t>72 bùi hữu nghĩa p7</t>
-  </si>
-  <si>
-    <t>702/45/31 điện biên phủ phường 10</t>
-  </si>
-  <si>
-    <t>100/2A Trần Hưng Đạo</t>
-  </si>
-  <si>
     <t>92 Nguyễn Trãi, phường Bến Thành</t>
   </si>
   <si>
-    <t>49 TX22, phường Thới An</t>
-  </si>
-  <si>
-    <t>THƯƠNG</t>
-  </si>
-  <si>
-    <t>KIỀU HOANH</t>
-  </si>
-  <si>
-    <t>277 âu dương lân p2</t>
-  </si>
-  <si>
-    <t>Hạnh Trần</t>
-  </si>
-  <si>
-    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phủ, phường Tân Tạo</t>
-  </si>
-  <si>
-    <t>Thuý Heri</t>
-  </si>
-  <si>
-    <t>184/17/35 bãi sậy, phường bình tiên</t>
-  </si>
-  <si>
-    <t>HD019514</t>
-  </si>
-  <si>
-    <t>2 nguyễn văn tưởng, phường tân phú</t>
-  </si>
-  <si>
-    <t>007 Lô B chung cư Tây Thạnh phường Tân Thạnh</t>
+    <t>NGAY 11-5</t>
+  </si>
+  <si>
+    <t>HD019808</t>
+  </si>
+  <si>
+    <t>11-05-2026</t>
+  </si>
+  <si>
+    <t>Minh Nguyệt + Lin Xiao + Hàng Air</t>
+  </si>
+  <si>
+    <t>HD019693</t>
+  </si>
+  <si>
+    <t>AT 11-05</t>
+  </si>
+  <si>
+    <t>Phan Nhi</t>
+  </si>
+  <si>
+    <t>HD019796</t>
+  </si>
+  <si>
+    <t>107/189 quang trung, f.10</t>
+  </si>
+  <si>
+    <t>Thúy Kiều</t>
+  </si>
+  <si>
+    <t>HD019818</t>
+  </si>
+  <si>
+    <t>Số 6 mai văn vĩnh tân quy</t>
+  </si>
+  <si>
+    <t>HD019881</t>
+  </si>
+  <si>
+    <t>Kiên Thị Thanh Hiền</t>
+  </si>
+  <si>
+    <t>HD019616</t>
+  </si>
+  <si>
+    <t>HD019735</t>
+  </si>
+  <si>
+    <t>HD019469</t>
+  </si>
+  <si>
+    <t>Na Na</t>
+  </si>
+  <si>
+    <t>HD019683</t>
+  </si>
+  <si>
+    <t>145/11 Nguyễn Văn trỗi</t>
+  </si>
+  <si>
+    <t>Diệu Linh</t>
+  </si>
+  <si>
+    <t>HD019905</t>
+  </si>
+  <si>
+    <t>Ngô Thị Bích Loan</t>
+  </si>
+  <si>
+    <t>HD019626</t>
+  </si>
+  <si>
+    <t>Mary Tran</t>
+  </si>
+  <si>
+    <t>HD019738</t>
+  </si>
+  <si>
+    <t>Phương Bình</t>
+  </si>
+  <si>
+    <t>HD019877</t>
+  </si>
+  <si>
+    <t>CC Ehome3, Hồ Học Lãm, An Lạc</t>
+  </si>
+  <si>
+    <t>HD019782</t>
+  </si>
+  <si>
+    <t>HD019780</t>
+  </si>
+  <si>
+    <t>42 nguyễn sơn hà f5</t>
+  </si>
+  <si>
+    <t>Nguyet</t>
+  </si>
+  <si>
+    <t>HD019907</t>
+  </si>
+  <si>
+    <t>Trang Nhung Bui</t>
+  </si>
+  <si>
+    <t>HD019787</t>
+  </si>
+  <si>
+    <t>HD19599</t>
+  </si>
+  <si>
+    <t>HD019899</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngọc Ngà</t>
+  </si>
+  <si>
+    <t>Minh Hải ( Ruby Eyelash - Nail )</t>
+  </si>
+  <si>
+    <t>HD019891</t>
+  </si>
+  <si>
+    <t>HD019705</t>
+  </si>
+  <si>
+    <t>Đỗ Đông Mi</t>
+  </si>
+  <si>
+    <t>HD019570</t>
+  </si>
+  <si>
+    <t>115 phan huy thuc ptan kieng</t>
+  </si>
+  <si>
+    <t>HD019745</t>
+  </si>
+  <si>
+    <t>HD019753</t>
+  </si>
+  <si>
+    <t>HD019639</t>
+  </si>
+  <si>
+    <t>132 Bến Vân Đồn Chung cư Millennium toà A 22.07</t>
+  </si>
+  <si>
+    <t>HD019644</t>
+  </si>
+  <si>
+    <t>Huỳnh Kim</t>
+  </si>
+  <si>
+    <t>HD019764</t>
+  </si>
+  <si>
+    <t>HD019779</t>
+  </si>
+  <si>
+    <t>Huynh Anh</t>
+  </si>
+  <si>
+    <t>HD019576</t>
+  </si>
+  <si>
+    <t>284 nguyễn thiện thuật</t>
+  </si>
+  <si>
+    <t>Trúc Uyên</t>
+  </si>
+  <si>
+    <t>HD019781</t>
+  </si>
+  <si>
+    <t>6B8/23/1c hương lộ 2, p bình trị đông A</t>
+  </si>
+  <si>
+    <t>Trang Cherry</t>
+  </si>
+  <si>
+    <t>HD019937</t>
+  </si>
+  <si>
+    <t>HD019767</t>
+  </si>
+  <si>
+    <t>HD019994</t>
+  </si>
+  <si>
+    <t>W24130 miki</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, Thới An</t>
+  </si>
+  <si>
+    <t>Myle Pham</t>
+  </si>
+  <si>
+    <t>HD019988</t>
+  </si>
+  <si>
+    <t>88/29 đường 17, phường Tân thuận Tây</t>
+  </si>
+  <si>
+    <t>HD019733</t>
+  </si>
+  <si>
+    <t>HD019969</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thuỳ Trang</t>
+  </si>
+  <si>
+    <t>HD020003</t>
+  </si>
+  <si>
+    <t>41A huỳnh tịnh của p19</t>
+  </si>
+  <si>
+    <t>Yến Nhi - fb Thanh Thanh</t>
+  </si>
+  <si>
+    <t>HD020012</t>
+  </si>
+  <si>
+    <t>Yến Phương</t>
+  </si>
+  <si>
+    <t>HD020005</t>
+  </si>
+  <si>
+    <t>Lê Hữu Nhân</t>
+  </si>
+  <si>
+    <t>HD019980</t>
+  </si>
+  <si>
+    <t>Ama Bella - zalo</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương An Đông</t>
+  </si>
+  <si>
+    <t>Titi</t>
+  </si>
+  <si>
+    <t>HD019977</t>
+  </si>
+  <si>
+    <t>Anh Thu</t>
+  </si>
+  <si>
+    <t>HD019992</t>
+  </si>
+  <si>
+    <t>157/59/11 Dương Bá Trạc Phường 1</t>
+  </si>
+  <si>
+    <t>Hồ Ly</t>
+  </si>
+  <si>
+    <t>HD019939</t>
+  </si>
+  <si>
+    <t>Võ Trần Như Bích</t>
+  </si>
+  <si>
+    <t>HD019760</t>
+  </si>
+  <si>
+    <t>Mỹ Hương</t>
+  </si>
+  <si>
+    <t>HD020008</t>
+  </si>
+  <si>
+    <t>Diễm My</t>
+  </si>
+  <si>
+    <t>HD020004</t>
+  </si>
+  <si>
+    <t>174 ton dan p4</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Ngân</t>
+  </si>
+  <si>
+    <t>HD019934</t>
+  </si>
+  <si>
+    <t>Lavida Plus, Nguyễn Văn Linh, Tân Phong</t>
+  </si>
+  <si>
+    <t>HƯƠNG TRẦN</t>
+  </si>
+  <si>
+    <t>UYÊN MI</t>
+  </si>
+  <si>
+    <t>Dung Nguyen</t>
+  </si>
+  <si>
+    <t>15/32/2 võ duy ninh f22</t>
+  </si>
+  <si>
+    <t>cổng B Cát Lái đường Lê Phụng Hiểu, Cát Lái</t>
+  </si>
+  <si>
+    <t>78 Trần Não, P. An Khánh</t>
+  </si>
+  <si>
+    <t>Toà Golden House - Sunwah Pearl 90 Nguyễn Hữu Cảnh - phường 22</t>
+  </si>
+  <si>
+    <t>16 đường 6, p linh chiểu</t>
+  </si>
+  <si>
+    <t>Vân Ốc</t>
+  </si>
+  <si>
+    <t>9/5 đường số 66 Phường thảo điền</t>
+  </si>
+  <si>
+    <t>Gate 4 - Feliz en vista, 1 trương văn bang, thạnh mỹ lợi Toà cruz - C810</t>
+  </si>
+  <si>
+    <t>Cẩm Tú</t>
+  </si>
+  <si>
+    <t>chung cư terrace 21 võ trường toản</t>
+  </si>
+  <si>
+    <t>261/26c chu văn an p12</t>
+  </si>
+  <si>
+    <t>chi hương fb Kim Tien Pham</t>
+  </si>
+  <si>
+    <t>31 đường số 30 phường cát lái</t>
+  </si>
+  <si>
+    <t>Đỗ Thị Kiều Chinh</t>
+  </si>
+  <si>
+    <t>42, đường 21,Khu dân cư bình chiểu, P tam binh (chợ đầu mối nông sản thủ đức)</t>
+  </si>
+  <si>
+    <t>Vinhomes central park( park 2 -P2) 720a Điện Biên Phủ, Phường 22</t>
+  </si>
+  <si>
+    <t>HD019556</t>
+  </si>
+  <si>
+    <t>167 đặng văn ngữ</t>
+  </si>
+  <si>
+    <t>109 bến vân đồn, phường 9</t>
+  </si>
+  <si>
+    <t>Nhy Lê</t>
+  </si>
+  <si>
+    <t>Vi Chanel</t>
+  </si>
+  <si>
+    <t>quyên quyên</t>
+  </si>
+  <si>
+    <t>89 thành thái diên hồng</t>
+  </si>
+  <si>
+    <t>Trần Chi / Yaya Tran</t>
+  </si>
+  <si>
+    <t>36 sư vạn hạnh p9</t>
+  </si>
+  <si>
+    <t>Phi Phụng</t>
+  </si>
+  <si>
+    <t>85 hồ tùng mậu bến nghé</t>
+  </si>
+  <si>
+    <t>Toà nhà lux 6...Vinhomes Golden River (Bason), 2 Nguyễn Hữu Cảnh, P. Bến Nghé</t>
+  </si>
+  <si>
+    <t>HD020009</t>
+  </si>
+  <si>
+    <t>196/16 Đề Thám, P. Cầu Ông Lãnh</t>
+  </si>
+  <si>
+    <t>Tuyet Nhung Nguyen</t>
+  </si>
+  <si>
+    <t>36 Lê lai phường Bảy Hiền</t>
+  </si>
+  <si>
+    <t>1A Đ. Lý Thường Kiệt, Phường 7</t>
+  </si>
+  <si>
+    <t>38 Nguyễn Bá Tuyển, P12</t>
+  </si>
+  <si>
+    <t>Chị Dương - fb Lien Phuong Bui</t>
+  </si>
+  <si>
+    <t>14 Bạch Mã, p15 cư xá bắc hải</t>
+  </si>
+  <si>
+    <t>Thanh Trần</t>
+  </si>
+  <si>
+    <t>HD014525</t>
+  </si>
+  <si>
+    <t>23 Đ. Phú Thuận, Phú Thuận , hcm Sunshine Sky City sảnh A1</t>
+  </si>
+  <si>
+    <t>Bùi Khánh Ngọc</t>
+  </si>
+  <si>
+    <t>HD014022</t>
+  </si>
+  <si>
+    <t>Cc River Panorama 20 Lê Thị Chợ phường Phú Thuận</t>
+  </si>
+  <si>
+    <t>AT 22-04</t>
+  </si>
+  <si>
+    <t>22-04-2026</t>
+  </si>
+  <si>
+    <t>MIE</t>
+  </si>
+  <si>
+    <t>135 hải thượng lãn Ông P10</t>
+  </si>
+  <si>
+    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà cũ</t>
+  </si>
+  <si>
+    <t>Nguyễn Cao Kim Anh</t>
+  </si>
+  <si>
+    <t>264 lê văn lương phước kiểng</t>
+  </si>
+  <si>
+    <t>HD019744</t>
+  </si>
+  <si>
+    <t>38b đường số 12 tân quy</t>
+  </si>
+  <si>
+    <t>17 Đường Số 13 Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Ruby Cẩm Tú</t>
+  </si>
+  <si>
+    <t>61 bui diên p4</t>
+  </si>
+  <si>
+    <t>Kaity Hg</t>
+  </si>
+  <si>
+    <t>HD019671</t>
+  </si>
+  <si>
+    <t>C16-17 lô C1, đường DD5, phường Đông Hưng Thuận (ghi chú: sau lưng chợ An Sương)</t>
+  </si>
+  <si>
+    <t>100.đinh văn ước ấp5 xã hưng long</t>
+  </si>
+  <si>
+    <t>53/3B Mai Hắc Đế, phường Phú Định</t>
+  </si>
+  <si>
+    <t>Toà nhà Namn 10 đường số 67 phường tân quy</t>
+  </si>
+  <si>
+    <t>Chung cư Richstar 1, sảnh RS1 - 278A Hoà Bình, P. Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Thuỳ</t>
+  </si>
+  <si>
+    <t>24b tân sơn nhì</t>
+  </si>
+  <si>
+    <t>Chung cư an gia thị trấn Tân túc</t>
   </si>
 </sst>
 </file>
@@ -4064,7 +4560,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I56" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -7139,7 +7635,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I55" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>2090</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -11847,10 +12343,12 @@
   <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="33.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="66.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -11928,10 +12426,10 @@
         <v>18</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>791</v>
+        <v>723</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>792</v>
+        <v>724</v>
       </c>
       <c r="F3" s="9">
         <v>8</v>
@@ -11943,17 +12441,17 @@
         <v>30</v>
       </c>
       <c r="I3" s="8">
-        <f>G3-H3</f>
+        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
         <v>0</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -11964,10 +12462,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>776</v>
+        <v>727</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>777</v>
+        <v>728</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>70</v>
@@ -11979,7 +12477,7 @@
         <v>30</v>
       </c>
       <c r="I4" s="3">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -11989,7 +12487,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12015,17 +12513,17 @@
         <v>35</v>
       </c>
       <c r="I5" s="8">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12036,10 +12534,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>790</v>
+        <v>729</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>789</v>
+        <v>730</v>
       </c>
       <c r="F6" s="8" t="s">
         <v>29</v>
@@ -12051,17 +12549,17 @@
         <v>35</v>
       </c>
       <c r="I6" s="8">
-        <f t="shared" ref="I6:I33" si="0">G6-H6</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12072,10 +12570,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>725</v>
+        <v>731</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>726</v>
+        <v>732</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>127</v>
@@ -12091,13 +12589,13 @@
         <v>620</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12108,10 +12606,10 @@
         <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>727</v>
+        <v>733</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>728</v>
+        <v>734</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>98</v>
@@ -12133,7 +12631,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12144,10 +12642,10 @@
         <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>729</v>
+        <v>735</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>780</v>
+        <v>736</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>102</v>
@@ -12169,7 +12667,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12180,10 +12678,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>775</v>
+        <v>737</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>85</v>
@@ -12205,7 +12703,7 @@
         <v>24</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12213,13 +12711,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>730</v>
+        <v>739</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>731</v>
+        <v>740</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>732</v>
+        <v>741</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>102</v>
@@ -12241,7 +12739,7 @@
         <v>24</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12249,13 +12747,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>733</v>
+        <v>742</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>734</v>
+        <v>743</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>778</v>
+        <v>744</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>70</v>
@@ -12277,7 +12775,7 @@
         <v>24</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12285,13 +12783,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>736</v>
+        <v>746</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>779</v>
+        <v>747</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>81</v>
@@ -12313,7 +12811,7 @@
         <v>24</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M13" s="3" t="s">
         <v>145</v>
@@ -12324,13 +12822,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>799</v>
+        <v>750</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>85</v>
@@ -12346,13 +12844,13 @@
         <v>-25</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12360,13 +12858,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>48</v>
@@ -12388,7 +12886,7 @@
         <v>24</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12396,13 +12894,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>787</v>
+        <v>756</v>
       </c>
       <c r="F16" s="7">
         <v>1</v>
@@ -12424,7 +12922,7 @@
         <v>24</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="17" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12432,13 +12930,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>744</v>
+        <v>757</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>745</v>
+        <v>758</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>784</v>
+        <v>759</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>63</v>
@@ -12460,7 +12958,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="18" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12471,7 +12969,7 @@
         <v>33</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>746</v>
+        <v>760</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>597</v>
@@ -12490,13 +12988,13 @@
         <v>0</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M18" s="8" t="s">
         <v>138</v>
@@ -12507,13 +13005,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>747</v>
+        <v>761</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>748</v>
+        <v>762</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>749</v>
+        <v>763</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>22</v>
@@ -12529,13 +13027,13 @@
         <v>-30</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12543,13 +13041,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>750</v>
+        <v>764</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>102</v>
@@ -12561,7 +13059,7 @@
         <v>30</v>
       </c>
       <c r="I20" s="3">
-        <f>G20-H20</f>
+        <f t="shared" si="0"/>
         <v>2280</v>
       </c>
       <c r="J20" s="3" t="s">
@@ -12571,7 +13069,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>145</v>
@@ -12582,13 +13080,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>793</v>
+        <v>767</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>752</v>
+        <v>768</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>794</v>
+        <v>769</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>22</v>
@@ -12604,13 +13102,13 @@
         <v>370</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="22" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12621,10 +13119,10 @@
         <v>680</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>753</v>
+        <v>770</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>786</v>
+        <v>771</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>308</v>
@@ -12646,7 +13144,7 @@
         <v>24</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>138</v>
@@ -12657,13 +13155,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>754</v>
+        <v>772</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>755</v>
+        <v>773</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>756</v>
+        <v>774</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>239</v>
@@ -12679,13 +13177,13 @@
         <v>640</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="24" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12696,10 +13194,10 @@
         <v>240</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>757</v>
+        <v>775</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>70</v>
@@ -12721,7 +13219,7 @@
         <v>24</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="25" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12729,13 +13227,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>758</v>
+        <v>777</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>759</v>
+        <v>778</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>760</v>
+        <v>779</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>63</v>
@@ -12757,7 +13255,7 @@
         <v>24</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="26" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12768,7 +13266,7 @@
         <v>711</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>761</v>
+        <v>780</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>713</v>
@@ -12793,7 +13291,7 @@
         <v>24</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>138</v>
@@ -12822,7 +13320,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="6">
-        <f t="shared" ref="I27" si="1">G27-H27</f>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J27" s="6" t="s">
@@ -12832,7 +13330,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="28" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12840,13 +13338,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>762</v>
+        <v>784</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>763</v>
+        <v>785</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>764</v>
+        <v>786</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>22</v>
@@ -12862,13 +13360,13 @@
         <v>790</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="29" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12876,13 +13374,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>795</v>
+        <v>787</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>765</v>
+        <v>788</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>127</v>
@@ -12898,13 +13396,13 @@
         <v>-25</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="30" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12912,13 +13410,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>766</v>
+        <v>790</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>767</v>
+        <v>791</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>59</v>
@@ -12940,7 +13438,7 @@
         <v>24</v>
       </c>
       <c r="L30" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="31" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12948,13 +13446,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>131</v>
@@ -12970,13 +13468,13 @@
         <v>740</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
     </row>
     <row r="32" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12987,7 +13485,7 @@
         <v>118</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>769</v>
+        <v>796</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>120</v>
@@ -13012,7 +13510,7 @@
         <v>24</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M32" s="3" t="s">
         <v>138</v>
@@ -13023,13 +13521,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>770</v>
+        <v>797</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>771</v>
+        <v>798</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="F33" s="6" t="s">
         <v>63</v>
@@ -13051,7 +13549,2315 @@
         <v>24</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>724</v>
+        <v>726</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:Q62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="93.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>922</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>801</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>923</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G3" s="6">
+        <v>685</v>
+      </c>
+      <c r="H3" s="6">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>660</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>803</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>957</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3">
+        <v>975</v>
+      </c>
+      <c r="H5" s="3">
+        <v>25</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>809</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>810</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>811</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1800</v>
+      </c>
+      <c r="H6" s="8">
+        <v>30</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="0"/>
+        <v>1770</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>812</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>958</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G7" s="8">
+        <v>35</v>
+      </c>
+      <c r="H7" s="8">
+        <v>35</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>814</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3">
+        <v>850</v>
+      </c>
+      <c r="H8" s="3">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>909</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>910</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3">
+        <v>400</v>
+      </c>
+      <c r="H9" s="3">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>817</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>818</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>819</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>20</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="3">
+        <v>840</v>
+      </c>
+      <c r="H12" s="3">
+        <v>20</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>822</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>917</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>918</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G13" s="6">
+        <v>1060</v>
+      </c>
+      <c r="H13" s="6">
+        <v>20</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>823</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="8">
+        <v>820</v>
+      </c>
+      <c r="H14" s="8">
+        <v>30</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>907</v>
+      </c>
+      <c r="F15" s="4">
+        <v>2</v>
+      </c>
+      <c r="G15" s="3">
+        <v>790</v>
+      </c>
+      <c r="H15" s="3">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>828</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G16" s="8">
+        <v>790</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>924</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>829</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>925</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>920</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>830</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>831</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="6">
+        <v>845</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>832</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>833</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1</v>
+      </c>
+      <c r="G19" s="6">
+        <v>915</v>
+      </c>
+      <c r="H19" s="6">
+        <v>25</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="3">
+        <v>970</v>
+      </c>
+      <c r="H20" s="3">
+        <v>20</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>912</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G21" s="3">
+        <v>975</v>
+      </c>
+      <c r="H21" s="3">
+        <v>25</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="3">
+        <v>890</v>
+      </c>
+      <c r="H22" s="3">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>860</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>838</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>950</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="8">
+        <v>780</v>
+      </c>
+      <c r="H23" s="8">
+        <v>30</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>839</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>840</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="8">
+        <v>1090</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>900</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>901</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H25" s="3">
+        <v>20</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>1280</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>842</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>843</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>844</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="8">
+        <v>850</v>
+      </c>
+      <c r="H26" s="8">
+        <v>30</v>
+      </c>
+      <c r="I26" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="3">
+        <v>750</v>
+      </c>
+      <c r="H27" s="3">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>926</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>846</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" s="6">
+        <v>1135</v>
+      </c>
+      <c r="H28" s="6">
+        <v>25</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="0"/>
+        <v>1110</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>921</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>847</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>848</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G29" s="6">
+        <v>1065</v>
+      </c>
+      <c r="H29" s="6">
+        <v>25</v>
+      </c>
+      <c r="I29" s="6">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>948</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>849</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G30" s="8">
+        <v>1185</v>
+      </c>
+      <c r="H30" s="8">
+        <v>35</v>
+      </c>
+      <c r="I30" s="8">
+        <f t="shared" si="0"/>
+        <v>1150</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>850</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>851</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>919</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G31" s="6">
+        <v>465</v>
+      </c>
+      <c r="H31" s="6">
+        <v>25</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>751</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>908</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G32" s="3">
+        <v>380</v>
+      </c>
+      <c r="H32" s="3">
+        <v>30</v>
+      </c>
+      <c r="I32" s="3">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>854</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G33" s="6">
+        <v>815</v>
+      </c>
+      <c r="H33" s="6">
+        <v>25</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>856</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>857</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>947</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G34" s="8">
+        <v>975</v>
+      </c>
+      <c r="H34" s="8">
+        <v>25</v>
+      </c>
+      <c r="I34" s="8">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>955</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>858</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G35" s="8">
+        <v>0</v>
+      </c>
+      <c r="H35" s="8">
+        <v>30</v>
+      </c>
+      <c r="I35" s="8">
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <v>-30</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>859</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>860</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="8">
+        <v>905</v>
+      </c>
+      <c r="H36" s="8">
+        <v>35</v>
+      </c>
+      <c r="I36" s="8">
+        <f t="shared" si="1"/>
+        <v>870</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>931</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>861</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>932</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G37" s="6">
+        <v>845</v>
+      </c>
+      <c r="H37" s="6">
+        <v>25</v>
+      </c>
+      <c r="I37" s="6">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J37" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>962</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>862</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>963</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38" s="8">
+        <v>0</v>
+      </c>
+      <c r="H38" s="8">
+        <v>25</v>
+      </c>
+      <c r="I38" s="8">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>863</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>864</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="8">
+        <v>0</v>
+      </c>
+      <c r="H39" s="8">
+        <v>30</v>
+      </c>
+      <c r="I39" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>866</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>867</v>
+      </c>
+      <c r="F40" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G40" s="8">
+        <v>820</v>
+      </c>
+      <c r="H40" s="8">
+        <v>30</v>
+      </c>
+      <c r="I40" s="8">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>868</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>936</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G41" s="6">
+        <v>3360</v>
+      </c>
+      <c r="H41" s="6">
+        <v>35</v>
+      </c>
+      <c r="I41" s="6">
+        <f t="shared" si="1"/>
+        <v>3325</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>802</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>869</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G42" s="6">
+        <v>895</v>
+      </c>
+      <c r="H42" s="6">
+        <v>25</v>
+      </c>
+      <c r="I42" s="6">
+        <f t="shared" si="1"/>
+        <v>870</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G43" s="3">
+        <v>0</v>
+      </c>
+      <c r="H43" s="3">
+        <v>20</v>
+      </c>
+      <c r="I43" s="3">
+        <f t="shared" si="1"/>
+        <v>-20</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>873</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>874</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G44" s="6">
+        <v>795</v>
+      </c>
+      <c r="H44" s="6">
+        <v>25</v>
+      </c>
+      <c r="I44" s="6">
+        <f t="shared" si="1"/>
+        <v>770</v>
+      </c>
+      <c r="J44" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>875</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>876</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>960</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G45" s="8">
+        <v>780</v>
+      </c>
+      <c r="H45" s="8">
+        <v>30</v>
+      </c>
+      <c r="I45" s="8">
+        <f t="shared" si="1"/>
+        <v>750</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>877</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>878</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G46" s="8">
+        <v>890</v>
+      </c>
+      <c r="H46" s="8">
+        <v>30</v>
+      </c>
+      <c r="I46" s="8">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>879</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>929</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>880</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G47" s="6">
+        <v>0</v>
+      </c>
+      <c r="H47" s="6">
+        <v>25</v>
+      </c>
+      <c r="I47" s="6">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J47" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>881</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>882</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>930</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G48" s="6">
+        <v>865</v>
+      </c>
+      <c r="H48" s="6">
+        <v>25</v>
+      </c>
+      <c r="I48" s="6">
+        <f t="shared" si="1"/>
+        <v>840</v>
+      </c>
+      <c r="J48" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>883</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>884</v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>885</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G49" s="8">
+        <v>900</v>
+      </c>
+      <c r="H49" s="8">
+        <v>30</v>
+      </c>
+      <c r="I49" s="8">
+        <f t="shared" si="1"/>
+        <v>870</v>
+      </c>
+      <c r="J49" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K49" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>886</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>887</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G50" s="3">
+        <v>0</v>
+      </c>
+      <c r="H50" s="3">
+        <v>30</v>
+      </c>
+      <c r="I50" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>888</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>889</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G51" s="8">
+        <v>845</v>
+      </c>
+      <c r="H51" s="8">
+        <v>25</v>
+      </c>
+      <c r="I51" s="8">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>890</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>891</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>933</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G52" s="6">
+        <v>915</v>
+      </c>
+      <c r="H52" s="6">
+        <v>25</v>
+      </c>
+      <c r="I52" s="6">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J52" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>892</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>893</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>894</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G53" s="6">
+        <v>715</v>
+      </c>
+      <c r="H53" s="6">
+        <v>25</v>
+      </c>
+      <c r="I53" s="6">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J53" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="6" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>895</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>896</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>897</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G54" s="8">
+        <v>30</v>
+      </c>
+      <c r="H54" s="8">
+        <v>30</v>
+      </c>
+      <c r="I54" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>898</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>911</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G55" s="3">
+        <v>455</v>
+      </c>
+      <c r="H55" s="3">
+        <v>25</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="1"/>
+        <v>430</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>946</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G56" s="8">
+        <v>30</v>
+      </c>
+      <c r="H56" s="8">
+        <v>30</v>
+      </c>
+      <c r="I56" s="8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J56" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K56" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>899</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G57" s="3">
+        <v>1405</v>
+      </c>
+      <c r="H57" s="3">
+        <v>35</v>
+      </c>
+      <c r="I57" s="3">
+        <f t="shared" si="1"/>
+        <v>1370</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>945</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G58" s="8">
+        <v>0</v>
+      </c>
+      <c r="H58" s="8">
+        <v>30</v>
+      </c>
+      <c r="I58" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J58" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="K58" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L58" s="8" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>416</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>417</v>
+      </c>
+      <c r="E59" s="11" t="s">
+        <v>418</v>
+      </c>
+      <c r="F59" s="12">
+        <v>8</v>
+      </c>
+      <c r="G59" s="11">
+        <v>690</v>
+      </c>
+      <c r="H59" s="11">
+        <v>30</v>
+      </c>
+      <c r="I59" s="11">
+        <v>660</v>
+      </c>
+      <c r="J59" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="K59" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L59" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="M59" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N59" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O59" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P59" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q59" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E60" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F60" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="G60" s="11">
+        <v>720</v>
+      </c>
+      <c r="H60" s="11">
+        <v>30</v>
+      </c>
+      <c r="I60" s="11">
+        <v>690</v>
+      </c>
+      <c r="J60" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K60" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L60" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N60" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O60" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P60" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q60" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>937</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>938</v>
+      </c>
+      <c r="E61" s="11" t="s">
+        <v>939</v>
+      </c>
+      <c r="F61" s="12">
+        <v>7</v>
+      </c>
+      <c r="G61" s="11">
+        <v>690</v>
+      </c>
+      <c r="H61" s="11">
+        <v>30</v>
+      </c>
+      <c r="I61" s="11">
+        <v>660</v>
+      </c>
+      <c r="J61" s="11" t="s">
+        <v>280</v>
+      </c>
+      <c r="K61" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L61" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="M61" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N61" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O61" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P61" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q61" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B62" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>940</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>941</v>
+      </c>
+      <c r="E62" s="11" t="s">
+        <v>942</v>
+      </c>
+      <c r="F62" s="12">
+        <v>7</v>
+      </c>
+      <c r="G62" s="11">
+        <v>1380</v>
+      </c>
+      <c r="H62" s="11">
+        <v>30</v>
+      </c>
+      <c r="I62" s="11">
+        <v>1350</v>
+      </c>
+      <c r="J62" s="11" t="s">
+        <v>943</v>
+      </c>
+      <c r="K62" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L62" s="11" t="s">
+        <v>944</v>
+      </c>
+      <c r="M62" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N62" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O62" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P62" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q62" s="11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A0C4ED8-891A-4361-B3AE-706A189CA14C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5ED4305-8A78-4E1A-A2DB-6B96350A2AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="08-05" sheetId="10" r:id="rId6"/>
     <sheet name="09-05" sheetId="11" r:id="rId7"/>
     <sheet name="11-05" sheetId="12" r:id="rId8"/>
+    <sheet name="12-05" sheetId="13" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2793" uniqueCount="965">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3019" uniqueCount="1034">
   <si>
     <t>THU 6</t>
   </si>
@@ -2448,9 +2449,15 @@
     <t>NGAY 11-5</t>
   </si>
   <si>
+    <t>quyên quyên</t>
+  </si>
+  <si>
     <t>HD019808</t>
   </si>
   <si>
+    <t>89 thành thái diên hồng</t>
+  </si>
+  <si>
     <t>11-05-2026</t>
   </si>
   <si>
@@ -2460,6 +2467,9 @@
     <t>HD019693</t>
   </si>
   <si>
+    <t>C16-17 lô C1, đường DD5, phường Đông Hưng Thuận (ghi chú: sau lưng chợ An Sương)</t>
+  </si>
+  <si>
     <t>AT 11-05</t>
   </si>
   <si>
@@ -2484,15 +2494,27 @@
     <t>HD019881</t>
   </si>
   <si>
+    <t>100.đinh văn ước ấp5 xã hưng long</t>
+  </si>
+  <si>
     <t>Kiên Thị Thanh Hiền</t>
   </si>
   <si>
     <t>HD019616</t>
   </si>
   <si>
+    <t>31 đường số 30 phường cát lái</t>
+  </si>
+  <si>
+    <t>Cẩm Tú</t>
+  </si>
+  <si>
     <t>HD019735</t>
   </si>
   <si>
+    <t>chung cư terrace 21 võ trường toản</t>
+  </si>
+  <si>
     <t>HD019469</t>
   </si>
   <si>
@@ -2511,18 +2533,36 @@
     <t>HD019905</t>
   </si>
   <si>
+    <t>Vinhomes central park( park 2 -P2) 720a Điện Biên Phủ, Phường 22</t>
+  </si>
+  <si>
     <t>Ngô Thị Bích Loan</t>
   </si>
   <si>
+    <t>HD019556</t>
+  </si>
+  <si>
+    <t>167 đặng văn ngữ</t>
+  </si>
+  <si>
+    <t>Ruby Cẩm Tú</t>
+  </si>
+  <si>
     <t>HD019626</t>
   </si>
   <si>
+    <t>61 bui diên p4</t>
+  </si>
+  <si>
     <t>Mary Tran</t>
   </si>
   <si>
     <t>HD019738</t>
   </si>
   <si>
+    <t>9/5 đường số 66 Phường thảo điền</t>
+  </si>
+  <si>
     <t>Phương Bình</t>
   </si>
   <si>
@@ -2532,9 +2572,18 @@
     <t>CC Ehome3, Hồ Học Lãm, An Lạc</t>
   </si>
   <si>
+    <t>Trần Chi / Yaya Tran</t>
+  </si>
+  <si>
     <t>HD019782</t>
   </si>
   <si>
+    <t>36 sư vạn hạnh p9</t>
+  </si>
+  <si>
+    <t>Nhy Lê</t>
+  </si>
+  <si>
     <t>HD019780</t>
   </si>
   <si>
@@ -2547,30 +2596,60 @@
     <t>HD019907</t>
   </si>
   <si>
+    <t>Toà nhà lux 6...Vinhomes Golden River (Bason), 2 Nguyễn Hữu Cảnh, P. Bến Nghé</t>
+  </si>
+  <si>
     <t>Trang Nhung Bui</t>
   </si>
   <si>
     <t>HD019787</t>
   </si>
   <si>
+    <t>Toà Golden House - Sunwah Pearl 90 Nguyễn Hữu Cảnh - phường 22</t>
+  </si>
+  <si>
+    <t>chi hương fb Kim Tien Pham</t>
+  </si>
+  <si>
     <t>HD19599</t>
   </si>
   <si>
+    <t>Đỗ Thị Kiều Chinh</t>
+  </si>
+  <si>
     <t>HD019899</t>
   </si>
   <si>
+    <t>42, đường 21,Khu dân cư bình chiểu, P tam binh (chợ đầu mối nông sản thủ đức)</t>
+  </si>
+  <si>
     <t>Nguyễn Thị Ngọc Ngà</t>
   </si>
   <si>
+    <t>HD019744</t>
+  </si>
+  <si>
+    <t>38b đường số 12 tân quy</t>
+  </si>
+  <si>
     <t>Minh Hải ( Ruby Eyelash - Nail )</t>
   </si>
   <si>
     <t>HD019891</t>
   </si>
   <si>
+    <t>17 Đường Số 13 Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Dung Nguyen</t>
+  </si>
+  <si>
     <t>HD019705</t>
   </si>
   <si>
+    <t>15/32/2 võ duy ninh f22</t>
+  </si>
+  <si>
     <t>Đỗ Đông Mi</t>
   </si>
   <si>
@@ -2580,30 +2659,57 @@
     <t>115 phan huy thuc ptan kieng</t>
   </si>
   <si>
+    <t>Vân Ốc</t>
+  </si>
+  <si>
     <t>HD019745</t>
   </si>
   <si>
+    <t>16 đường 6, p linh chiểu</t>
+  </si>
+  <si>
+    <t>Phi Phụng</t>
+  </si>
+  <si>
     <t>HD019753</t>
   </si>
   <si>
+    <t>85 hồ tùng mậu bến nghé</t>
+  </si>
+  <si>
+    <t>Vi Chanel</t>
+  </si>
+  <si>
     <t>HD019639</t>
   </si>
   <si>
     <t>132 Bến Vân Đồn Chung cư Millennium toà A 22.07</t>
   </si>
   <si>
+    <t>Nguyễn Cao Kim Anh</t>
+  </si>
+  <si>
     <t>HD019644</t>
   </si>
   <si>
+    <t>264 lê văn lương phước kiểng</t>
+  </si>
+  <si>
     <t>Huỳnh Kim</t>
   </si>
   <si>
     <t>HD019764</t>
   </si>
   <si>
+    <t>109 bến vân đồn, phường 9</t>
+  </si>
+  <si>
     <t>HD019779</t>
   </si>
   <si>
+    <t>Gate 4 - Feliz en vista, 1 trương văn bang, thạnh mỹ lợi Toà cruz - C810</t>
+  </si>
+  <si>
     <t>Huynh Anh</t>
   </si>
   <si>
@@ -2619,6 +2725,15 @@
     <t>HD019781</t>
   </si>
   <si>
+    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà cũ</t>
+  </si>
+  <si>
+    <t>Kaity Hg</t>
+  </si>
+  <si>
+    <t>HD019671</t>
+  </si>
+  <si>
     <t>6B8/23/1c hương lộ 2, p bình trị đông A</t>
   </si>
   <si>
@@ -2628,12 +2743,27 @@
     <t>HD019937</t>
   </si>
   <si>
+    <t>Chung cư an gia thị trấn Tân túc</t>
+  </si>
+  <si>
+    <t>Tuyet Nhung Nguyen</t>
+  </si>
+  <si>
     <t>HD019767</t>
   </si>
   <si>
+    <t>36 Lê lai phường Bảy Hiền</t>
+  </si>
+  <si>
+    <t>Thuỳ</t>
+  </si>
+  <si>
     <t>HD019994</t>
   </si>
   <si>
+    <t>24b tân sơn nhì</t>
+  </si>
+  <si>
     <t>W24130 miki</t>
   </si>
   <si>
@@ -2649,9 +2779,15 @@
     <t>88/29 đường 17, phường Tân thuận Tây</t>
   </si>
   <si>
+    <t>Chị Dương - fb Lien Phuong Bui</t>
+  </si>
+  <si>
     <t>HD019733</t>
   </si>
   <si>
+    <t>14 Bạch Mã, p15 cư xá bắc hải</t>
+  </si>
+  <si>
     <t>HD019969</t>
   </si>
   <si>
@@ -2670,21 +2806,33 @@
     <t>HD020012</t>
   </si>
   <si>
+    <t>38 Nguyễn Bá Tuyển, P12</t>
+  </si>
+  <si>
     <t>Yến Phương</t>
   </si>
   <si>
     <t>HD020005</t>
   </si>
   <si>
+    <t>Toà nhà Namn 10 đường số 67 phường tân quy</t>
+  </si>
+  <si>
     <t>Lê Hữu Nhân</t>
   </si>
   <si>
     <t>HD019980</t>
   </si>
   <si>
+    <t>53/3B Mai Hắc Đế, phường Phú Định</t>
+  </si>
+  <si>
     <t>Ama Bella - zalo</t>
   </si>
   <si>
+    <t>HD020009</t>
+  </si>
+  <si>
     <t>363 Hùng Vương An Đông</t>
   </si>
   <si>
@@ -2694,6 +2842,9 @@
     <t>HD019977</t>
   </si>
   <si>
+    <t>196/16 Đề Thám, P. Cầu Ông Lãnh</t>
+  </si>
+  <si>
     <t>Anh Thu</t>
   </si>
   <si>
@@ -2709,18 +2860,27 @@
     <t>HD019939</t>
   </si>
   <si>
+    <t>cổng B Cát Lái đường Lê Phụng Hiểu, Cát Lái</t>
+  </si>
+  <si>
     <t>Võ Trần Như Bích</t>
   </si>
   <si>
     <t>HD019760</t>
   </si>
   <si>
+    <t>Chung cư Richstar 1, sảnh RS1 - 278A Hoà Bình, P. Hiệp Tân</t>
+  </si>
+  <si>
     <t>Mỹ Hương</t>
   </si>
   <si>
     <t>HD020008</t>
   </si>
   <si>
+    <t>1A Đ. Lý Thường Kiệt, Phường 7</t>
+  </si>
+  <si>
     <t>Diễm My</t>
   </si>
   <si>
@@ -2742,118 +2902,19 @@
     <t>HƯƠNG TRẦN</t>
   </si>
   <si>
+    <t>261/26c chu văn an p12</t>
+  </si>
+  <si>
+    <t>135 hải thượng lãn Ông P10</t>
+  </si>
+  <si>
     <t>UYÊN MI</t>
   </si>
   <si>
-    <t>Dung Nguyen</t>
-  </si>
-  <si>
-    <t>15/32/2 võ duy ninh f22</t>
-  </si>
-  <si>
-    <t>cổng B Cát Lái đường Lê Phụng Hiểu, Cát Lái</t>
-  </si>
-  <si>
     <t>78 Trần Não, P. An Khánh</t>
   </si>
   <si>
-    <t>Toà Golden House - Sunwah Pearl 90 Nguyễn Hữu Cảnh - phường 22</t>
-  </si>
-  <si>
-    <t>16 đường 6, p linh chiểu</t>
-  </si>
-  <si>
-    <t>Vân Ốc</t>
-  </si>
-  <si>
-    <t>9/5 đường số 66 Phường thảo điền</t>
-  </si>
-  <si>
-    <t>Gate 4 - Feliz en vista, 1 trương văn bang, thạnh mỹ lợi Toà cruz - C810</t>
-  </si>
-  <si>
-    <t>Cẩm Tú</t>
-  </si>
-  <si>
-    <t>chung cư terrace 21 võ trường toản</t>
-  </si>
-  <si>
-    <t>261/26c chu văn an p12</t>
-  </si>
-  <si>
-    <t>chi hương fb Kim Tien Pham</t>
-  </si>
-  <si>
-    <t>31 đường số 30 phường cát lái</t>
-  </si>
-  <si>
-    <t>Đỗ Thị Kiều Chinh</t>
-  </si>
-  <si>
-    <t>42, đường 21,Khu dân cư bình chiểu, P tam binh (chợ đầu mối nông sản thủ đức)</t>
-  </si>
-  <si>
-    <t>Vinhomes central park( park 2 -P2) 720a Điện Biên Phủ, Phường 22</t>
-  </si>
-  <si>
-    <t>HD019556</t>
-  </si>
-  <si>
-    <t>167 đặng văn ngữ</t>
-  </si>
-  <si>
-    <t>109 bến vân đồn, phường 9</t>
-  </si>
-  <si>
-    <t>Nhy Lê</t>
-  </si>
-  <si>
-    <t>Vi Chanel</t>
-  </si>
-  <si>
-    <t>quyên quyên</t>
-  </si>
-  <si>
-    <t>89 thành thái diên hồng</t>
-  </si>
-  <si>
-    <t>Trần Chi / Yaya Tran</t>
-  </si>
-  <si>
-    <t>36 sư vạn hạnh p9</t>
-  </si>
-  <si>
-    <t>Phi Phụng</t>
-  </si>
-  <si>
-    <t>85 hồ tùng mậu bến nghé</t>
-  </si>
-  <si>
-    <t>Toà nhà lux 6...Vinhomes Golden River (Bason), 2 Nguyễn Hữu Cảnh, P. Bến Nghé</t>
-  </si>
-  <si>
-    <t>HD020009</t>
-  </si>
-  <si>
-    <t>196/16 Đề Thám, P. Cầu Ông Lãnh</t>
-  </si>
-  <si>
-    <t>Tuyet Nhung Nguyen</t>
-  </si>
-  <si>
-    <t>36 Lê lai phường Bảy Hiền</t>
-  </si>
-  <si>
-    <t>1A Đ. Lý Thường Kiệt, Phường 7</t>
-  </si>
-  <si>
-    <t>38 Nguyễn Bá Tuyển, P12</t>
-  </si>
-  <si>
-    <t>Chị Dương - fb Lien Phuong Bui</t>
-  </si>
-  <si>
-    <t>14 Bạch Mã, p15 cư xá bắc hải</t>
+    <t>MIE</t>
   </si>
   <si>
     <t>Thanh Trần</t>
@@ -2880,64 +2941,211 @@
     <t>22-04-2026</t>
   </si>
   <si>
-    <t>MIE</t>
-  </si>
-  <si>
-    <t>135 hải thượng lãn Ông P10</t>
-  </si>
-  <si>
-    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà cũ</t>
-  </si>
-  <si>
-    <t>Nguyễn Cao Kim Anh</t>
-  </si>
-  <si>
-    <t>264 lê văn lương phước kiểng</t>
-  </si>
-  <si>
-    <t>HD019744</t>
-  </si>
-  <si>
-    <t>38b đường số 12 tân quy</t>
-  </si>
-  <si>
-    <t>17 Đường Số 13 Phường Bình Hưng Hòa</t>
-  </si>
-  <si>
-    <t>Ruby Cẩm Tú</t>
-  </si>
-  <si>
-    <t>61 bui diên p4</t>
-  </si>
-  <si>
-    <t>Kaity Hg</t>
-  </si>
-  <si>
-    <t>HD019671</t>
-  </si>
-  <si>
-    <t>C16-17 lô C1, đường DD5, phường Đông Hưng Thuận (ghi chú: sau lưng chợ An Sương)</t>
-  </si>
-  <si>
-    <t>100.đinh văn ước ấp5 xã hưng long</t>
-  </si>
-  <si>
-    <t>53/3B Mai Hắc Đế, phường Phú Định</t>
-  </si>
-  <si>
-    <t>Toà nhà Namn 10 đường số 67 phường tân quy</t>
-  </si>
-  <si>
-    <t>Chung cư Richstar 1, sảnh RS1 - 278A Hoà Bình, P. Hiệp Tân</t>
-  </si>
-  <si>
-    <t>Thuỳ</t>
-  </si>
-  <si>
-    <t>24b tân sơn nhì</t>
-  </si>
-  <si>
-    <t>Chung cư an gia thị trấn Tân túc</t>
+    <t>NGAY 12-5</t>
+  </si>
+  <si>
+    <t>Thế Diễm</t>
+  </si>
+  <si>
+    <t>HD020049</t>
+  </si>
+  <si>
+    <t>159 Võ Nguyên Giáp, P Thảo Điền Chung cư Masteri Thảo Điền (Tháp 3)</t>
+  </si>
+  <si>
+    <t>12-05-2026</t>
+  </si>
+  <si>
+    <t>kim xuyến</t>
+  </si>
+  <si>
+    <t>HD019918</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bửu p6</t>
+  </si>
+  <si>
+    <t>AT 12-05</t>
+  </si>
+  <si>
+    <t>Trần Thị Ngọc Trâm</t>
+  </si>
+  <si>
+    <t>HD020123</t>
+  </si>
+  <si>
+    <t>5/1H đường số 11 Bình Thọ</t>
+  </si>
+  <si>
+    <t>HD020162</t>
+  </si>
+  <si>
+    <t>Bella</t>
+  </si>
+  <si>
+    <t>HD020155</t>
+  </si>
+  <si>
+    <t>Lọ Lem</t>
+  </si>
+  <si>
+    <t>HD020148</t>
+  </si>
+  <si>
+    <t>Bella Tran (Lê Huy)</t>
+  </si>
+  <si>
+    <t>HD020184</t>
+  </si>
+  <si>
+    <t>67B đường T5, phường Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Phạm Oanh</t>
+  </si>
+  <si>
+    <t>510 Ngô Gia Tự, P.An Đông</t>
+  </si>
+  <si>
+    <t>HD020192</t>
+  </si>
+  <si>
+    <t>Hải Anh</t>
+  </si>
+  <si>
+    <t>Trần Thị Kim Phương</t>
+  </si>
+  <si>
+    <t>HD020054</t>
+  </si>
+  <si>
+    <t>Hoàng Thị Hồng</t>
+  </si>
+  <si>
+    <t>HD020036</t>
+  </si>
+  <si>
+    <t>Trinh Kim</t>
+  </si>
+  <si>
+    <t>HD020079</t>
+  </si>
+  <si>
+    <t>2117A/9 Phạm Thế Hiển phường 6</t>
+  </si>
+  <si>
+    <t>Hoang Yen</t>
+  </si>
+  <si>
+    <t>HD020081</t>
+  </si>
+  <si>
+    <t>Thiên Nga</t>
+  </si>
+  <si>
+    <t>HD020151</t>
+  </si>
+  <si>
+    <t>HD020221</t>
+  </si>
+  <si>
+    <t>Tram Hoang Ngoc</t>
+  </si>
+  <si>
+    <t>HD020186</t>
+  </si>
+  <si>
+    <t>105K 15 hồ thị kỷ vườn lài</t>
+  </si>
+  <si>
+    <t>Thu Thủy</t>
+  </si>
+  <si>
+    <t>HD020187</t>
+  </si>
+  <si>
+    <t>287 Kinh Dương Vương, P An Lạc</t>
+  </si>
+  <si>
+    <t>Phương Anh Chu</t>
+  </si>
+  <si>
+    <t>HD020219</t>
+  </si>
+  <si>
+    <t>Chung cư Grand Riverside - 278 Bến Vân Đồn P2</t>
+  </si>
+  <si>
+    <t>Đoàn Ngọc</t>
+  </si>
+  <si>
+    <t>HD020082</t>
+  </si>
+  <si>
+    <t>137/2 bình long</t>
+  </si>
+  <si>
+    <t>Em Na</t>
+  </si>
+  <si>
+    <t>L-1506, chung cư One Verandah, số 2 Bát Nàn p. Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
+    <t>HDO1778410597940_472532</t>
+  </si>
+  <si>
+    <t>652/7A Cộng Hoà - P13</t>
+  </si>
+  <si>
+    <t>209/8 nguyễn duy cung, P12</t>
+  </si>
+  <si>
+    <t>HẠNH NARIN</t>
+  </si>
+  <si>
+    <t>484B no trang long p13</t>
+  </si>
+  <si>
+    <t>#301 Pham Ngu Lao Street</t>
+  </si>
+  <si>
+    <t>Chị Quyên fb An Nhiên</t>
+  </si>
+  <si>
+    <t>HD020066</t>
+  </si>
+  <si>
+    <t>HD020091</t>
+  </si>
+  <si>
+    <t>594/7 điện biên phủ p10</t>
+  </si>
+  <si>
+    <t>Nguyễn My</t>
+  </si>
+  <si>
+    <t>Tk18/3 nguyễn cảnh chân p cầu kho</t>
+  </si>
+  <si>
+    <t>Xe Khải Nam</t>
+  </si>
+  <si>
+    <t>S5.02 Vinhomes grand park, Nguyễn Xiển, Long Mỹ</t>
+  </si>
+  <si>
+    <t>1870\1\98\14a tỉnh lộ 10 tân tạo bình tân</t>
+  </si>
+  <si>
+    <t>HD020045</t>
+  </si>
+  <si>
+    <t>Cty Eidaikake xưởng 2. đường số 8 phường tân thuận đông đường huỳnh tấn phát kcxtt</t>
+  </si>
+  <si>
+    <t>Eco green tòa E nguyễn văn linh tân thuận tây</t>
+  </si>
+  <si>
+    <t>90a /10/10 Âu duong lân p3</t>
   </si>
 </sst>
 </file>
@@ -13562,10 +13770,12 @@
   <dimension ref="A1:Q62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="47.28515625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="93.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.28515625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -13637,13 +13847,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>922</v>
+        <v>801</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>923</v>
+        <v>803</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>308</v>
@@ -13665,7 +13875,7 @@
         <v>24</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13673,13 +13883,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>957</v>
+        <v>807</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>29</v>
@@ -13695,13 +13905,13 @@
         <v>-30</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13709,13 +13919,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>70</v>
@@ -13737,7 +13947,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13745,13 +13955,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>131</v>
@@ -13767,13 +13977,13 @@
         <v>1770</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13784,10 +13994,10 @@
         <v>500</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>958</v>
+        <v>816</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>52</v>
@@ -13803,13 +14013,13 @@
         <v>0</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M7" s="8" t="s">
         <v>138</v>
@@ -13820,13 +14030,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>913</v>
+        <v>819</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>48</v>
@@ -13848,7 +14058,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13856,13 +14066,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>909</v>
+        <v>820</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>815</v>
+        <v>821</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>910</v>
+        <v>822</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>48</v>
@@ -13884,7 +14094,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13895,7 +14105,7 @@
         <v>708</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>710</v>
@@ -13920,7 +14130,7 @@
         <v>24</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>138</v>
@@ -13931,13 +14141,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>355</v>
@@ -13959,7 +14169,7 @@
         <v>24</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>138</v>
@@ -13970,13 +14180,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>916</v>
+        <v>829</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>81</v>
@@ -13998,7 +14208,7 @@
         <v>24</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14006,13 +14216,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>917</v>
+        <v>831</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>918</v>
+        <v>832</v>
       </c>
       <c r="F13" s="7" t="s">
         <v>355</v>
@@ -14034,7 +14244,7 @@
         <v>24</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14042,13 +14252,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>953</v>
+        <v>833</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>823</v>
+        <v>834</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>954</v>
+        <v>835</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>41</v>
@@ -14064,13 +14274,13 @@
         <v>790</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L14" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14078,13 +14288,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>907</v>
+        <v>838</v>
       </c>
       <c r="F15" s="4">
         <v>2</v>
@@ -14106,7 +14316,7 @@
         <v>24</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14114,13 +14324,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>826</v>
+        <v>839</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>827</v>
+        <v>840</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>828</v>
+        <v>841</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>22</v>
@@ -14136,13 +14346,13 @@
         <v>760</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="17" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14150,13 +14360,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>924</v>
+        <v>842</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>829</v>
+        <v>843</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>925</v>
+        <v>844</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>59</v>
@@ -14178,7 +14388,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14186,13 +14396,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>920</v>
+        <v>845</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>830</v>
+        <v>846</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>831</v>
+        <v>847</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>98</v>
@@ -14214,7 +14424,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="19" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14222,13 +14432,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>832</v>
+        <v>848</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>833</v>
+        <v>849</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>928</v>
+        <v>850</v>
       </c>
       <c r="F19" s="7">
         <v>1</v>
@@ -14250,7 +14460,7 @@
         <v>24</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="20" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14258,13 +14468,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>834</v>
+        <v>851</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>835</v>
+        <v>852</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>904</v>
+        <v>853</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>81</v>
@@ -14286,7 +14496,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="21" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14294,10 +14504,10 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>912</v>
+        <v>854</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>836</v>
+        <v>855</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>242</v>
@@ -14322,7 +14532,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="22" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14330,13 +14540,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>914</v>
+        <v>856</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>915</v>
+        <v>858</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>77</v>
@@ -14358,7 +14568,7 @@
         <v>24</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="23" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14366,13 +14576,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>838</v>
+        <v>859</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>950</v>
+        <v>860</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>951</v>
+        <v>861</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>131</v>
@@ -14388,13 +14598,13 @@
         <v>750</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="24" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14402,13 +14612,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>839</v>
+        <v>862</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>840</v>
+        <v>863</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>952</v>
+        <v>864</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>22</v>
@@ -14424,13 +14634,13 @@
         <v>1060</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="25" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14438,13 +14648,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>900</v>
+        <v>865</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>841</v>
+        <v>866</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>901</v>
+        <v>867</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>81</v>
@@ -14466,7 +14676,7 @@
         <v>24</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="26" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14474,13 +14684,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>842</v>
+        <v>868</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>843</v>
+        <v>869</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>844</v>
+        <v>870</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>131</v>
@@ -14496,13 +14706,13 @@
         <v>820</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="27" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14510,13 +14720,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>906</v>
+        <v>871</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>845</v>
+        <v>872</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>905</v>
+        <v>873</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>77</v>
@@ -14538,7 +14748,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="28" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14546,13 +14756,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>926</v>
+        <v>874</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>846</v>
+        <v>875</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>927</v>
+        <v>876</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>63</v>
@@ -14574,7 +14784,7 @@
         <v>24</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="29" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14582,13 +14792,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>921</v>
+        <v>877</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>847</v>
+        <v>878</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>848</v>
+        <v>879</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>186</v>
@@ -14610,7 +14820,7 @@
         <v>24</v>
       </c>
       <c r="L29" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="30" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14618,13 +14828,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>948</v>
+        <v>880</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>849</v>
+        <v>881</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>949</v>
+        <v>882</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>36</v>
@@ -14640,13 +14850,13 @@
         <v>1150</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="31" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14654,13 +14864,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>850</v>
+        <v>883</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>851</v>
+        <v>884</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>919</v>
+        <v>885</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>186</v>
@@ -14682,7 +14892,7 @@
         <v>24</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="32" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14693,10 +14903,10 @@
         <v>751</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>852</v>
+        <v>886</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>908</v>
+        <v>887</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>48</v>
@@ -14718,7 +14928,7 @@
         <v>24</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="33" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14726,13 +14936,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>853</v>
+        <v>888</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>854</v>
+        <v>889</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>855</v>
+        <v>890</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>98</v>
@@ -14754,7 +14964,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="34" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14762,13 +14972,13 @@
         <v>18</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>856</v>
+        <v>891</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>857</v>
+        <v>892</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>947</v>
+        <v>893</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>85</v>
@@ -14784,13 +14994,13 @@
         <v>950</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K34" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L34" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="35" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14798,13 +15008,13 @@
         <v>18</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>955</v>
+        <v>894</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>956</v>
+        <v>895</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>858</v>
+        <v>896</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>22</v>
@@ -14820,13 +15030,13 @@
         <v>-30</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K35" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="36" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14834,13 +15044,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>859</v>
+        <v>897</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>860</v>
+        <v>898</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>964</v>
+        <v>899</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>52</v>
@@ -14856,13 +15066,13 @@
         <v>870</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K36" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="37" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14870,13 +15080,13 @@
         <v>18</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>931</v>
+        <v>900</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>861</v>
+        <v>901</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>932</v>
+        <v>902</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>102</v>
@@ -14898,7 +15108,7 @@
         <v>24</v>
       </c>
       <c r="L37" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14906,13 +15116,13 @@
         <v>18</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>962</v>
+        <v>903</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>862</v>
+        <v>904</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>963</v>
+        <v>905</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>85</v>
@@ -14928,13 +15138,13 @@
         <v>-25</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K38" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="39" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14942,10 +15152,10 @@
         <v>18</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>863</v>
+        <v>906</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>864</v>
+        <v>907</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>29</v>
@@ -14961,13 +15171,13 @@
         <v>-30</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="40" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14975,13 +15185,13 @@
         <v>18</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>865</v>
+        <v>908</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>866</v>
+        <v>909</v>
       </c>
       <c r="E40" s="8" t="s">
-        <v>867</v>
+        <v>910</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>131</v>
@@ -14997,13 +15207,13 @@
         <v>790</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="41" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15011,13 +15221,13 @@
         <v>18</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>935</v>
+        <v>911</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>868</v>
+        <v>912</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>936</v>
+        <v>913</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>308</v>
@@ -15039,7 +15249,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>145</v>
@@ -15053,7 +15263,7 @@
         <v>558</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>869</v>
+        <v>914</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>560</v>
@@ -15078,7 +15288,7 @@
         <v>24</v>
       </c>
       <c r="L42" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="43" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15086,13 +15296,13 @@
         <v>18</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>870</v>
+        <v>915</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>871</v>
+        <v>916</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>872</v>
+        <v>917</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>81</v>
@@ -15114,7 +15324,7 @@
         <v>24</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="44" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15122,13 +15332,13 @@
         <v>18</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>873</v>
+        <v>918</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>874</v>
+        <v>919</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>934</v>
+        <v>920</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>102</v>
@@ -15150,7 +15360,7 @@
         <v>24</v>
       </c>
       <c r="L44" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="45" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15158,13 +15368,13 @@
         <v>18</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>875</v>
+        <v>921</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>876</v>
+        <v>922</v>
       </c>
       <c r="E45" s="8" t="s">
-        <v>960</v>
+        <v>923</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>131</v>
@@ -15180,13 +15390,13 @@
         <v>750</v>
       </c>
       <c r="J45" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K45" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L45" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="46" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15194,13 +15404,13 @@
         <v>18</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>877</v>
+        <v>924</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>878</v>
+        <v>925</v>
       </c>
       <c r="E46" s="8" t="s">
-        <v>959</v>
+        <v>926</v>
       </c>
       <c r="F46" s="9" t="s">
         <v>41</v>
@@ -15216,13 +15426,13 @@
         <v>860</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K46" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L46" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="47" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15230,13 +15440,13 @@
         <v>18</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>879</v>
+        <v>927</v>
       </c>
       <c r="D47" s="6" t="s">
+        <v>928</v>
+      </c>
+      <c r="E47" s="6" t="s">
         <v>929</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>880</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>59</v>
@@ -15258,7 +15468,7 @@
         <v>24</v>
       </c>
       <c r="L47" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="48" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15266,13 +15476,13 @@
         <v>18</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>881</v>
+        <v>930</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>882</v>
+        <v>931</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>63</v>
@@ -15294,7 +15504,7 @@
         <v>24</v>
       </c>
       <c r="L48" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="49" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15302,13 +15512,13 @@
         <v>18</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>883</v>
+        <v>933</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>884</v>
+        <v>934</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>885</v>
+        <v>935</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>41</v>
@@ -15324,13 +15534,13 @@
         <v>870</v>
       </c>
       <c r="J49" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K49" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L49" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="50" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15338,13 +15548,13 @@
         <v>18</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>886</v>
+        <v>936</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>887</v>
+        <v>937</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>902</v>
+        <v>938</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>48</v>
@@ -15366,7 +15576,7 @@
         <v>24</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="51" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15374,13 +15584,13 @@
         <v>18</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>888</v>
+        <v>939</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>889</v>
+        <v>940</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>961</v>
+        <v>941</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>85</v>
@@ -15396,13 +15606,13 @@
         <v>820</v>
       </c>
       <c r="J51" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K51" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L51" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="52" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15410,13 +15620,13 @@
         <v>18</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>890</v>
+        <v>942</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>891</v>
+        <v>943</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>102</v>
@@ -15438,7 +15648,7 @@
         <v>24</v>
       </c>
       <c r="L52" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="53" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15446,13 +15656,13 @@
         <v>18</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>892</v>
+        <v>945</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>893</v>
+        <v>946</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>894</v>
+        <v>947</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>186</v>
@@ -15474,7 +15684,7 @@
         <v>24</v>
       </c>
       <c r="L53" s="6" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="54" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15482,13 +15692,13 @@
         <v>18</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>895</v>
+        <v>948</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>896</v>
+        <v>949</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>897</v>
+        <v>950</v>
       </c>
       <c r="F54" s="9" t="s">
         <v>131</v>
@@ -15504,13 +15714,13 @@
         <v>0</v>
       </c>
       <c r="J54" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K54" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L54" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M54" s="8" t="s">
         <v>138</v>
@@ -15524,10 +15734,10 @@
         <v>18</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>898</v>
+        <v>951</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>911</v>
+        <v>952</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>81</v>
@@ -15549,7 +15759,7 @@
         <v>24</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="56" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15563,7 +15773,7 @@
         <v>197</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="F56" s="9" t="s">
         <v>59</v>
@@ -15579,13 +15789,13 @@
         <v>0</v>
       </c>
       <c r="J56" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K56" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L56" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="57" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15596,10 +15806,10 @@
         <v>18</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>899</v>
+        <v>954</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>903</v>
+        <v>955</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>48</v>
@@ -15621,7 +15831,7 @@
         <v>24</v>
       </c>
       <c r="L57" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="58" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15632,7 +15842,7 @@
         <v>18</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="E58" s="8" t="s">
         <v>630</v>
@@ -15651,13 +15861,13 @@
         <v>-30</v>
       </c>
       <c r="J58" s="8" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="K58" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L58" s="8" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
     </row>
     <row r="59" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -15765,13 +15975,13 @@
         <v>18</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>938</v>
+        <v>958</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>939</v>
+        <v>959</v>
       </c>
       <c r="F61" s="12">
         <v>7</v>
@@ -15815,13 +16025,13 @@
         <v>18</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>940</v>
+        <v>960</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="F62" s="12">
         <v>7</v>
@@ -15836,13 +16046,13 @@
         <v>1350</v>
       </c>
       <c r="J62" s="11" t="s">
-        <v>943</v>
+        <v>963</v>
       </c>
       <c r="K62" s="11" t="s">
         <v>24</v>
       </c>
       <c r="L62" s="11" t="s">
-        <v>944</v>
+        <v>964</v>
       </c>
       <c r="M62" s="11" t="s">
         <v>264</v>
@@ -15858,6 +16068,1024 @@
       </c>
       <c r="Q62" s="11">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+  <dimension ref="A1:P28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="85.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1760</v>
+      </c>
+      <c r="H3" s="3">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I27" si="0">G3-H3</f>
+        <v>1730</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>971</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>972</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1020</v>
+      </c>
+      <c r="H4" s="8">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>974</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="3">
+        <v>920</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>977</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="6">
+        <v>975</v>
+      </c>
+      <c r="H6" s="6">
+        <v>25</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>979</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>980</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>981</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G8" s="3">
+        <v>910</v>
+      </c>
+      <c r="H8" s="3">
+        <v>20</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>983</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>984</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="8">
+        <v>0</v>
+      </c>
+      <c r="H9" s="8">
+        <v>25</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>985</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="8">
+        <v>400</v>
+      </c>
+      <c r="H10" s="8">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>986</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="6">
+        <v>2070</v>
+      </c>
+      <c r="H11" s="6">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="0"/>
+        <v>2045</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>969</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>757</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>987</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>988</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="3">
+        <v>920</v>
+      </c>
+      <c r="H13" s="3">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>989</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>990</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="8">
+        <v>920</v>
+      </c>
+      <c r="H14" s="8">
+        <v>30</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>677</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F15" s="7">
+        <v>10</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>991</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>992</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="8">
+        <v>920</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>993</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>994</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>995</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="8">
+        <v>980</v>
+      </c>
+      <c r="H17" s="8">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>996</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>997</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="3">
+        <v>865</v>
+      </c>
+      <c r="H18" s="3">
+        <v>25</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>999</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G19" s="5">
+        <v>820</v>
+      </c>
+      <c r="H19" s="5">
+        <v>30</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J19" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>567</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>1000</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="8">
+        <v>900</v>
+      </c>
+      <c r="H20" s="8">
+        <v>30</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1145</v>
+      </c>
+      <c r="H21" s="6">
+        <v>25</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="8">
+        <v>670</v>
+      </c>
+      <c r="H22" s="8">
+        <v>30</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G23" s="6">
+        <v>845</v>
+      </c>
+      <c r="H23" s="6">
+        <v>25</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="8">
+        <v>920</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>40</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>1013</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0</v>
+      </c>
+      <c r="H26" s="6">
+        <v>30</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
+        <v>30</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="8">
+        <v>915</v>
+      </c>
+      <c r="H28" s="8">
+        <v>25</v>
+      </c>
+      <c r="I28" s="8">
+        <v>890</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>973</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>804</v>
       </c>
     </row>
   </sheetData>

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5ED4305-8A78-4E1A-A2DB-6B96350A2AF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292F7A71-2A46-4A72-A053-920634975D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -22,6 +22,7 @@
     <sheet name="09-05" sheetId="11" r:id="rId7"/>
     <sheet name="11-05" sheetId="12" r:id="rId8"/>
     <sheet name="12-05" sheetId="13" r:id="rId9"/>
+    <sheet name="13-05" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3019" uniqueCount="1034">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="1121">
   <si>
     <t>THU 6</t>
   </si>
@@ -2977,21 +2978,33 @@
     <t>5/1H đường số 11 Bình Thọ</t>
   </si>
   <si>
+    <t>Nguyễn My</t>
+  </si>
+  <si>
     <t>HD020162</t>
   </si>
   <si>
+    <t>Tk18/3 nguyễn cảnh chân p cầu kho</t>
+  </si>
+  <si>
     <t>Bella</t>
   </si>
   <si>
     <t>HD020155</t>
   </si>
   <si>
+    <t>209/8 nguyễn duy cung, P12</t>
+  </si>
+  <si>
     <t>Lọ Lem</t>
   </si>
   <si>
     <t>HD020148</t>
   </si>
   <si>
+    <t>484B no trang long p13</t>
+  </si>
+  <si>
     <t>Bella Tran (Lê Huy)</t>
   </si>
   <si>
@@ -3004,27 +3017,60 @@
     <t>Phạm Oanh</t>
   </si>
   <si>
+    <t>HD020045</t>
+  </si>
+  <si>
+    <t>Cty Eidaikake xưởng 2. đường số 8 phường tân thuận đông đường huỳnh tấn phát kcxtt</t>
+  </si>
+  <si>
+    <t>Chị Quyên fb An Nhiên</t>
+  </si>
+  <si>
+    <t>HD020066</t>
+  </si>
+  <si>
     <t>510 Ngô Gia Tự, P.An Đông</t>
   </si>
   <si>
     <t>HD020192</t>
   </si>
   <si>
+    <t>#301 Pham Ngu Lao Street</t>
+  </si>
+  <si>
     <t>Hải Anh</t>
   </si>
   <si>
+    <t>HDO1778410597940_472532</t>
+  </si>
+  <si>
+    <t>L-1506, chung cư One Verandah, số 2 Bát Nàn p. Thạnh Mỹ Lợi</t>
+  </si>
+  <si>
     <t>Trần Thị Kim Phương</t>
   </si>
   <si>
     <t>HD020054</t>
   </si>
   <si>
+    <t>1870\1\98\14a tỉnh lộ 10 tân tạo bình tân</t>
+  </si>
+  <si>
+    <t>HD020091</t>
+  </si>
+  <si>
+    <t>594/7 điện biên phủ p10</t>
+  </si>
+  <si>
     <t>Hoàng Thị Hồng</t>
   </si>
   <si>
     <t>HD020036</t>
   </si>
   <si>
+    <t>Eco green tòa E nguyễn văn linh tân thuận tây</t>
+  </si>
+  <si>
     <t>Trinh Kim</t>
   </si>
   <si>
@@ -3040,15 +3086,24 @@
     <t>HD020081</t>
   </si>
   <si>
+    <t>652/7A Cộng Hoà - P13</t>
+  </si>
+  <si>
     <t>Thiên Nga</t>
   </si>
   <si>
     <t>HD020151</t>
   </si>
   <si>
+    <t>S5.02 Vinhomes grand park, Nguyễn Xiển, Long Mỹ</t>
+  </si>
+  <si>
     <t>HD020221</t>
   </si>
   <si>
+    <t>90a /10/10 Âu duong lân p3</t>
+  </si>
+  <si>
     <t>Tram Hoang Ngoc</t>
   </si>
   <si>
@@ -3085,67 +3140,274 @@
     <t>137/2 bình long</t>
   </si>
   <si>
+    <t>HẠNH NARIN</t>
+  </si>
+  <si>
     <t>Em Na</t>
   </si>
   <si>
-    <t>L-1506, chung cư One Verandah, số 2 Bát Nàn p. Thạnh Mỹ Lợi</t>
-  </si>
-  <si>
-    <t>HDO1778410597940_472532</t>
-  </si>
-  <si>
-    <t>652/7A Cộng Hoà - P13</t>
-  </si>
-  <si>
-    <t>209/8 nguyễn duy cung, P12</t>
-  </si>
-  <si>
-    <t>HẠNH NARIN</t>
-  </si>
-  <si>
-    <t>484B no trang long p13</t>
-  </si>
-  <si>
-    <t>#301 Pham Ngu Lao Street</t>
-  </si>
-  <si>
-    <t>Chị Quyên fb An Nhiên</t>
-  </si>
-  <si>
-    <t>HD020066</t>
-  </si>
-  <si>
-    <t>HD020091</t>
-  </si>
-  <si>
-    <t>594/7 điện biên phủ p10</t>
-  </si>
-  <si>
-    <t>Nguyễn My</t>
-  </si>
-  <si>
-    <t>Tk18/3 nguyễn cảnh chân p cầu kho</t>
-  </si>
-  <si>
     <t>Xe Khải Nam</t>
   </si>
   <si>
-    <t>S5.02 Vinhomes grand park, Nguyễn Xiển, Long Mỹ</t>
-  </si>
-  <si>
-    <t>1870\1\98\14a tỉnh lộ 10 tân tạo bình tân</t>
-  </si>
-  <si>
-    <t>HD020045</t>
-  </si>
-  <si>
-    <t>Cty Eidaikake xưởng 2. đường số 8 phường tân thuận đông đường huỳnh tấn phát kcxtt</t>
-  </si>
-  <si>
-    <t>Eco green tòa E nguyễn văn linh tân thuận tây</t>
-  </si>
-  <si>
-    <t>90a /10/10 Âu duong lân p3</t>
+    <t>NGAY 13-5</t>
+  </si>
+  <si>
+    <t>huỳnh như</t>
+  </si>
+  <si>
+    <t>HD020300</t>
+  </si>
+  <si>
+    <t>387/12 phan văn trị chợ quán</t>
+  </si>
+  <si>
+    <t>13-05-2026</t>
+  </si>
+  <si>
+    <t>Sun Na</t>
+  </si>
+  <si>
+    <t>HD020281</t>
+  </si>
+  <si>
+    <t>Chung cư cardinal court toà B</t>
+  </si>
+  <si>
+    <t>AT 13-05</t>
+  </si>
+  <si>
+    <t>HD020452</t>
+  </si>
+  <si>
+    <t>965/14c quang Trung, P.14</t>
+  </si>
+  <si>
+    <t>Nho Nhỏ</t>
+  </si>
+  <si>
+    <t>HD020360</t>
+  </si>
+  <si>
+    <t>HD020279</t>
+  </si>
+  <si>
+    <t>654/6 lạc long quân p9</t>
+  </si>
+  <si>
+    <t>Đoan Trang</t>
+  </si>
+  <si>
+    <t>HD020499</t>
+  </si>
+  <si>
+    <t>Linh Đan</t>
+  </si>
+  <si>
+    <t>HD020536</t>
+  </si>
+  <si>
+    <t>Saigon Royal; Tháp AP1, 34-35 Bến Vân Đồn, P. 12</t>
+  </si>
+  <si>
+    <t>Thanh Phương</t>
+  </si>
+  <si>
+    <t>Kim Nhân</t>
+  </si>
+  <si>
+    <t>Mie Mie</t>
+  </si>
+  <si>
+    <t>HD020255</t>
+  </si>
+  <si>
+    <t>HD020451</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Thoa</t>
+  </si>
+  <si>
+    <t>HD020457</t>
+  </si>
+  <si>
+    <t>số 25a đường 22 tình hưng hòa a</t>
+  </si>
+  <si>
+    <t>Bé Ty - fb Anh Lan</t>
+  </si>
+  <si>
+    <t>HD020293</t>
+  </si>
+  <si>
+    <t>Tâm Vũ</t>
+  </si>
+  <si>
+    <t>FB NGUYỄN THỊ TRÚC NGÂN</t>
+  </si>
+  <si>
+    <t>HD020315</t>
+  </si>
+  <si>
+    <t>suz, fb Bei Bei</t>
+  </si>
+  <si>
+    <t>HD020496</t>
+  </si>
+  <si>
+    <t>HD020453</t>
+  </si>
+  <si>
+    <t>Heng Roza (EV35382)</t>
+  </si>
+  <si>
+    <t>HD019725</t>
+  </si>
+  <si>
+    <t>Kim Tuyến</t>
+  </si>
+  <si>
+    <t>HD012977</t>
+  </si>
+  <si>
+    <t>HD020460</t>
+  </si>
+  <si>
+    <t>Nytha</t>
+  </si>
+  <si>
+    <t>HD020287</t>
+  </si>
+  <si>
+    <t>392/2 ung văn khiêm p25</t>
+  </si>
+  <si>
+    <t>Hồng Phấn</t>
+  </si>
+  <si>
+    <t>HD020494</t>
+  </si>
+  <si>
+    <t>Ship Sảnh RS4 chung cư richstar 278 hoà bình, p.phú thạnh</t>
+  </si>
+  <si>
+    <t>HD020509</t>
+  </si>
+  <si>
+    <t>số 25a đường 22 bình hưng hòa a</t>
+  </si>
+  <si>
+    <t>lindsiepham</t>
+  </si>
+  <si>
+    <t>HD020177</t>
+  </si>
+  <si>
+    <t>landmark 5b vinhomes central park</t>
+  </si>
+  <si>
+    <t>HD020295</t>
+  </si>
+  <si>
+    <t>HD020486</t>
+  </si>
+  <si>
+    <t>Mai Mai</t>
+  </si>
+  <si>
+    <t>HD020230</t>
+  </si>
+  <si>
+    <t>21b lý van phức tân định</t>
+  </si>
+  <si>
+    <t>36 Lê Lai phường bảy Hiền</t>
+  </si>
+  <si>
+    <t>HD020444</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building S6 G26, đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>Thanh Hương-Hương Missi</t>
+  </si>
+  <si>
+    <t>215 Nam Kì Khởi Nghĩa Phường Võ Thị Sáu</t>
+  </si>
+  <si>
+    <t>718/3/12 trần hưng đạo p2</t>
+  </si>
+  <si>
+    <t>HD020337</t>
+  </si>
+  <si>
+    <t>256- 258 Lý thường kiết p14 (chung cư xi grand) Lock A2</t>
+  </si>
+  <si>
+    <t>nguyễn minh hải</t>
+  </si>
+  <si>
+    <t>No. 17, Street No. 13, Binh Hung Hoa Ward</t>
+  </si>
+  <si>
+    <t>gộp, shop chịu ship</t>
+  </si>
+  <si>
+    <t>HD020448</t>
+  </si>
+  <si>
+    <t>5M1/10 An Hạ</t>
+  </si>
+  <si>
+    <t>532/3/6 Kinh Dương Vương, Phường An Lạc</t>
+  </si>
+  <si>
+    <t>Số 78 Đường Số 7, P. Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>Đoàn Kim</t>
+  </si>
+  <si>
+    <t>HD020450</t>
+  </si>
+  <si>
+    <t>Block D, chung cư floria đường số 1, tân hưng</t>
+  </si>
+  <si>
+    <t>tran Bảo Châu</t>
+  </si>
+  <si>
+    <t>38 đường số 3, phường Tân Phú</t>
+  </si>
+  <si>
+    <t>Roxy Nguyen</t>
+  </si>
+  <si>
+    <t>Số 35 đường 34 phường linh đông</t>
+  </si>
+  <si>
+    <t>Chung cư CitiEsto, Đ. 33-CL, Cát Lái, B02-07, Phường Cát Lái</t>
+  </si>
+  <si>
+    <t>HD020429</t>
+  </si>
+  <si>
+    <t>100/40/56 lê văn duyệt, phường gia định (p1 cũ)</t>
+  </si>
+  <si>
+    <t>(phan pham ngô nhi)</t>
+  </si>
+  <si>
+    <t>403 đường tân sơn - phường an hội tây</t>
+  </si>
+  <si>
+    <t>HD020393</t>
+  </si>
+  <si>
+    <t>zalo tuyền hoàng</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường Gò Vấp (phường 17 CŨ)</t>
   </si>
 </sst>
 </file>
@@ -5551,6 +5813,1214 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:P33"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="6">
+        <v>815</v>
+      </c>
+      <c r="H3" s="6">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <v>790</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="8">
+        <v>980</v>
+      </c>
+      <c r="H4" s="8">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3">
+        <v>875</v>
+      </c>
+      <c r="H5" s="3">
+        <v>25</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="8">
+        <v>845</v>
+      </c>
+      <c r="H7" s="8">
+        <v>25</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3">
+        <v>920</v>
+      </c>
+      <c r="H8" s="3">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1051</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="6">
+        <v>765</v>
+      </c>
+      <c r="H9" s="6">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="6">
+        <v>25</v>
+      </c>
+      <c r="H10" s="6">
+        <v>25</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="8">
+        <v>35</v>
+      </c>
+      <c r="H11" s="8">
+        <v>35</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="8">
+        <v>900</v>
+      </c>
+      <c r="H12" s="8">
+        <v>30</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="3">
+        <v>870</v>
+      </c>
+      <c r="H13" s="3">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>1061</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1570</v>
+      </c>
+      <c r="H14" s="8">
+        <v>35</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>1535</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1063</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="8">
+        <v>3930</v>
+      </c>
+      <c r="H15" s="8">
+        <v>40</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>3890</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="3">
+        <v>20</v>
+      </c>
+      <c r="H16" s="3">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G18" s="6">
+        <v>725</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>1095</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="6">
+        <v>765</v>
+      </c>
+      <c r="H19" s="6">
+        <v>25</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1117</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>25</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>30</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>1096</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1115</v>
+      </c>
+      <c r="H22" s="6">
+        <v>25</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>1118</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="3">
+        <v>875</v>
+      </c>
+      <c r="H23" s="3">
+        <v>25</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>1074</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G24" s="8">
+        <v>880</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>20</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="8">
+        <v>875</v>
+      </c>
+      <c r="H26" s="8">
+        <v>25</v>
+      </c>
+      <c r="I26" s="8">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>30</v>
+      </c>
+      <c r="I27" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1059</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>1081</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="8">
+        <v>780</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="3">
+        <v>840</v>
+      </c>
+      <c r="H29" s="3">
+        <v>20</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>1086</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="6">
+        <v>815</v>
+      </c>
+      <c r="H30" s="6">
+        <v>25</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>1087</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G31" s="6">
+        <v>45</v>
+      </c>
+      <c r="H31" s="6">
+        <v>25</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>1088</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" s="6">
+        <v>765</v>
+      </c>
+      <c r="H32" s="6">
+        <v>25</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>1099</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>1100</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="8">
+        <v>50</v>
+      </c>
+      <c r="H33" s="8">
+        <v>50</v>
+      </c>
+      <c r="I33" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{287A4485-5F29-4948-B3C6-C79991D725F4}">
   <dimension ref="A1:Q26"/>
@@ -16080,10 +17550,12 @@
   <dimension ref="A1:P28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="85.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -16263,13 +17735,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1025</v>
+        <v>977</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>1026</v>
+        <v>979</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>63</v>
@@ -16299,13 +17771,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>1017</v>
+        <v>982</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>70</v>
@@ -16335,13 +17807,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>980</v>
+        <v>983</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>1019</v>
+        <v>985</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>81</v>
@@ -16371,13 +17843,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>85</v>
@@ -16407,13 +17879,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1030</v>
+        <v>990</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1031</v>
+        <v>991</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>131</v>
@@ -16443,13 +17915,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1021</v>
+        <v>992</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1022</v>
+        <v>993</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>59</v>
@@ -16485,10 +17957,10 @@
         <v>757</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1020</v>
+        <v>996</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>63</v>
@@ -16518,13 +17990,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>988</v>
+        <v>997</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1015</v>
+        <v>998</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1014</v>
+        <v>999</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>48</v>
@@ -16554,13 +18026,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>1029</v>
+        <v>1002</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>22</v>
@@ -16593,10 +18065,10 @@
         <v>677</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1023</v>
+        <v>1003</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1024</v>
+        <v>1004</v>
       </c>
       <c r="F15" s="7">
         <v>10</v>
@@ -16626,13 +18098,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>991</v>
+        <v>1005</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>992</v>
+        <v>1006</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>1032</v>
+        <v>1007</v>
       </c>
       <c r="F16" s="8" t="s">
         <v>131</v>
@@ -16662,13 +18134,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>993</v>
+        <v>1008</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>994</v>
+        <v>1009</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="F17" s="8" t="s">
         <v>41</v>
@@ -16698,13 +18170,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>996</v>
+        <v>1011</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>997</v>
+        <v>1012</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>102</v>
@@ -16734,13 +18206,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>998</v>
+        <v>1014</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>999</v>
+        <v>1015</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>1028</v>
+        <v>1016</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>149</v>
@@ -16773,10 +18245,10 @@
         <v>567</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1000</v>
+        <v>1017</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="F20" s="8" t="s">
         <v>41</v>
@@ -16806,13 +18278,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1001</v>
+        <v>1019</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1002</v>
+        <v>1020</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1003</v>
+        <v>1021</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>308</v>
@@ -16842,13 +18314,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1004</v>
+        <v>1022</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1005</v>
+        <v>1023</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1006</v>
+        <v>1024</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>22</v>
@@ -16878,13 +18350,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1007</v>
+        <v>1025</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1008</v>
+        <v>1026</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>1009</v>
+        <v>1027</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>186</v>
@@ -16914,13 +18386,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1010</v>
+        <v>1028</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1011</v>
+        <v>1029</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>1012</v>
+        <v>1030</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>22</v>
@@ -16953,7 +18425,7 @@
         <v>18</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>1018</v>
+        <v>1031</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>511</v>
@@ -16989,10 +18461,10 @@
         <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1013</v>
+        <v>1032</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>1027</v>
+        <v>1033</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>59</v>

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{292F7A71-2A46-4A72-A053-920634975D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8499EE5E-5161-4C66-88F9-A2696A91346E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -23,6 +23,9 @@
     <sheet name="11-05" sheetId="12" r:id="rId8"/>
     <sheet name="12-05" sheetId="13" r:id="rId9"/>
     <sheet name="13-05" sheetId="14" r:id="rId10"/>
+    <sheet name="14-05" sheetId="15" r:id="rId11"/>
+    <sheet name="15-05" sheetId="16" r:id="rId12"/>
+    <sheet name="16-05" sheetId="17" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3289" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4223" uniqueCount="1403">
   <si>
     <t>THU 6</t>
   </si>
@@ -3176,6 +3179,9 @@
     <t>AT 13-05</t>
   </si>
   <si>
+    <t>Roxy Nguyen</t>
+  </si>
+  <si>
     <t>HD020452</t>
   </si>
   <si>
@@ -3188,6 +3194,12 @@
     <t>HD020360</t>
   </si>
   <si>
+    <t>Số 35 đường 34 phường linh đông</t>
+  </si>
+  <si>
+    <t>tran Bảo Châu</t>
+  </si>
+  <si>
     <t>HD020279</t>
   </si>
   <si>
@@ -3200,6 +3212,9 @@
     <t>HD020499</t>
   </si>
   <si>
+    <t>Chung cư CitiEsto, Đ. 33-CL, Cát Lái, B02-07, Phường Cát Lái</t>
+  </si>
+  <si>
     <t>Linh Đan</t>
   </si>
   <si>
@@ -3212,15 +3227,30 @@
     <t>Thanh Phương</t>
   </si>
   <si>
+    <t>HD020444</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building S6 G26, đường C22, Phường 12</t>
+  </si>
+  <si>
     <t>Kim Nhân</t>
   </si>
   <si>
+    <t>HD020448</t>
+  </si>
+  <si>
+    <t>5M1/10 An Hạ</t>
+  </si>
+  <si>
     <t>Mie Mie</t>
   </si>
   <si>
     <t>HD020255</t>
   </si>
   <si>
+    <t>38 đường số 3, phường Tân Phú</t>
+  </si>
+  <si>
     <t>HD020451</t>
   </si>
   <si>
@@ -3233,30 +3263,63 @@
     <t>số 25a đường 22 tình hưng hòa a</t>
   </si>
   <si>
+    <t>gộp, shop chịu ship</t>
+  </si>
+  <si>
     <t>Bé Ty - fb Anh Lan</t>
   </si>
   <si>
     <t>HD020293</t>
   </si>
   <si>
+    <t>532/3/6 Kinh Dương Vương, Phường An Lạc</t>
+  </si>
+  <si>
     <t>Tâm Vũ</t>
   </si>
   <si>
+    <t>HD020429</t>
+  </si>
+  <si>
+    <t>100/40/56 lê văn duyệt, phường gia định (p1 cũ)</t>
+  </si>
+  <si>
     <t>FB NGUYỄN THỊ TRÚC NGÂN</t>
   </si>
   <si>
     <t>HD020315</t>
   </si>
   <si>
+    <t>Số 78 Đường Số 7, P. Bình Hưng Hòa</t>
+  </si>
+  <si>
     <t>suz, fb Bei Bei</t>
   </si>
   <si>
+    <t>HD020337</t>
+  </si>
+  <si>
+    <t>256- 258 Lý thường kiết p14 (chung cư xi grand) Lock A2</t>
+  </si>
+  <si>
+    <t>Thanh Hương-Hương Missi</t>
+  </si>
+  <si>
     <t>HD020496</t>
   </si>
   <si>
+    <t>215 Nam Kì Khởi Nghĩa Phường Võ Thị Sáu</t>
+  </si>
+  <si>
+    <t>(phan pham ngô nhi)</t>
+  </si>
+  <si>
     <t>HD020453</t>
   </si>
   <si>
+    <t>403 đường tân sơn - phường an hội tây</t>
+  </si>
+  <si>
     <t>Heng Roza (EV35382)</t>
   </si>
   <si>
@@ -3269,6 +3332,18 @@
     <t>HD012977</t>
   </si>
   <si>
+    <t>718/3/12 trần hưng đạo p2</t>
+  </si>
+  <si>
+    <t>zalo tuyền hoàng</t>
+  </si>
+  <si>
+    <t>HD020393</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường Gò Vấp (phường 17 CŨ)</t>
+  </si>
+  <si>
     <t>HD020460</t>
   </si>
   <si>
@@ -3290,6 +3365,15 @@
     <t>Ship Sảnh RS4 chung cư richstar 278 hoà bình, p.phú thạnh</t>
   </si>
   <si>
+    <t>Đoàn Kim</t>
+  </si>
+  <si>
+    <t>HD020450</t>
+  </si>
+  <si>
+    <t>Block D, chung cư floria đường số 1, tân hưng</t>
+  </si>
+  <si>
     <t>HD020509</t>
   </si>
   <si>
@@ -3308,6 +3392,9 @@
     <t>HD020295</t>
   </si>
   <si>
+    <t>36 Lê Lai phường bảy Hiền</t>
+  </si>
+  <si>
     <t>HD020486</t>
   </si>
   <si>
@@ -3320,94 +3407,856 @@
     <t>21b lý van phức tân định</t>
   </si>
   <si>
-    <t>36 Lê Lai phường bảy Hiền</t>
-  </si>
-  <si>
-    <t>HD020444</t>
-  </si>
-  <si>
-    <t>Tòa nhà C22 Building S6 G26, đường C22, Phường 12</t>
-  </si>
-  <si>
-    <t>Thanh Hương-Hương Missi</t>
-  </si>
-  <si>
-    <t>215 Nam Kì Khởi Nghĩa Phường Võ Thị Sáu</t>
-  </si>
-  <si>
-    <t>718/3/12 trần hưng đạo p2</t>
-  </si>
-  <si>
-    <t>HD020337</t>
-  </si>
-  <si>
-    <t>256- 258 Lý thường kiết p14 (chung cư xi grand) Lock A2</t>
-  </si>
-  <si>
     <t>nguyễn minh hải</t>
   </si>
   <si>
     <t>No. 17, Street No. 13, Binh Hung Hoa Ward</t>
   </si>
   <si>
-    <t>gộp, shop chịu ship</t>
-  </si>
-  <si>
-    <t>HD020448</t>
-  </si>
-  <si>
-    <t>5M1/10 An Hạ</t>
-  </si>
-  <si>
-    <t>532/3/6 Kinh Dương Vương, Phường An Lạc</t>
-  </si>
-  <si>
-    <t>Số 78 Đường Số 7, P. Bình Hưng Hòa</t>
-  </si>
-  <si>
-    <t>Đoàn Kim</t>
-  </si>
-  <si>
-    <t>HD020450</t>
-  </si>
-  <si>
-    <t>Block D, chung cư floria đường số 1, tân hưng</t>
-  </si>
-  <si>
-    <t>tran Bảo Châu</t>
-  </si>
-  <si>
-    <t>38 đường số 3, phường Tân Phú</t>
-  </si>
-  <si>
-    <t>Roxy Nguyen</t>
-  </si>
-  <si>
-    <t>Số 35 đường 34 phường linh đông</t>
-  </si>
-  <si>
-    <t>Chung cư CitiEsto, Đ. 33-CL, Cát Lái, B02-07, Phường Cát Lái</t>
-  </si>
-  <si>
-    <t>HD020429</t>
-  </si>
-  <si>
-    <t>100/40/56 lê văn duyệt, phường gia định (p1 cũ)</t>
-  </si>
-  <si>
-    <t>(phan pham ngô nhi)</t>
-  </si>
-  <si>
-    <t>403 đường tân sơn - phường an hội tây</t>
-  </si>
-  <si>
-    <t>HD020393</t>
-  </si>
-  <si>
-    <t>zalo tuyền hoàng</t>
-  </si>
-  <si>
-    <t>433/11/2 Lê Đức Thọ, Phường Gò Vấp (phường 17 CŨ)</t>
+    <t>NGAY 14-5</t>
+  </si>
+  <si>
+    <t>Bookzan</t>
+  </si>
+  <si>
+    <t>137 phan huy ich p15</t>
+  </si>
+  <si>
+    <t>14-05-2026</t>
+  </si>
+  <si>
+    <t>LYKA</t>
+  </si>
+  <si>
+    <t>Gửi qua xe Khải Nam 363 Đường Hùng vương P. 9</t>
+  </si>
+  <si>
+    <t>tân sơn phường 12</t>
+  </si>
+  <si>
+    <t>LDVKH</t>
+  </si>
+  <si>
+    <t>HD020852</t>
+  </si>
+  <si>
+    <t>(LDVKH1211714)177C ( Đối diện 93C) Đường Số 1, Phường Hưng Hoà B</t>
+  </si>
+  <si>
+    <t>AT 14-05</t>
+  </si>
+  <si>
+    <t>Anh Thư</t>
+  </si>
+  <si>
+    <t>HD020661</t>
+  </si>
+  <si>
+    <t>số 69 trần quốc tuấn hạnh thông</t>
+  </si>
+  <si>
+    <t>HD020802</t>
+  </si>
+  <si>
+    <t>Lê Ngọc Nhân</t>
+  </si>
+  <si>
+    <t>HD20811</t>
+  </si>
+  <si>
+    <t>192 Phạm đức Sơn, P. Phú Định</t>
+  </si>
+  <si>
+    <t>Kim Hân</t>
+  </si>
+  <si>
+    <t>HD020598</t>
+  </si>
+  <si>
+    <t>302 Nguyễn chí thanh p5</t>
+  </si>
+  <si>
+    <t>kim nhung châu</t>
+  </si>
+  <si>
+    <t>HD020804</t>
+  </si>
+  <si>
+    <t>phòng 14.07 chung cư riva park số 504 nguyễn tất thành phường xóm chiếu</t>
+  </si>
+  <si>
+    <t>My My</t>
+  </si>
+  <si>
+    <t>HD020534</t>
+  </si>
+  <si>
+    <t>114 vỏ liêm Sơn, phường Chánh hưng</t>
+  </si>
+  <si>
+    <t>Bé Sarah</t>
+  </si>
+  <si>
+    <t>HD020613</t>
+  </si>
+  <si>
+    <t>Vinhome grand park toà gh2</t>
+  </si>
+  <si>
+    <t>cát giang</t>
+  </si>
+  <si>
+    <t>HD020867</t>
+  </si>
+  <si>
+    <t>1 ấp bắc</t>
+  </si>
+  <si>
+    <t>Khánh</t>
+  </si>
+  <si>
+    <t>HD020813</t>
+  </si>
+  <si>
+    <t>11 tam bình khu phố 7, phường hiệp bình</t>
+  </si>
+  <si>
+    <t>Thùy An</t>
+  </si>
+  <si>
+    <t>HD020806</t>
+  </si>
+  <si>
+    <t>57/16 Phùng Chí Kiên</t>
+  </si>
+  <si>
+    <t>Ngan Tran</t>
+  </si>
+  <si>
+    <t>HD020814</t>
+  </si>
+  <si>
+    <t>11/39, Nguyễn Văn Mại, Phường Tân Sơn Nhất</t>
+  </si>
+  <si>
+    <t>Linh Anh</t>
+  </si>
+  <si>
+    <t>HD020801</t>
+  </si>
+  <si>
+    <t>208 nguyễn hữu cảnh phường 22</t>
+  </si>
+  <si>
+    <t>MeyMey EV28641</t>
+  </si>
+  <si>
+    <t>HD020601</t>
+  </si>
+  <si>
+    <t>315/18/6 Nguyễn Thị Tú Bình Hưng Hòa B</t>
+  </si>
+  <si>
+    <t>Cherry Nguyễn</t>
+  </si>
+  <si>
+    <t>HD020793</t>
+  </si>
+  <si>
+    <t>66 hùng vương p1</t>
+  </si>
+  <si>
+    <t>thanh nhàn - fb Lam Ng</t>
+  </si>
+  <si>
+    <t>HD020612</t>
+  </si>
+  <si>
+    <t>156a Tân quý phường Phú thọ hòa</t>
+  </si>
+  <si>
+    <t>VTS-34309SAK</t>
+  </si>
+  <si>
+    <t>HD020558</t>
+  </si>
+  <si>
+    <t>VTS-34309SAK, 601 QL1A, An Lạc</t>
+  </si>
+  <si>
+    <t>Trâm</t>
+  </si>
+  <si>
+    <t>HD020800</t>
+  </si>
+  <si>
+    <t>132 bến vân đồn p9</t>
+  </si>
+  <si>
+    <t>___det___ insta</t>
+  </si>
+  <si>
+    <t>HD020529</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương,p9</t>
+  </si>
+  <si>
+    <t>Mỹ Linh</t>
+  </si>
+  <si>
+    <t>HD020896</t>
+  </si>
+  <si>
+    <t>117/4b/15 hồ văn long, tân tạo, gần cây xăng đức lợi phát</t>
+  </si>
+  <si>
+    <t>Hiếu Lee</t>
+  </si>
+  <si>
+    <t>HD020637</t>
+  </si>
+  <si>
+    <t>Chung cu folita him lam</t>
+  </si>
+  <si>
+    <t>Nguyên Hà</t>
+  </si>
+  <si>
+    <t>HD020597</t>
+  </si>
+  <si>
+    <t>007 lô B chung cư Tây Thạnh, phườn Tân Thạnh</t>
+  </si>
+  <si>
+    <t>HD020687</t>
+  </si>
+  <si>
+    <t>HD020757</t>
+  </si>
+  <si>
+    <t>324/11 lý thường kiệt</t>
+  </si>
+  <si>
+    <t>HD020548</t>
+  </si>
+  <si>
+    <t>Tòa landmark 2</t>
+  </si>
+  <si>
+    <t>HD020885</t>
+  </si>
+  <si>
+    <t>Linh Huệ</t>
+  </si>
+  <si>
+    <t>HD020761</t>
+  </si>
+  <si>
+    <t>12 tôn đản</t>
+  </si>
+  <si>
+    <t>Kami - fb Đan Khanh</t>
+  </si>
+  <si>
+    <t>HD020872</t>
+  </si>
+  <si>
+    <t>Chung cư DELASOL, căn A2.09.04, số 1 Tôn Thất Thuyết, P1</t>
+  </si>
+  <si>
+    <t>Thảo Ngân Lê</t>
+  </si>
+  <si>
+    <t>HD020823</t>
+  </si>
+  <si>
+    <t>1264/19/8 lê đức thọ, p13</t>
+  </si>
+  <si>
+    <t>Thư Thỏ</t>
+  </si>
+  <si>
+    <t>HD020632</t>
+  </si>
+  <si>
+    <t>13 phạm thế hiển phường chánh hưng</t>
+  </si>
+  <si>
+    <t>Uyen Cam Cao</t>
+  </si>
+  <si>
+    <t>HD020895</t>
+  </si>
+  <si>
+    <t>182/8 đường số 6, bình hưng hoà b</t>
+  </si>
+  <si>
+    <t>Elly Nguyễn</t>
+  </si>
+  <si>
+    <t>HD020858</t>
+  </si>
+  <si>
+    <t>431/7b đường Phan Văn Trị phường 7</t>
+  </si>
+  <si>
+    <t>THẢO PHẠM</t>
+  </si>
+  <si>
+    <t>NHÀ XE MINH QUỐC</t>
+  </si>
+  <si>
+    <t>NGAY 15-5</t>
+  </si>
+  <si>
+    <t>Kiên Hoàng Khiêm</t>
+  </si>
+  <si>
+    <t>HD020881</t>
+  </si>
+  <si>
+    <t>531 Điện Biên Phủ P. Bàn Cờ</t>
+  </si>
+  <si>
+    <t>AT 15-05</t>
+  </si>
+  <si>
+    <t>15-05-2026</t>
+  </si>
+  <si>
+    <t>Nguyễn Hoài An</t>
+  </si>
+  <si>
+    <t>HD020928</t>
+  </si>
+  <si>
+    <t>15 đặng thai mai p7</t>
+  </si>
+  <si>
+    <t>Hồ Nguyễn Quỳnh Như</t>
+  </si>
+  <si>
+    <t>HD020995</t>
+  </si>
+  <si>
+    <t>Central premium lock A 0946374247</t>
+  </si>
+  <si>
+    <t>Trang Nguyên</t>
+  </si>
+  <si>
+    <t>HD021087</t>
+  </si>
+  <si>
+    <t>13c lê thánh tôn</t>
+  </si>
+  <si>
+    <t>W24130 MiKi</t>
+  </si>
+  <si>
+    <t>HD021125</t>
+  </si>
+  <si>
+    <t>64 Lê Thị Riêng</t>
+  </si>
+  <si>
+    <t>Thanh Hà Phạm</t>
+  </si>
+  <si>
+    <t>HD020997</t>
+  </si>
+  <si>
+    <t>29/15 yên thế, p2</t>
+  </si>
+  <si>
+    <t>Binh Hương</t>
+  </si>
+  <si>
+    <t>HD020878</t>
+  </si>
+  <si>
+    <t>13 đươngg 44 phường 14</t>
+  </si>
+  <si>
+    <t>Người nhận: Vũ Hạ</t>
+  </si>
+  <si>
+    <t>HD020648</t>
+  </si>
+  <si>
+    <t>cầu thang số 2 lô F, chung cư Sơn Kỳ, đường CC5, P. Tây Thạnh</t>
+  </si>
+  <si>
+    <t>Jenny Đoàn</t>
+  </si>
+  <si>
+    <t>HD021013</t>
+  </si>
+  <si>
+    <t>lô m3 chung cư số 1 tôn thất thuyết p1</t>
+  </si>
+  <si>
+    <t>Người Nhận BN2705</t>
+  </si>
+  <si>
+    <t>HD021163</t>
+  </si>
+  <si>
+    <t>Mứt Dâu</t>
+  </si>
+  <si>
+    <t>HD018064</t>
+  </si>
+  <si>
+    <t>238/14 quốc lộ 50 phường 6</t>
+  </si>
+  <si>
+    <t>HD021101</t>
+  </si>
+  <si>
+    <t>Đăng + Hạnh</t>
+  </si>
+  <si>
+    <t>HD021152</t>
+  </si>
+  <si>
+    <t>403 Tân Sơn, P12</t>
+  </si>
+  <si>
+    <t>HD021002</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building Số G26, đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>Lê Thị Ngọc Vân</t>
+  </si>
+  <si>
+    <t>HD021150</t>
+  </si>
+  <si>
+    <t>34 phùng văn cung p7</t>
+  </si>
+  <si>
+    <t>Megan Truong</t>
+  </si>
+  <si>
+    <t>HD020862</t>
+  </si>
+  <si>
+    <t>số nhà 1527/3/1 hẻm 1545 lê văn lương, nhơn đức</t>
+  </si>
+  <si>
+    <t>HD021024</t>
+  </si>
+  <si>
+    <t>Nguyễn Thùy</t>
+  </si>
+  <si>
+    <t>HD021164</t>
+  </si>
+  <si>
+    <t>71/46 gò xoài p bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Bảo Trân</t>
+  </si>
+  <si>
+    <t>HD021085</t>
+  </si>
+  <si>
+    <t>90a đường 37 Tân Quy</t>
+  </si>
+  <si>
+    <t>Bác Thanh - fb Pé Síu</t>
+  </si>
+  <si>
+    <t>HDO21082</t>
+  </si>
+  <si>
+    <t>566/17 An Duong Vuong p11</t>
+  </si>
+  <si>
+    <t>VTS-51916TNV</t>
+  </si>
+  <si>
+    <t>HD020984</t>
+  </si>
+  <si>
+    <t>601 QL1A, An Lạc</t>
+  </si>
+  <si>
+    <t>coca ( kẹ)</t>
+  </si>
+  <si>
+    <t>HD021127</t>
+  </si>
+  <si>
+    <t>532/3/93 kinh dương vương, Phường an lạc</t>
+  </si>
+  <si>
+    <t>Huyền Trang</t>
+  </si>
+  <si>
+    <t>HD021153</t>
+  </si>
+  <si>
+    <t>108 hồng hà p2</t>
+  </si>
+  <si>
+    <t>Phương Dung</t>
+  </si>
+  <si>
+    <t>HD020877</t>
+  </si>
+  <si>
+    <t>Sunshine sky city tòa A2</t>
+  </si>
+  <si>
+    <t>Đức nhận hộ Mimi -87780266</t>
+  </si>
+  <si>
+    <t>HD020538</t>
+  </si>
+  <si>
+    <t>39 an nhơn phương 17</t>
+  </si>
+  <si>
+    <t>Bing Bing</t>
+  </si>
+  <si>
+    <t>HD021129</t>
+  </si>
+  <si>
+    <t>Landmark 5, Vinhome central park, F22</t>
+  </si>
+  <si>
+    <t>Vu Hiếu</t>
+  </si>
+  <si>
+    <t>HD021028</t>
+  </si>
+  <si>
+    <t>Số 10 đuong 18 linh đông</t>
+  </si>
+  <si>
+    <t>ĐÔNG MIÊN malay</t>
+  </si>
+  <si>
+    <t>HD021014</t>
+  </si>
+  <si>
+    <t>22 TÂN THỚI NHẤT 1B, Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Daisy</t>
+  </si>
+  <si>
+    <t>HD021054</t>
+  </si>
+  <si>
+    <t>5A Lam Sơn, Phường Tân Sơn Hòa</t>
+  </si>
+  <si>
+    <t>Phuong Ho</t>
+  </si>
+  <si>
+    <t>HD021147</t>
+  </si>
+  <si>
+    <t>576a dien bien phu phuong vuon lai</t>
+  </si>
+  <si>
+    <t>Mr Thế</t>
+  </si>
+  <si>
+    <t>27/5 Quách Văn Tuấn, F12</t>
+  </si>
+  <si>
+    <t>THƯƠNG 1994</t>
+  </si>
+  <si>
+    <t>Tòa S501, Vinhome grand park, Long Thạnh Mỹ</t>
+  </si>
+  <si>
+    <t>NGAY 16-5</t>
+  </si>
+  <si>
+    <t>Người nhận: Fb Phương Mai</t>
+  </si>
+  <si>
+    <t>HD020876</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường 17</t>
+  </si>
+  <si>
+    <t>16-05-2026</t>
+  </si>
+  <si>
+    <t>yến trinh</t>
+  </si>
+  <si>
+    <t>HD021308</t>
+  </si>
+  <si>
+    <t>321 an dương vương, an lạc, bình tân Chung cư khang điền lộck b</t>
+  </si>
+  <si>
+    <t>AT 16-05</t>
+  </si>
+  <si>
+    <t>HD021355</t>
+  </si>
+  <si>
+    <t>HD021442</t>
+  </si>
+  <si>
+    <t>Phạm T. Thảo</t>
+  </si>
+  <si>
+    <t>HD021288</t>
+  </si>
+  <si>
+    <t>VERISKA (YAYANG) - ROOM 104.</t>
+  </si>
+  <si>
+    <t>HD021409</t>
+  </si>
+  <si>
+    <t>chị Huyền</t>
+  </si>
+  <si>
+    <t>HĐ021386</t>
+  </si>
+  <si>
+    <t>Nhận hành giúp chị phương (ở Úc) fb Phương My</t>
+  </si>
+  <si>
+    <t>HD021421</t>
+  </si>
+  <si>
+    <t>hoc mon</t>
+  </si>
+  <si>
+    <t>Duyên Duyên</t>
+  </si>
+  <si>
+    <t>HD021253</t>
+  </si>
+  <si>
+    <t>Đường số 9 hẻm 58/36 linh tây</t>
+  </si>
+  <si>
+    <t>Nuong Huynh</t>
+  </si>
+  <si>
+    <t>HD021213</t>
+  </si>
+  <si>
+    <t>Trần Bảo Hân (inst tienbaohen17)</t>
+  </si>
+  <si>
+    <t>HD021310</t>
+  </si>
+  <si>
+    <t>Hiệp fb Đặng Tổ Trinh</t>
+  </si>
+  <si>
+    <t>HD021379</t>
+  </si>
+  <si>
+    <t>HD021267</t>
+  </si>
+  <si>
+    <t>HD021227</t>
+  </si>
+  <si>
+    <t>BN9663</t>
+  </si>
+  <si>
+    <t>HD021364</t>
+  </si>
+  <si>
+    <t>Đỗ T. Thu Hồng</t>
+  </si>
+  <si>
+    <t>HD021466</t>
+  </si>
+  <si>
+    <t>Lock A - eco green - nguyễn văn linh</t>
+  </si>
+  <si>
+    <t>Khả Di</t>
+  </si>
+  <si>
+    <t>HD021217</t>
+  </si>
+  <si>
+    <t>54A đường số 7, Linh Trung</t>
+  </si>
+  <si>
+    <t>Nguyễn Lê</t>
+  </si>
+  <si>
+    <t>HD021425</t>
+  </si>
+  <si>
+    <t>287/1/5 thành công, tấn thành</t>
+  </si>
+  <si>
+    <t>Ngọc Mỹ Kim</t>
+  </si>
+  <si>
+    <t>HD021327</t>
+  </si>
+  <si>
+    <t>Chung cu topaz elite drgon 2c p4 ta quang buu</t>
+  </si>
+  <si>
+    <t>Trần Bảo Hân (inst tranbaohan17)</t>
+  </si>
+  <si>
+    <t>HD021309</t>
+  </si>
+  <si>
+    <t>HD021193</t>
+  </si>
+  <si>
+    <t>Sam Sam</t>
+  </si>
+  <si>
+    <t>HD021214</t>
+  </si>
+  <si>
+    <t>172 lê thị bạch cát p11</t>
+  </si>
+  <si>
+    <t>HD021369</t>
+  </si>
+  <si>
+    <t>87/10 trần quang cơ phú thạnh</t>
+  </si>
+  <si>
+    <t>HD021282</t>
+  </si>
+  <si>
+    <t>Thien Phu Nguyen</t>
+  </si>
+  <si>
+    <t>HD021468</t>
+  </si>
+  <si>
+    <t>Ánh Hoàng</t>
+  </si>
+  <si>
+    <t>HD021275</t>
+  </si>
+  <si>
+    <t>HD021185</t>
+  </si>
+  <si>
+    <t>Mai Sương</t>
+  </si>
+  <si>
+    <t>Huỳnh Phương Mỹ Duyên</t>
+  </si>
+  <si>
+    <t>HD021212</t>
+  </si>
+  <si>
+    <t>21 bis đường số 10, phường bình an</t>
+  </si>
+  <si>
+    <t>Hồng Thắm</t>
+  </si>
+  <si>
+    <t>Heng Stella</t>
+  </si>
+  <si>
+    <t>tân sơn p12</t>
+  </si>
+  <si>
+    <t>9B nguyễn xí, phường 26</t>
+  </si>
+  <si>
+    <t>Stown Tham Lương sảnh B Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>42, đường 21,Khu dân cư bình chiểu, P tam bình (chợ đầu mối nông sản thủ đức)</t>
+  </si>
+  <si>
+    <t>67 mai chí thọ phường an phú</t>
+  </si>
+  <si>
+    <t>27 đông hưng thuận 45 tân hưng thuận</t>
+  </si>
+  <si>
+    <t>Linh Tiêu</t>
+  </si>
+  <si>
+    <t>97 Ký Con, p. Nguyễn Thái Bình</t>
+  </si>
+  <si>
+    <t>Block B - Chung cư RiverGate Residence 151-155 Bến Vân Đồn, Phường Khánh Hội</t>
+  </si>
+  <si>
+    <t>HD021271</t>
+  </si>
+  <si>
+    <t>Số 3 hoàng minh giám phường đức nhuận</t>
+  </si>
+  <si>
+    <t>HD021246</t>
+  </si>
+  <si>
+    <t>HD021469</t>
+  </si>
+  <si>
+    <t>55/3 trần đình xu, phường cầu kho</t>
+  </si>
+  <si>
+    <t>Số 207 đường Đề Thám, phường bến Thành</t>
+  </si>
+  <si>
+    <t>Saigon Europe Hotel, Số 207 đường Đề Thám, phường bến Thành</t>
+  </si>
+  <si>
+    <t>Ann Ann</t>
+  </si>
+  <si>
+    <t>Loan Trần</t>
+  </si>
+  <si>
+    <t>64/24C hoà bình phường hòa bình</t>
+  </si>
+  <si>
+    <t>Cẩm Cẩm</t>
+  </si>
+  <si>
+    <t>150 Hoàng Trọng Mậu Tân Hưng</t>
+  </si>
+  <si>
+    <t>Sunrise city view tòa B .33 Nguyễn Hữu Thọ phường tân hưng</t>
+  </si>
+  <si>
+    <t>126/5h song hành, tân hiệp</t>
+  </si>
+  <si>
+    <t>63 dương bá trạc p. rạch ông</t>
+  </si>
+  <si>
+    <t>287/1/5 thành công, tân thành</t>
+  </si>
+  <si>
+    <t>kh ck shop 4210k</t>
+  </si>
+  <si>
+    <t>E4/25a đường Nguyễn Hữu Trí, khu phố 12, thị trấn Tân Túc</t>
+  </si>
+  <si>
+    <t>kh ck shop 1820k</t>
   </si>
 </sst>
 </file>
@@ -5818,9 +6667,3873 @@
   <dimension ref="A1:P33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1035</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1036</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="6">
+        <v>815</v>
+      </c>
+      <c r="H3" s="6">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <v>790</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1039</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="8">
+        <v>980</v>
+      </c>
+      <c r="H4" s="8">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3">
+        <v>875</v>
+      </c>
+      <c r="H5" s="3">
+        <v>25</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1046</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="8">
+        <v>845</v>
+      </c>
+      <c r="H7" s="8">
+        <v>25</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" s="3">
+        <v>920</v>
+      </c>
+      <c r="H8" s="3">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="6">
+        <v>765</v>
+      </c>
+      <c r="H9" s="6">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>1059</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="6">
+        <v>25</v>
+      </c>
+      <c r="H10" s="6">
+        <v>25</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1061</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1062</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>1063</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G11" s="8">
+        <v>35</v>
+      </c>
+      <c r="H11" s="8">
+        <v>35</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G12" s="8">
+        <v>900</v>
+      </c>
+      <c r="H12" s="8">
+        <v>30</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="3">
+        <v>870</v>
+      </c>
+      <c r="H13" s="3">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>1069</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>1070</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1570</v>
+      </c>
+      <c r="H14" s="8">
+        <v>35</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>1535</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1073</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1074</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="8">
+        <v>3930</v>
+      </c>
+      <c r="H15" s="8">
+        <v>40</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>3890</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="3">
+        <v>20</v>
+      </c>
+      <c r="H16" s="3">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G18" s="6">
+        <v>725</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="6">
+        <v>765</v>
+      </c>
+      <c r="H19" s="6">
+        <v>25</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>25</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1090</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>1091</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G21" s="8">
+        <v>0</v>
+      </c>
+      <c r="H21" s="8">
+        <v>30</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1115</v>
+      </c>
+      <c r="H22" s="6">
+        <v>25</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G23" s="3">
+        <v>875</v>
+      </c>
+      <c r="H23" s="3">
+        <v>25</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>637</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>639</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G24" s="8">
+        <v>880</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1101</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="3">
+        <v>0</v>
+      </c>
+      <c r="H25" s="3">
+        <v>20</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>1102</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G26" s="8">
+        <v>875</v>
+      </c>
+      <c r="H26" s="8">
+        <v>25</v>
+      </c>
+      <c r="I26" s="8">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1105</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1107</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>30</v>
+      </c>
+      <c r="I27" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1068</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>1108</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>1109</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G28" s="8">
+        <v>780</v>
+      </c>
+      <c r="H28" s="8">
+        <v>0</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="3">
+        <v>840</v>
+      </c>
+      <c r="H29" s="3">
+        <v>20</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>900</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="6">
+        <v>815</v>
+      </c>
+      <c r="H30" s="6">
+        <v>25</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>1025</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G31" s="6">
+        <v>45</v>
+      </c>
+      <c r="H31" s="6">
+        <v>25</v>
+      </c>
+      <c r="I31" s="6">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>1038</v>
+      </c>
+      <c r="M31" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G32" s="6">
+        <v>765</v>
+      </c>
+      <c r="H32" s="6">
+        <v>25</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F33" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G33" s="8">
+        <v>50</v>
+      </c>
+      <c r="H33" s="8">
+        <v>50</v>
+      </c>
+      <c r="I33" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+  <dimension ref="A1:P39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="78" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>40</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I39" si="0">G3-H3</f>
+        <v>-40</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>30</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3">
+        <v>30</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="6">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>30</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8">
+        <v>0</v>
+      </c>
+      <c r="H7" s="8">
+        <v>30</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1134</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="3">
+        <v>25</v>
+      </c>
+      <c r="H8" s="3">
+        <v>25</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="8">
+        <v>810</v>
+      </c>
+      <c r="H10" s="8">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>1139</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>1141</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G11" s="6">
+        <v>805</v>
+      </c>
+      <c r="H11" s="6">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>1143</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>1144</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G12" s="6">
+        <v>0</v>
+      </c>
+      <c r="H12" s="6">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1550</v>
+      </c>
+      <c r="H13" s="8">
+        <v>30</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="G14" s="5">
+        <v>980</v>
+      </c>
+      <c r="H14" s="5">
+        <v>30</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J14" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1145</v>
+      </c>
+      <c r="H15" s="3">
+        <v>25</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0</v>
+      </c>
+      <c r="H16" s="3">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G17" s="8">
+        <v>835</v>
+      </c>
+      <c r="H17" s="8">
+        <v>25</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="0"/>
+        <v>810</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1160</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1161</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>1162</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1655</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>1630</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>1164</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="3">
+        <v>660</v>
+      </c>
+      <c r="H19" s="3">
+        <v>20</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1166</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>1168</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>30</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>1171</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G21" s="6">
+        <v>375</v>
+      </c>
+      <c r="H21" s="6">
+        <v>25</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1173</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1174</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="8">
+        <v>805</v>
+      </c>
+      <c r="H22" s="8">
+        <v>25</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>30</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G24" s="6">
+        <v>1455</v>
+      </c>
+      <c r="H24" s="6">
+        <v>25</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="0"/>
+        <v>1430</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>1181</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>1182</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>1183</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
+        <v>25</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>1184</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>1185</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G26" s="8">
+        <v>810</v>
+      </c>
+      <c r="H26" s="8">
+        <v>30</v>
+      </c>
+      <c r="I26" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1189</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="8">
+        <v>720</v>
+      </c>
+      <c r="H27" s="8">
+        <v>30</v>
+      </c>
+      <c r="I27" s="8">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G28" s="8">
+        <v>0</v>
+      </c>
+      <c r="H28" s="8">
+        <v>25</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>1193</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>1086</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G29" s="6">
+        <v>715</v>
+      </c>
+      <c r="H29" s="6">
+        <v>25</v>
+      </c>
+      <c r="I29" s="6">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>1194</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G30" s="6">
+        <v>895</v>
+      </c>
+      <c r="H30" s="6">
+        <v>25</v>
+      </c>
+      <c r="I30" s="6">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>1196</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G31" s="3">
+        <v>800</v>
+      </c>
+      <c r="H31" s="3">
+        <v>20</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>1198</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" s="6">
+        <v>0</v>
+      </c>
+      <c r="H32" s="6">
+        <v>25</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>1199</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>1200</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>1201</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G33" s="6">
+        <v>815</v>
+      </c>
+      <c r="H33" s="6">
+        <v>25</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>1202</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>1203</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>1204</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G34" s="6">
+        <v>3100</v>
+      </c>
+      <c r="H34" s="6">
+        <v>35</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" si="0"/>
+        <v>3065</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1205</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>1206</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1207</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="3">
+        <v>825</v>
+      </c>
+      <c r="H35" s="3">
+        <v>25</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>1209</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G36" s="8">
+        <v>810</v>
+      </c>
+      <c r="H36" s="8">
+        <v>30</v>
+      </c>
+      <c r="I36" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>1211</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>1212</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G37" s="8">
+        <v>750</v>
+      </c>
+      <c r="H37" s="8">
+        <v>30</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>1214</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>1215</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>1216</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G38" s="6">
+        <v>775</v>
+      </c>
+      <c r="H38" s="6">
+        <v>25</v>
+      </c>
+      <c r="I38" s="6">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J38" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="6" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G39" s="3">
+        <v>0</v>
+      </c>
+      <c r="H39" s="3">
+        <v>40</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+  <dimension ref="A1:P34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="56.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1220</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>1221</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="8">
+        <v>865</v>
+      </c>
+      <c r="H3" s="8">
+        <v>25</v>
+      </c>
+      <c r="I3" s="8">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>840</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1226</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>1229</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>1230</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" s="8">
+        <v>1890</v>
+      </c>
+      <c r="H5" s="8">
+        <v>30</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="0"/>
+        <v>1860</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1232</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1233</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G6" s="3">
+        <v>845</v>
+      </c>
+      <c r="H6" s="3">
+        <v>25</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1234</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1235</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1236</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="3">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3">
+        <v>40</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1237</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1238</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1239</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="3">
+        <v>805</v>
+      </c>
+      <c r="H8" s="3">
+        <v>25</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1240</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1241</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G9" s="3">
+        <v>695</v>
+      </c>
+      <c r="H9" s="3">
+        <v>25</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>670</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1243</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1244</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1245</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="8">
+        <v>815</v>
+      </c>
+      <c r="H10" s="8">
+        <v>25</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1246</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1247</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>1248</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="G11" s="8">
+        <v>895</v>
+      </c>
+      <c r="H11" s="8">
+        <v>25</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>1252</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>1253</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>30</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>1254</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1765</v>
+      </c>
+      <c r="H14" s="8">
+        <v>25</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>1256</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>1257</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15" s="3">
+        <v>3600</v>
+      </c>
+      <c r="H15" s="3">
+        <v>35</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>3565</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1258</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1259</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G16" s="3">
+        <v>25</v>
+      </c>
+      <c r="H16" s="3">
+        <v>25</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1260</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>1261</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="G17" s="3">
+        <v>660</v>
+      </c>
+      <c r="H17" s="3">
+        <v>20</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>640</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>1264</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="8">
+        <v>815</v>
+      </c>
+      <c r="H18" s="8">
+        <v>35</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>1266</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G19" s="8">
+        <v>805</v>
+      </c>
+      <c r="H19" s="8">
+        <v>25</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>1268</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="8">
+        <v>690</v>
+      </c>
+      <c r="H20" s="8">
+        <v>30</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>1271</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>1272</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="8">
+        <v>1420</v>
+      </c>
+      <c r="H21" s="8">
+        <v>30</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="0"/>
+        <v>1390</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1273</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>25</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1276</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>30</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>1279</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>1280</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="8">
+        <v>1390</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>1360</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="3">
+        <v>985</v>
+      </c>
+      <c r="H25" s="3">
+        <v>25</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>1285</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>1286</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>1287</v>
+      </c>
+      <c r="F26" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="8">
+        <v>1630</v>
+      </c>
+      <c r="H26" s="8">
+        <v>30</v>
+      </c>
+      <c r="I26" s="8">
+        <f t="shared" si="0"/>
+        <v>1600</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1695</v>
+      </c>
+      <c r="H27" s="3">
+        <v>25</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>1670</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>1292</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1293</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="3">
+        <v>990</v>
+      </c>
+      <c r="H28" s="3">
+        <v>20</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1295</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1296</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="3">
+        <v>540</v>
+      </c>
+      <c r="H29" s="3">
+        <v>30</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="0"/>
+        <v>510</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>1298</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1299</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="3">
+        <v>1530</v>
+      </c>
+      <c r="H30" s="3">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>1301</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>1302</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G31" s="3">
+        <v>765</v>
+      </c>
+      <c r="H31" s="3">
+        <v>25</v>
+      </c>
+      <c r="I31" s="3">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>1303</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>1305</v>
+      </c>
+      <c r="F32" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="G32" s="8">
+        <v>815</v>
+      </c>
+      <c r="H32" s="8">
+        <v>25</v>
+      </c>
+      <c r="I32" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>1223</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="3">
+        <v>30</v>
+      </c>
+      <c r="H33" s="3">
+        <v>30</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>1309</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G34" s="5">
+        <v>35</v>
+      </c>
+      <c r="H34" s="5">
+        <v>35</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="5" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+  <dimension ref="A1:Q41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="93.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -5832,10 +10545,10 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
-        <v>434</v>
+        <v>721</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1034</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -5888,40 +10601,40 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>1036</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>1037</v>
-      </c>
-      <c r="F3" s="6" t="s">
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1311</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="G3" s="6">
-        <v>815</v>
-      </c>
-      <c r="H3" s="6">
-        <v>25</v>
-      </c>
-      <c r="I3" s="6">
-        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
-        <v>790</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>1038</v>
+      <c r="G3" s="3">
+        <v>715</v>
+      </c>
+      <c r="H3" s="3">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I39" si="0">G3-H3</f>
+        <v>690</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -5929,35 +10642,38 @@
         <v>18</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>1039</v>
+        <v>1315</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1040</v>
+        <v>1316</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>1041</v>
+        <v>1317</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>131</v>
+        <v>22</v>
       </c>
       <c r="G4" s="8">
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="H4" s="8">
         <v>30</v>
       </c>
       <c r="I4" s="8">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>-30</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>1042</v>
+        <v>1318</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>1038</v>
+        <v>1314</v>
+      </c>
+      <c r="M4" s="8" t="s">
+        <v>1400</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -5965,26 +10681,26 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1111</v>
+        <v>854</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1043</v>
+        <v>1319</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F5" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G5" s="3">
-        <v>875</v>
+        <v>0</v>
       </c>
       <c r="H5" s="3">
         <v>25</v>
       </c>
       <c r="I5" s="3">
         <f t="shared" si="0"/>
-        <v>850</v>
+        <v>-25</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>24</v>
@@ -5993,7 +10709,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>1038</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6001,26 +10717,26 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1045</v>
+        <v>856</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1046</v>
+        <v>1320</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1112</v>
+        <v>1378</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="3">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="H6" s="3">
         <v>30</v>
       </c>
       <c r="I6" s="3">
         <f t="shared" si="0"/>
-        <v>-30</v>
+        <v>350</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>24</v>
@@ -6029,7 +10745,7 @@
         <v>24</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>1038</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6037,293 +10753,293 @@
         <v>18</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1109</v>
+        <v>1321</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1047</v>
+        <v>1322</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1048</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>102</v>
+        <v>1398</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>41</v>
       </c>
       <c r="G7" s="8">
-        <v>845</v>
+        <v>0</v>
       </c>
       <c r="H7" s="8">
         <v>25</v>
       </c>
       <c r="I7" s="8">
         <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1323</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1325</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>1376</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G9" s="3">
+        <v>810</v>
+      </c>
+      <c r="H9" s="3">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1327</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1328</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>1329</v>
+      </c>
+      <c r="G10" s="8">
+        <v>865</v>
+      </c>
+      <c r="H10" s="8">
+        <v>35</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>1330</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>1331</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1332</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="3">
         <v>820</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>1042</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>1050</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="H11" s="3">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1379</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G8" s="3">
-        <v>920</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="G12" s="3">
+        <v>990</v>
+      </c>
+      <c r="H12" s="3">
         <v>30</v>
       </c>
-      <c r="I8" s="3">
-        <f t="shared" si="0"/>
-        <v>890</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>1051</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>1052</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>1053</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="G9" s="6">
-        <v>765</v>
-      </c>
-      <c r="H9" s="6">
-        <v>25</v>
-      </c>
-      <c r="I9" s="6">
-        <f t="shared" si="0"/>
-        <v>740</v>
-      </c>
-      <c r="J9" s="6" t="s">
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>1335</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>1336</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="8">
+        <v>1135</v>
+      </c>
+      <c r="H13" s="8">
+        <v>35</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
+        <v>1100</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>1337</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>1384</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>1385</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G14" s="6">
+        <v>780</v>
+      </c>
+      <c r="H14" s="6">
+        <v>20</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>1054</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>1092</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>1093</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G10" s="6">
-        <v>25</v>
-      </c>
-      <c r="H10" s="6">
-        <v>25</v>
-      </c>
-      <c r="I10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>1055</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>1102</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="8">
-        <v>35</v>
-      </c>
-      <c r="H11" s="8">
-        <v>35</v>
-      </c>
-      <c r="I11" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>1042</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>1056</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>1057</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>1110</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="G12" s="8">
-        <v>900</v>
-      </c>
-      <c r="H12" s="8">
-        <v>30</v>
-      </c>
-      <c r="I12" s="8">
-        <f t="shared" si="0"/>
-        <v>870</v>
-      </c>
-      <c r="J12" s="8" t="s">
-        <v>1042</v>
-      </c>
-      <c r="K12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" s="3">
-        <v>870</v>
-      </c>
-      <c r="H13" s="3">
-        <v>20</v>
-      </c>
-      <c r="I13" s="3">
-        <f t="shared" si="0"/>
-        <v>850</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>1059</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>1060</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>1061</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G14" s="8">
-        <v>1570</v>
-      </c>
-      <c r="H14" s="8">
-        <v>35</v>
-      </c>
-      <c r="I14" s="8">
-        <f t="shared" si="0"/>
-        <v>1535</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>1042</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>1038</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>1101</v>
+      <c r="K14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6331,179 +11047,179 @@
         <v>18</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1062</v>
+        <v>1392</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1063</v>
+        <v>1338</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1104</v>
+        <v>1393</v>
       </c>
       <c r="F15" s="8" t="s">
-        <v>22</v>
+        <v>239</v>
       </c>
       <c r="G15" s="8">
-        <v>3930</v>
+        <v>1135</v>
       </c>
       <c r="H15" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="I15" s="8">
         <f t="shared" si="0"/>
-        <v>3890</v>
+        <v>1110</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>1042</v>
+        <v>1318</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>1114</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F16" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>1381</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>1339</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G16" s="6">
+        <v>755</v>
+      </c>
+      <c r="H16" s="6">
+        <v>25</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="0"/>
+        <v>730</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G17" s="3">
+        <v>1770</v>
+      </c>
+      <c r="H17" s="3">
         <v>20</v>
       </c>
-      <c r="H16" s="3">
-        <v>20</v>
-      </c>
-      <c r="I16" s="3">
-        <f t="shared" si="0"/>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1341</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="3">
         <v>0</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="17" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>1065</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>1066</v>
-      </c>
-      <c r="E17" s="8" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G17" s="8">
-        <v>0</v>
-      </c>
-      <c r="H17" s="8">
+      <c r="H18" s="3">
         <v>30</v>
       </c>
-      <c r="I17" s="8">
+      <c r="I18" s="3">
         <f t="shared" si="0"/>
         <v>-30</v>
       </c>
-      <c r="J17" s="8" t="s">
-        <v>1042</v>
-      </c>
-      <c r="K17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="18" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>1067</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>1097</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="G18" s="6">
-        <v>725</v>
-      </c>
-      <c r="H18" s="6">
-        <v>25</v>
-      </c>
-      <c r="I18" s="6">
-        <f t="shared" si="0"/>
-        <v>700</v>
-      </c>
-      <c r="J18" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L18" s="6" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="19" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>1094</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>1095</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="6">
-        <v>765</v>
-      </c>
-      <c r="H19" s="6">
-        <v>25</v>
-      </c>
-      <c r="I19" s="6">
-        <f t="shared" si="0"/>
-        <v>740</v>
-      </c>
-      <c r="J19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L19" s="6" t="s">
-        <v>1038</v>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="8">
+        <v>470</v>
+      </c>
+      <c r="H19" s="8">
+        <v>30</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="20" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -6511,26 +11227,26 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1116</v>
+        <v>1346</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1069</v>
+        <v>1347</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1117</v>
+        <v>1348</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>880</v>
       </c>
       <c r="H20" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="I20" s="3">
         <f t="shared" si="0"/>
-        <v>-25</v>
+        <v>850</v>
       </c>
       <c r="J20" s="3" t="s">
         <v>24</v>
@@ -6539,7 +11255,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>1038</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="21" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6547,107 +11263,116 @@
         <v>18</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1070</v>
+        <v>1349</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1071</v>
+        <v>1350</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>763</v>
+        <v>1399</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="G21" s="8">
+        <v>985</v>
+      </c>
+      <c r="H21" s="8">
+        <v>25</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1352</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1353</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1354</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="8">
         <v>0</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H22" s="8">
         <v>30</v>
       </c>
-      <c r="I21" s="8">
+      <c r="I22" s="8">
         <f t="shared" si="0"/>
         <v>-30</v>
       </c>
-      <c r="J21" s="8" t="s">
-        <v>1042</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="22" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="6">
-        <v>1115</v>
-      </c>
-      <c r="H22" s="6">
-        <v>25</v>
-      </c>
-      <c r="I22" s="6">
-        <f t="shared" si="0"/>
-        <v>1090</v>
-      </c>
-      <c r="J22" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="K22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" s="6" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="23" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>1119</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>1120</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G23" s="3">
-        <v>875</v>
-      </c>
-      <c r="H23" s="3">
-        <v>25</v>
-      </c>
-      <c r="I23" s="3">
-        <f t="shared" si="0"/>
-        <v>850</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>1038</v>
+      <c r="J22" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1355</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1356</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>0</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>1314</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6655,71 +11380,71 @@
         <v>18</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>637</v>
+        <v>1394</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1074</v>
+        <v>1357</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>639</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>149</v>
+        <v>1395</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>131</v>
       </c>
       <c r="G24" s="8">
-        <v>880</v>
+        <v>850</v>
       </c>
       <c r="H24" s="8">
         <v>30</v>
       </c>
       <c r="I24" s="8">
         <f t="shared" si="0"/>
-        <v>850</v>
+        <v>820</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>1042</v>
+        <v>1318</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="25" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>1076</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" s="3">
-        <v>0</v>
-      </c>
-      <c r="H25" s="3">
-        <v>20</v>
-      </c>
-      <c r="I25" s="3">
-        <f t="shared" si="0"/>
-        <v>-20</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>1038</v>
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>1358</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>1359</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>1396</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="8">
+        <v>820</v>
+      </c>
+      <c r="H25" s="8">
+        <v>30</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>1318</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="26" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6727,35 +11452,35 @@
         <v>18</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1078</v>
+        <v>1391</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1079</v>
+        <v>1386</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>1080</v>
+        <v>1360</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>85</v>
+        <v>239</v>
       </c>
       <c r="G26" s="8">
-        <v>875</v>
+        <v>1505</v>
       </c>
       <c r="H26" s="8">
         <v>25</v>
       </c>
       <c r="I26" s="8">
         <f t="shared" si="0"/>
-        <v>850</v>
+        <v>1480</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>1042</v>
+        <v>1318</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>1038</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="27" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6763,35 +11488,35 @@
         <v>18</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1106</v>
+        <v>748</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1107</v>
+        <v>1361</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>131</v>
+        <v>1362</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="G27" s="8">
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="H27" s="8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I27" s="8">
         <f t="shared" si="0"/>
-        <v>-30</v>
+        <v>700</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>1042</v>
+        <v>1318</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>1038</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="28" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -6799,110 +11524,110 @@
         <v>18</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1059</v>
+        <v>1349</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1081</v>
+        <v>1363</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>1082</v>
+        <v>1351</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
       <c r="G28" s="8">
-        <v>780</v>
+        <v>850</v>
       </c>
       <c r="H28" s="8">
         <v>0</v>
       </c>
       <c r="I28" s="8">
         <f t="shared" si="0"/>
-        <v>780</v>
+        <v>850</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>1042</v>
+        <v>1318</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>1038</v>
+        <v>1314</v>
       </c>
       <c r="M28" s="8" t="s">
         <v>288</v>
       </c>
     </row>
-    <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>1083</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>1084</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>1085</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G29" s="3">
-        <v>840</v>
-      </c>
-      <c r="H29" s="3">
-        <v>20</v>
-      </c>
-      <c r="I29" s="3">
-        <f t="shared" si="0"/>
-        <v>820</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="30" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>900</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>1086</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="G30" s="6">
-        <v>815</v>
-      </c>
-      <c r="H30" s="6">
-        <v>25</v>
-      </c>
-      <c r="I30" s="6">
-        <f t="shared" si="0"/>
-        <v>790</v>
-      </c>
-      <c r="J30" s="6" t="s">
+    <row r="29" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>1365</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>1383</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G29" s="6">
+        <v>985</v>
+      </c>
+      <c r="H29" s="6">
+        <v>25</v>
+      </c>
+      <c r="I29" s="6">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J29" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="K30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="L30" s="6" t="s">
-        <v>1038</v>
+      <c r="K29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>1367</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1377</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G30" s="3">
+        <v>880</v>
+      </c>
+      <c r="H30" s="3">
+        <v>30</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>1314</v>
       </c>
     </row>
     <row r="31" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6910,26 +11635,26 @@
         <v>18</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1025</v>
+        <v>1323</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1087</v>
+        <v>1368</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>1027</v>
+        <v>1389</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>186</v>
+        <v>63</v>
       </c>
       <c r="G31" s="6">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="H31" s="6">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I31" s="6">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>37</v>
@@ -6938,10 +11663,10 @@
         <v>24</v>
       </c>
       <c r="L31" s="6" t="s">
-        <v>1038</v>
+        <v>1314</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>138</v>
+        <v>288</v>
       </c>
     </row>
     <row r="32" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -6949,26 +11674,26 @@
         <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>1088</v>
+        <v>1369</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1089</v>
+        <v>1387</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1090</v>
-      </c>
-      <c r="F32" s="7" t="s">
+        <v>1388</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>63</v>
       </c>
       <c r="G32" s="6">
-        <v>765</v>
+        <v>925</v>
       </c>
       <c r="H32" s="6">
         <v>25</v>
       </c>
       <c r="I32" s="6">
         <f t="shared" si="0"/>
-        <v>740</v>
+        <v>900</v>
       </c>
       <c r="J32" s="6" t="s">
         <v>37</v>
@@ -6977,47 +11702,364 @@
         <v>24</v>
       </c>
       <c r="L32" s="6" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1370</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1371</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1372</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="3">
+        <v>820</v>
+      </c>
+      <c r="H33" s="3">
+        <v>30</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G34" s="6">
+        <v>25</v>
+      </c>
+      <c r="H34" s="6">
+        <v>25</v>
+      </c>
+      <c r="I34" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1373</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1380</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0</v>
+      </c>
+      <c r="H35" s="3">
+        <v>35</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>1374</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" s="6">
+        <v>0</v>
+      </c>
+      <c r="H36" s="6">
+        <v>30</v>
+      </c>
+      <c r="I36" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J36" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="6" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G37" s="3">
+        <v>865</v>
+      </c>
+      <c r="H37" s="3">
+        <v>35</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1375</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" s="3">
+        <v>30</v>
+      </c>
+      <c r="H38" s="3">
+        <v>30</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G39" s="3">
+        <v>860</v>
+      </c>
+      <c r="H39" s="3">
+        <v>30</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F40" s="12">
+        <v>10</v>
+      </c>
+      <c r="G40" s="11">
+        <v>1145</v>
+      </c>
+      <c r="H40" s="11">
+        <v>25</v>
+      </c>
+      <c r="I40" s="11">
+        <v>1120</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K40" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="11" t="s">
+        <v>969</v>
+      </c>
+      <c r="M40" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N40" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O40" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P40" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q40" s="11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>1053</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>1054</v>
+      </c>
+      <c r="F41" s="12">
+        <v>2</v>
+      </c>
+      <c r="G41" s="11">
+        <v>920</v>
+      </c>
+      <c r="H41" s="11">
+        <v>30</v>
+      </c>
+      <c r="I41" s="11">
+        <v>890</v>
+      </c>
+      <c r="J41" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="11" t="s">
         <v>1038</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8" t="s">
-        <v>193</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>1100</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G33" s="8">
-        <v>50</v>
-      </c>
-      <c r="H33" s="8">
-        <v>50</v>
-      </c>
-      <c r="I33" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J33" s="8" t="s">
-        <v>1042</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>1038</v>
+      <c r="M41" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N41" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P41" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q41" s="11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8499EE5E-5161-4C66-88F9-A2696A91346E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C407264-DD13-4CF3-9CE2-CE8072A9A7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="14-05" sheetId="15" r:id="rId11"/>
     <sheet name="15-05" sheetId="16" r:id="rId12"/>
     <sheet name="16-05" sheetId="17" r:id="rId13"/>
+    <sheet name="18-05" sheetId="18" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -48,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4223" uniqueCount="1403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4558" uniqueCount="1496">
   <si>
     <t>THU 6</t>
   </si>
@@ -4007,36 +4008,54 @@
     <t>AT 16-05</t>
   </si>
   <si>
+    <t>kh ck shop 4210k</t>
+  </si>
+  <si>
     <t>HD021355</t>
   </si>
   <si>
     <t>HD021442</t>
   </si>
   <si>
+    <t>42, đường 21,Khu dân cư bình chiểu, P tam bình (chợ đầu mối nông sản thủ đức)</t>
+  </si>
+  <si>
     <t>Phạm T. Thảo</t>
   </si>
   <si>
     <t>HD021288</t>
   </si>
   <si>
+    <t>63 dương bá trạc p. rạch ông</t>
+  </si>
+  <si>
     <t>VERISKA (YAYANG) - ROOM 104.</t>
   </si>
   <si>
     <t>HD021409</t>
   </si>
   <si>
+    <t>Saigon Europe Hotel, Số 207 đường Đề Thám, phường bến Thành</t>
+  </si>
+  <si>
     <t>chị Huyền</t>
   </si>
   <si>
     <t>HĐ021386</t>
   </si>
   <si>
+    <t>9B nguyễn xí, phường 26</t>
+  </si>
+  <si>
     <t>Nhận hành giúp chị phương (ở Úc) fb Phương My</t>
   </si>
   <si>
     <t>HD021421</t>
   </si>
   <si>
+    <t>126/5h song hành, tân hiệp</t>
+  </si>
+  <si>
     <t>hoc mon</t>
   </si>
   <si>
@@ -4055,21 +4074,45 @@
     <t>HD021213</t>
   </si>
   <si>
+    <t>67 mai chí thọ phường an phú</t>
+  </si>
+  <si>
     <t>Trần Bảo Hân (inst tienbaohen17)</t>
   </si>
   <si>
     <t>HD021310</t>
   </si>
   <si>
+    <t>E4/25a đường Nguyễn Hữu Trí, khu phố 12, thị trấn Tân Túc</t>
+  </si>
+  <si>
     <t>Hiệp fb Đặng Tổ Trinh</t>
   </si>
   <si>
+    <t>HD021271</t>
+  </si>
+  <si>
+    <t>Số 3 hoàng minh giám phường đức nhuận</t>
+  </si>
+  <si>
+    <t>Loan Trần</t>
+  </si>
+  <si>
     <t>HD021379</t>
   </si>
   <si>
+    <t>64/24C hoà bình phường hòa bình</t>
+  </si>
+  <si>
+    <t>Linh Tiêu</t>
+  </si>
+  <si>
     <t>HD021267</t>
   </si>
   <si>
+    <t>97 Ký Con, p. Nguyễn Thái Bình</t>
+  </si>
+  <si>
     <t>HD021227</t>
   </si>
   <si>
@@ -4103,63 +4146,99 @@
     <t>HD021425</t>
   </si>
   <si>
+    <t>287/1/5 thành công, tân thành</t>
+  </si>
+  <si>
+    <t>Ngọc Mỹ Kim</t>
+  </si>
+  <si>
+    <t>HD021327</t>
+  </si>
+  <si>
+    <t>Chung cu topaz elite drgon 2c p4 ta quang buu</t>
+  </si>
+  <si>
+    <t>kh ck shop 1820k</t>
+  </si>
+  <si>
+    <t>Trần Bảo Hân (inst tranbaohan17)</t>
+  </si>
+  <si>
+    <t>HD021309</t>
+  </si>
+  <si>
+    <t>Cẩm Cẩm</t>
+  </si>
+  <si>
+    <t>HD021193</t>
+  </si>
+  <si>
+    <t>150 Hoàng Trọng Mậu Tân Hưng</t>
+  </si>
+  <si>
+    <t>Sam Sam</t>
+  </si>
+  <si>
+    <t>HD021214</t>
+  </si>
+  <si>
+    <t>Sunrise city view tòa B .33 Nguyễn Hữu Thọ phường tân hưng</t>
+  </si>
+  <si>
+    <t>Ann Ann</t>
+  </si>
+  <si>
+    <t>HD021246</t>
+  </si>
+  <si>
+    <t>172 lê thị bạch cát p11</t>
+  </si>
+  <si>
+    <t>HD021369</t>
+  </si>
+  <si>
+    <t>87/10 trần quang cơ phú thạnh</t>
+  </si>
+  <si>
+    <t>HD021282</t>
+  </si>
+  <si>
     <t>287/1/5 thành công, tấn thành</t>
   </si>
   <si>
-    <t>Ngọc Mỹ Kim</t>
-  </si>
-  <si>
-    <t>HD021327</t>
-  </si>
-  <si>
-    <t>Chung cu topaz elite drgon 2c p4 ta quang buu</t>
-  </si>
-  <si>
-    <t>Trần Bảo Hân (inst tranbaohan17)</t>
-  </si>
-  <si>
-    <t>HD021309</t>
-  </si>
-  <si>
-    <t>HD021193</t>
-  </si>
-  <si>
-    <t>Sam Sam</t>
-  </si>
-  <si>
-    <t>HD021214</t>
-  </si>
-  <si>
-    <t>172 lê thị bạch cát p11</t>
-  </si>
-  <si>
-    <t>HD021369</t>
-  </si>
-  <si>
-    <t>87/10 trần quang cơ phú thạnh</t>
-  </si>
-  <si>
-    <t>HD021282</t>
-  </si>
-  <si>
     <t>Thien Phu Nguyen</t>
   </si>
   <si>
     <t>HD021468</t>
   </si>
   <si>
+    <t>Block B - Chung cư RiverGate Residence 151-155 Bến Vân Đồn, Phường Khánh Hội</t>
+  </si>
+  <si>
     <t>Ánh Hoàng</t>
   </si>
   <si>
     <t>HD021275</t>
   </si>
   <si>
+    <t>Stown Tham Lương sảnh B Phường Tân Thới Nhất</t>
+  </si>
+  <si>
     <t>HD021185</t>
   </si>
   <si>
+    <t>Số 207 đường Đề Thám, phường bến Thành</t>
+  </si>
+  <si>
     <t>Mai Sương</t>
   </si>
   <si>
+    <t>HD021469</t>
+  </si>
+  <si>
+    <t>55/3 trần đình xu, phường cầu kho</t>
+  </si>
+  <si>
     <t>Huỳnh Phương Mỹ Duyên</t>
   </si>
   <si>
@@ -4172,91 +4251,292 @@
     <t>Hồng Thắm</t>
   </si>
   <si>
+    <t>27 đông hưng thuận 45 tân hưng thuận</t>
+  </si>
+  <si>
     <t>Heng Stella</t>
   </si>
   <si>
     <t>tân sơn p12</t>
   </si>
   <si>
-    <t>9B nguyễn xí, phường 26</t>
-  </si>
-  <si>
-    <t>Stown Tham Lương sảnh B Phường Tân Thới Nhất</t>
-  </si>
-  <si>
-    <t>42, đường 21,Khu dân cư bình chiểu, P tam bình (chợ đầu mối nông sản thủ đức)</t>
-  </si>
-  <si>
-    <t>67 mai chí thọ phường an phú</t>
-  </si>
-  <si>
-    <t>27 đông hưng thuận 45 tân hưng thuận</t>
-  </si>
-  <si>
-    <t>Linh Tiêu</t>
-  </si>
-  <si>
-    <t>97 Ký Con, p. Nguyễn Thái Bình</t>
-  </si>
-  <si>
-    <t>Block B - Chung cư RiverGate Residence 151-155 Bến Vân Đồn, Phường Khánh Hội</t>
-  </si>
-  <si>
-    <t>HD021271</t>
-  </si>
-  <si>
-    <t>Số 3 hoàng minh giám phường đức nhuận</t>
-  </si>
-  <si>
-    <t>HD021246</t>
-  </si>
-  <si>
-    <t>HD021469</t>
-  </si>
-  <si>
-    <t>55/3 trần đình xu, phường cầu kho</t>
-  </si>
-  <si>
-    <t>Số 207 đường Đề Thám, phường bến Thành</t>
-  </si>
-  <si>
-    <t>Saigon Europe Hotel, Số 207 đường Đề Thám, phường bến Thành</t>
-  </si>
-  <si>
-    <t>Ann Ann</t>
-  </si>
-  <si>
-    <t>Loan Trần</t>
-  </si>
-  <si>
-    <t>64/24C hoà bình phường hòa bình</t>
-  </si>
-  <si>
-    <t>Cẩm Cẩm</t>
-  </si>
-  <si>
-    <t>150 Hoàng Trọng Mậu Tân Hưng</t>
-  </si>
-  <si>
-    <t>Sunrise city view tòa B .33 Nguyễn Hữu Thọ phường tân hưng</t>
-  </si>
-  <si>
-    <t>126/5h song hành, tân hiệp</t>
-  </si>
-  <si>
-    <t>63 dương bá trạc p. rạch ông</t>
-  </si>
-  <si>
-    <t>287/1/5 thành công, tân thành</t>
-  </si>
-  <si>
-    <t>kh ck shop 4210k</t>
-  </si>
-  <si>
-    <t>E4/25a đường Nguyễn Hữu Trí, khu phố 12, thị trấn Tân Túc</t>
-  </si>
-  <si>
-    <t>kh ck shop 1820k</t>
+    <t>NGAY 18-5</t>
+  </si>
+  <si>
+    <t>18-05-2026</t>
+  </si>
+  <si>
+    <t>NIKI</t>
+  </si>
+  <si>
+    <t>AT 18-05</t>
+  </si>
+  <si>
+    <t>Heng Roza (EV38382)</t>
+  </si>
+  <si>
+    <t>Gia Huy nhận của ELIS NGUYỄN ( singapore)</t>
+  </si>
+  <si>
+    <t>HD021334</t>
+  </si>
+  <si>
+    <t>HD021855</t>
+  </si>
+  <si>
+    <t>Quỳnh Nga</t>
+  </si>
+  <si>
+    <t>HD021747</t>
+  </si>
+  <si>
+    <t>Ngọc - fb Naila Unner</t>
+  </si>
+  <si>
+    <t>HD021827</t>
+  </si>
+  <si>
+    <t>Rivergate</t>
+  </si>
+  <si>
+    <t>HD021876</t>
+  </si>
+  <si>
+    <t>Ngọc Hồng Thương</t>
+  </si>
+  <si>
+    <t>HD021553</t>
+  </si>
+  <si>
+    <t>51 đường 81 tân quy</t>
+  </si>
+  <si>
+    <t>PIMVIPA 3883</t>
+  </si>
+  <si>
+    <t>HD021837</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Mỹ Phúc</t>
+  </si>
+  <si>
+    <t>HD021574</t>
+  </si>
+  <si>
+    <t>nha The Sun Avenue (tòa S5) 28 Mai Chí Thọ, An Phú</t>
+  </si>
+  <si>
+    <t>HD021424</t>
+  </si>
+  <si>
+    <t>Gia Tuệ</t>
+  </si>
+  <si>
+    <t>HD021808</t>
+  </si>
+  <si>
+    <t>42/32 trần đại nghĩa, tân tạo a</t>
+  </si>
+  <si>
+    <t>Ngọc</t>
+  </si>
+  <si>
+    <t>HD021842</t>
+  </si>
+  <si>
+    <t>Hoàng Trâm Anh</t>
+  </si>
+  <si>
+    <t>HD021810</t>
+  </si>
+  <si>
+    <t>HSM RIDA CHUON</t>
+  </si>
+  <si>
+    <t>HD021615</t>
+  </si>
+  <si>
+    <t>177c đường số 1 bình hưng hòa b</t>
+  </si>
+  <si>
+    <t>Trúc Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021871</t>
+  </si>
+  <si>
+    <t>38 Đường 6 Linh Chiếu</t>
+  </si>
+  <si>
+    <t>Hợp Vũ</t>
+  </si>
+  <si>
+    <t>HD021640</t>
+  </si>
+  <si>
+    <t>2A Phan Chu Trinh, P Hiệp Phú</t>
+  </si>
+  <si>
+    <t>HD021866</t>
+  </si>
+  <si>
+    <t>Đối diện 110/42 đường số 5 phường 17</t>
+  </si>
+  <si>
+    <t>HD021418</t>
+  </si>
+  <si>
+    <t>Ái Nương</t>
+  </si>
+  <si>
+    <t>HD021666</t>
+  </si>
+  <si>
+    <t>154/33 au dương lân phường 3</t>
+  </si>
+  <si>
+    <t>Trân Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021600</t>
+  </si>
+  <si>
+    <t>HD021539</t>
+  </si>
+  <si>
+    <t>MC Phương Nhi</t>
+  </si>
+  <si>
+    <t>HD021829</t>
+  </si>
+  <si>
+    <t>99 Trần Bá Giao An Nhơn</t>
+  </si>
+  <si>
+    <t>chị Bích Huyền</t>
+  </si>
+  <si>
+    <t>HD021868</t>
+  </si>
+  <si>
+    <t>Số 4 đường số 22 kdc bình hưng</t>
+  </si>
+  <si>
+    <t>HD021775</t>
+  </si>
+  <si>
+    <t>Ngân Ngân</t>
+  </si>
+  <si>
+    <t>Phuong Nguyen</t>
+  </si>
+  <si>
+    <t>HD021530</t>
+  </si>
+  <si>
+    <t>Eco green toà I, HR30710, 39 Nguyễn Văn linh</t>
+  </si>
+  <si>
+    <t>HD021612</t>
+  </si>
+  <si>
+    <t>497/73/5 phan văn trị Phường 5</t>
+  </si>
+  <si>
+    <t>Ngann Lee</t>
+  </si>
+  <si>
+    <t>HD021534</t>
+  </si>
+  <si>
+    <t>222 pasteur, phường xuân hòa</t>
+  </si>
+  <si>
+    <t>2/11 Đường Thiên Phước, Phường 9</t>
+  </si>
+  <si>
+    <t>29/7 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>Hong Nho + NGUYỄN THỊ DIỄM CHI</t>
+  </si>
+  <si>
+    <t>SU ANH</t>
+  </si>
+  <si>
+    <t>177 Nguyễn Đình Chiểu, p. Xuân Hòa</t>
+  </si>
+  <si>
+    <t>Thinh HB</t>
+  </si>
+  <si>
+    <t>HD021608</t>
+  </si>
+  <si>
+    <t>17 cô giang, phường cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Tô Tô</t>
+  </si>
+  <si>
+    <t>HD021603</t>
+  </si>
+  <si>
+    <t>46 Lê Thị Riêng, phường Bến Thành</t>
+  </si>
+  <si>
+    <t>56/7 đường Tân Hoà 2 phường Hiệp Phú</t>
+  </si>
+  <si>
+    <t>Vân Thuỳ</t>
+  </si>
+  <si>
+    <t>như fb Đặng Tố Trinh</t>
+  </si>
+  <si>
+    <t>129/34 Nguyễn Văn Công, P. 3</t>
+  </si>
+  <si>
+    <t>11 Nguyễn Bá Huân phường thảo điền</t>
+  </si>
+  <si>
+    <t>HD021620</t>
+  </si>
+  <si>
+    <t>74B/148 thống nhất p15</t>
+  </si>
+  <si>
+    <t>Nguyễn Thảo Uyên</t>
+  </si>
+  <si>
+    <t>HD021746</t>
+  </si>
+  <si>
+    <t>15/32/56 võ duy ninh p22</t>
+  </si>
+  <si>
+    <t>Nga Còi</t>
+  </si>
+  <si>
+    <t>Sửa xe Anh Sơn, liên ấp 2,3,4 Vĩnh Lộc A</t>
+  </si>
+  <si>
+    <t>Central premium lock A</t>
+  </si>
+  <si>
+    <t>Chị Bích Huyền</t>
+  </si>
+  <si>
+    <t>số 4 đường số 22 kdc bình hưng</t>
+  </si>
+  <si>
+    <t>HD021621</t>
+  </si>
+  <si>
+    <t>360 lạc long quân phường 5 (phường hòa bình)</t>
+  </si>
+  <si>
+    <t>HD020691</t>
   </si>
 </sst>
 </file>
@@ -10531,10 +10811,12 @@
   <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="93.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -10673,7 +10955,7 @@
         <v>1314</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>1400</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -10684,7 +10966,7 @@
         <v>854</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>242</v>
@@ -10720,10 +11002,10 @@
         <v>856</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1378</v>
+        <v>1322</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>77</v>
@@ -10753,13 +11035,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1398</v>
+        <v>1325</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>41</v>
@@ -10789,13 +11071,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1390</v>
+        <v>1328</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>63</v>
@@ -10828,13 +11110,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>1325</v>
+        <v>1329</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>1326</v>
+        <v>1330</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>1376</v>
+        <v>1331</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>81</v>
@@ -10864,16 +11146,16 @@
         <v>18</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1327</v>
+        <v>1332</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1328</v>
+        <v>1333</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1397</v>
+        <v>1334</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>1329</v>
+        <v>1335</v>
       </c>
       <c r="G10" s="8">
         <v>865</v>
@@ -10900,13 +11182,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>1330</v>
+        <v>1336</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1331</v>
+        <v>1337</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1332</v>
+        <v>1338</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>77</v>
@@ -10936,13 +11218,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1333</v>
+        <v>1339</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1334</v>
+        <v>1340</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1379</v>
+        <v>1341</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>48</v>
@@ -10972,13 +11254,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1335</v>
+        <v>1342</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1336</v>
+        <v>1343</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1401</v>
+        <v>1344</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>52</v>
@@ -11011,13 +11293,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1337</v>
+        <v>1345</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1384</v>
+        <v>1346</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1385</v>
+        <v>1347</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>355</v>
@@ -11047,13 +11329,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1392</v>
+        <v>1348</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1338</v>
+        <v>1349</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1393</v>
+        <v>1350</v>
       </c>
       <c r="F15" s="8" t="s">
         <v>239</v>
@@ -11083,13 +11365,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1381</v>
+        <v>1351</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1339</v>
+        <v>1352</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>1382</v>
+        <v>1353</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>63</v>
@@ -11122,7 +11404,7 @@
         <v>177</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1340</v>
+        <v>1354</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>179</v>
@@ -11155,10 +11437,10 @@
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1341</v>
+        <v>1355</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1342</v>
+        <v>1356</v>
       </c>
       <c r="E18" s="3" t="s">
         <v>511</v>
@@ -11191,13 +11473,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1343</v>
+        <v>1357</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1344</v>
+        <v>1358</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1345</v>
+        <v>1359</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>131</v>
@@ -11227,13 +11509,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1346</v>
+        <v>1360</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1347</v>
+        <v>1361</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1348</v>
+        <v>1362</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>77</v>
@@ -11263,13 +11545,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1349</v>
+        <v>1363</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1350</v>
+        <v>1364</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>1399</v>
+        <v>1365</v>
       </c>
       <c r="F21" s="8" t="s">
         <v>85</v>
@@ -11302,13 +11584,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1352</v>
+        <v>1366</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1353</v>
+        <v>1367</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1354</v>
+        <v>1368</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>41</v>
@@ -11333,7 +11615,7 @@
         <v>1314</v>
       </c>
       <c r="M22" s="8" t="s">
-        <v>1402</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="23" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -11341,13 +11623,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1355</v>
+        <v>1370</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1356</v>
+        <v>1371</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>1401</v>
+        <v>1344</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>52</v>
@@ -11380,13 +11662,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1394</v>
+        <v>1372</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1357</v>
+        <v>1373</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>1395</v>
+        <v>1374</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>131</v>
@@ -11416,13 +11698,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1358</v>
+        <v>1375</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1359</v>
+        <v>1376</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>1396</v>
+        <v>1377</v>
       </c>
       <c r="F25" s="8" t="s">
         <v>131</v>
@@ -11452,13 +11734,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1391</v>
+        <v>1378</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1386</v>
+        <v>1379</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>1360</v>
+        <v>1380</v>
       </c>
       <c r="F26" s="8" t="s">
         <v>239</v>
@@ -11491,10 +11773,10 @@
         <v>748</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1361</v>
+        <v>1381</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1362</v>
+        <v>1382</v>
       </c>
       <c r="F27" s="8" t="s">
         <v>85</v>
@@ -11524,13 +11806,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1349</v>
+        <v>1363</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1363</v>
+        <v>1383</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>1351</v>
+        <v>1384</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>85</v>
@@ -11563,13 +11845,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>1364</v>
+        <v>1385</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1365</v>
+        <v>1386</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>1383</v>
+        <v>1387</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>186</v>
@@ -11599,13 +11881,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1366</v>
+        <v>1388</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1367</v>
+        <v>1389</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1377</v>
+        <v>1390</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>29</v>
@@ -11635,13 +11917,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1368</v>
+        <v>1391</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>1389</v>
+        <v>1392</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>63</v>
@@ -11674,13 +11956,13 @@
         <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>1369</v>
+        <v>1393</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1387</v>
+        <v>1394</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1388</v>
+        <v>1395</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>63</v>
@@ -11710,13 +11992,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1370</v>
+        <v>1396</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1371</v>
+        <v>1397</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>1372</v>
+        <v>1398</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>48</v>
@@ -11785,10 +12067,10 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1373</v>
+        <v>1399</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1380</v>
+        <v>1400</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>29</v>
@@ -11821,7 +12103,7 @@
         <v>18</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>1374</v>
+        <v>1401</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>1033</v>
@@ -11896,7 +12178,7 @@
         <v>426</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1375</v>
+        <v>1402</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>70</v>
@@ -12060,6 +12342,1505 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+  <dimension ref="A1:P41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="39.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="64.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0</v>
+      </c>
+      <c r="H3" s="6">
+        <v>30</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3" si="0">G3-H3</f>
+        <v>-30</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>60</v>
+      </c>
+      <c r="I4" s="3">
+        <f>G4-H4</f>
+        <v>-60</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3">
+        <v>30</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f>G5-H5</f>
+        <v>0</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>30</v>
+      </c>
+      <c r="I6" s="8">
+        <f>G6-H6</f>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1469</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>1468</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="6">
+        <v>30</v>
+      </c>
+      <c r="H7" s="6">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" ref="I7:I41" si="1">G7-H7</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="3">
+        <v>595</v>
+      </c>
+      <c r="H8" s="3">
+        <v>35</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" ref="I8" si="2">G8-H8</f>
+        <v>560</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>1366</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>1493</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>1368</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="8">
+        <v>380</v>
+      </c>
+      <c r="H9" s="8">
+        <v>30</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>1404</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>1408</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1078</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>1410</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>30</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1478</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G13" s="5">
+        <v>850</v>
+      </c>
+      <c r="H13" s="5">
+        <v>30</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J13" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>1413</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="6">
+        <v>1075</v>
+      </c>
+      <c r="H14" s="6">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="1"/>
+        <v>1050</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>1416</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="6">
+        <v>1065</v>
+      </c>
+      <c r="H15" s="6">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="1"/>
+        <v>1040</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1417</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1419</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="8">
+        <v>0</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1420</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>1421</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G17" s="8">
+        <v>0</v>
+      </c>
+      <c r="H17" s="8">
+        <v>25</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1422</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1423</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18" s="3">
+        <v>890</v>
+      </c>
+      <c r="H18" s="3">
+        <v>30</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>1425</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="3">
+        <v>380</v>
+      </c>
+      <c r="H19" s="3">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1426</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>1427</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>1428</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="8">
+        <v>0</v>
+      </c>
+      <c r="H20" s="8">
+        <v>30</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>1429</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G21" s="6">
+        <v>25</v>
+      </c>
+      <c r="H21" s="6">
+        <v>25</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>1404</v>
+      </c>
+      <c r="M21" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1431</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1432</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G22" s="3">
+        <v>1020</v>
+      </c>
+      <c r="H22" s="3">
+        <v>30</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="1"/>
+        <v>990</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1434</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1435</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>30</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1436</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1437</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>30</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G25" s="8">
+        <v>0</v>
+      </c>
+      <c r="H25" s="8">
+        <v>35</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="1"/>
+        <v>-35</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>1404</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>1440</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G26" s="5">
+        <v>600</v>
+      </c>
+      <c r="H26" s="5">
+        <v>30</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="1"/>
+        <v>570</v>
+      </c>
+      <c r="J26" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1480</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1443</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="3">
+        <v>295</v>
+      </c>
+      <c r="H27" s="3">
+        <v>25</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>1472</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>1473</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>1474</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G28" s="6">
+        <v>915</v>
+      </c>
+      <c r="H28" s="6">
+        <v>25</v>
+      </c>
+      <c r="I28" s="6">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1485</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>1487</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G29" s="3">
+        <v>1190</v>
+      </c>
+      <c r="H29" s="3">
+        <v>20</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" si="1"/>
+        <v>1170</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>1228</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>1444</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>1490</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G30" s="8">
+        <v>980</v>
+      </c>
+      <c r="H30" s="8">
+        <v>30</v>
+      </c>
+      <c r="I30" s="8">
+        <f t="shared" si="1"/>
+        <v>950</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>1447</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G31" s="8">
+        <v>380</v>
+      </c>
+      <c r="H31" s="8">
+        <v>30</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" si="1"/>
+        <v>350</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>1448</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G32" s="6">
+        <v>765</v>
+      </c>
+      <c r="H32" s="6">
+        <v>25</v>
+      </c>
+      <c r="I32" s="6">
+        <f t="shared" si="1"/>
+        <v>740</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G33" s="6">
+        <v>855</v>
+      </c>
+      <c r="H33" s="6">
+        <v>25</v>
+      </c>
+      <c r="I33" s="6">
+        <f t="shared" si="1"/>
+        <v>830</v>
+      </c>
+      <c r="J33" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1481</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G34" s="3">
+        <v>0</v>
+      </c>
+      <c r="H34" s="3">
+        <v>25</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="3">
+        <v>885</v>
+      </c>
+      <c r="H35" s="3">
+        <v>25</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="1"/>
+        <v>860</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>1454</v>
+      </c>
+      <c r="D36" s="8" t="s">
+        <v>1455</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>1456</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G36" s="8">
+        <v>695</v>
+      </c>
+      <c r="H36" s="8">
+        <v>35</v>
+      </c>
+      <c r="I36" s="8">
+        <f t="shared" si="1"/>
+        <v>660</v>
+      </c>
+      <c r="J36" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K36" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>1404</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>1492</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G37" s="8">
+        <v>820</v>
+      </c>
+      <c r="H37" s="8">
+        <v>0</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>1404</v>
+      </c>
+      <c r="M37" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>1458</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>1483</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>1484</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G38" s="3">
+        <v>915</v>
+      </c>
+      <c r="H38" s="3">
+        <v>25</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="1"/>
+        <v>890</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G39" s="8">
+        <v>980</v>
+      </c>
+      <c r="H39" s="8">
+        <v>30</v>
+      </c>
+      <c r="I39" s="8">
+        <f t="shared" si="1"/>
+        <v>950</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>1479</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>1463</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G40" s="3">
+        <v>815</v>
+      </c>
+      <c r="H40" s="3">
+        <v>25</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>1464</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>1494</v>
+      </c>
+      <c r="F41" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="G41" s="8">
+        <v>985</v>
+      </c>
+      <c r="H41" s="8">
+        <v>25</v>
+      </c>
+      <c r="I41" s="8">
+        <f t="shared" si="1"/>
+        <v>960</v>
+      </c>
+      <c r="J41" s="8" t="s">
+        <v>1406</v>
+      </c>
+      <c r="K41" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
 </file>
 

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C407264-DD13-4CF3-9CE2-CE8072A9A7D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5AF13F-AA3D-40BC-B3BC-72C65BF88C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -27,6 +27,7 @@
     <sheet name="15-05" sheetId="16" r:id="rId12"/>
     <sheet name="16-05" sheetId="17" r:id="rId13"/>
     <sheet name="18-05" sheetId="18" r:id="rId14"/>
+    <sheet name="19-05" sheetId="19" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4558" uniqueCount="1496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4793" uniqueCount="1565">
   <si>
     <t>THU 6</t>
   </si>
@@ -4263,6 +4264,9 @@
     <t>NGAY 18-5</t>
   </si>
   <si>
+    <t>SU ANH</t>
+  </si>
+  <si>
     <t>18-05-2026</t>
   </si>
   <si>
@@ -4272,15 +4276,30 @@
     <t>AT 18-05</t>
   </si>
   <si>
+    <t>Hong Nho + NGUYỄN THỊ DIỄM CHI</t>
+  </si>
+  <si>
+    <t>29/7 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>HD021621</t>
+  </si>
+  <si>
     <t>Heng Roza (EV38382)</t>
   </si>
   <si>
+    <t>HD020691</t>
+  </si>
+  <si>
     <t>Gia Huy nhận của ELIS NGUYỄN ( singapore)</t>
   </si>
   <si>
     <t>HD021334</t>
   </si>
   <si>
+    <t>2/11 Đường Thiên Phước, Phường 9</t>
+  </si>
+  <si>
     <t>HD021855</t>
   </si>
   <si>
@@ -4290,6 +4309,9 @@
     <t>HD021747</t>
   </si>
   <si>
+    <t>56/7 đường Tân Hoà 2 phường Hiệp Phú</t>
+  </si>
+  <si>
     <t>Ngọc - fb Naila Unner</t>
   </si>
   <si>
@@ -4344,12 +4366,18 @@
     <t>HD021842</t>
   </si>
   <si>
+    <t>222 pasteur, phường xuân hòa</t>
+  </si>
+  <si>
     <t>Hoàng Trâm Anh</t>
   </si>
   <si>
     <t>HD021810</t>
   </si>
   <si>
+    <t>11 Nguyễn Bá Huân phường thảo điền</t>
+  </si>
+  <si>
     <t>HSM RIDA CHUON</t>
   </si>
   <si>
@@ -4368,6 +4396,12 @@
     <t>38 Đường 6 Linh Chiếu</t>
   </si>
   <si>
+    <t>Nga Còi</t>
+  </si>
+  <si>
+    <t>Sửa xe Anh Sơn, liên ấp 2,3,4 Vĩnh Lộc A</t>
+  </si>
+  <si>
     <t>Hợp Vũ</t>
   </si>
   <si>
@@ -4377,15 +4411,39 @@
     <t>2A Phan Chu Trinh, P Hiệp Phú</t>
   </si>
   <si>
+    <t>như fb Đặng Tố Trinh</t>
+  </si>
+  <si>
     <t>HD021866</t>
   </si>
   <si>
     <t>Đối diện 110/42 đường số 5 phường 17</t>
   </si>
   <si>
+    <t>Thinh HB</t>
+  </si>
+  <si>
+    <t>HD021608</t>
+  </si>
+  <si>
+    <t>17 cô giang, phường cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>Nguyễn Thảo Uyên</t>
+  </si>
+  <si>
+    <t>HD021746</t>
+  </si>
+  <si>
+    <t>15/32/56 võ duy ninh p22</t>
+  </si>
+  <si>
     <t>HD021418</t>
   </si>
   <si>
+    <t>Central premium lock A</t>
+  </si>
+  <si>
     <t>Ái Nương</t>
   </si>
   <si>
@@ -4401,9 +4459,24 @@
     <t>HD021600</t>
   </si>
   <si>
+    <t>177 Nguyễn Đình Chiểu, p. Xuân Hòa</t>
+  </si>
+  <si>
+    <t>Tô Tô</t>
+  </si>
+  <si>
+    <t>HD021603</t>
+  </si>
+  <si>
+    <t>46 Lê Thị Riêng, phường Bến Thành</t>
+  </si>
+  <si>
     <t>HD021539</t>
   </si>
   <si>
+    <t>129/34 Nguyễn Văn Công, P. 3</t>
+  </si>
+  <si>
     <t>MC Phương Nhi</t>
   </si>
   <si>
@@ -4422,12 +4495,24 @@
     <t>Số 4 đường số 22 kdc bình hưng</t>
   </si>
   <si>
+    <t>Chị Bích Huyền</t>
+  </si>
+  <si>
     <t>HD021775</t>
   </si>
   <si>
+    <t>số 4 đường số 22 kdc bình hưng</t>
+  </si>
+  <si>
     <t>Ngân Ngân</t>
   </si>
   <si>
+    <t>HD021620</t>
+  </si>
+  <si>
+    <t>74B/148 thống nhất p15</t>
+  </si>
+  <si>
     <t>Phuong Nguyen</t>
   </si>
   <si>
@@ -4437,6 +4522,9 @@
     <t>Eco green toà I, HR30710, 39 Nguyễn Văn linh</t>
   </si>
   <si>
+    <t>Vân Thuỳ</t>
+  </si>
+  <si>
     <t>HD021612</t>
   </si>
   <si>
@@ -4449,94 +4537,214 @@
     <t>HD021534</t>
   </si>
   <si>
-    <t>222 pasteur, phường xuân hòa</t>
-  </si>
-  <si>
-    <t>2/11 Đường Thiên Phước, Phường 9</t>
-  </si>
-  <si>
-    <t>29/7 Yên Thế, Phường 2</t>
-  </si>
-  <si>
-    <t>Hong Nho + NGUYỄN THỊ DIỄM CHI</t>
-  </si>
-  <si>
-    <t>SU ANH</t>
-  </si>
-  <si>
-    <t>177 Nguyễn Đình Chiểu, p. Xuân Hòa</t>
-  </si>
-  <si>
-    <t>Thinh HB</t>
-  </si>
-  <si>
-    <t>HD021608</t>
-  </si>
-  <si>
-    <t>17 cô giang, phường cầu ông lãnh</t>
-  </si>
-  <si>
-    <t>Tô Tô</t>
-  </si>
-  <si>
-    <t>HD021603</t>
-  </si>
-  <si>
-    <t>46 Lê Thị Riêng, phường Bến Thành</t>
-  </si>
-  <si>
-    <t>56/7 đường Tân Hoà 2 phường Hiệp Phú</t>
-  </si>
-  <si>
-    <t>Vân Thuỳ</t>
-  </si>
-  <si>
-    <t>như fb Đặng Tố Trinh</t>
-  </si>
-  <si>
-    <t>129/34 Nguyễn Văn Công, P. 3</t>
-  </si>
-  <si>
-    <t>11 Nguyễn Bá Huân phường thảo điền</t>
-  </si>
-  <si>
-    <t>HD021620</t>
-  </si>
-  <si>
-    <t>74B/148 thống nhất p15</t>
-  </si>
-  <si>
-    <t>Nguyễn Thảo Uyên</t>
-  </si>
-  <si>
-    <t>HD021746</t>
-  </si>
-  <si>
-    <t>15/32/56 võ duy ninh p22</t>
-  </si>
-  <si>
-    <t>Nga Còi</t>
-  </si>
-  <si>
-    <t>Sửa xe Anh Sơn, liên ấp 2,3,4 Vĩnh Lộc A</t>
-  </si>
-  <si>
-    <t>Central premium lock A</t>
-  </si>
-  <si>
-    <t>Chị Bích Huyền</t>
-  </si>
-  <si>
-    <t>số 4 đường số 22 kdc bình hưng</t>
-  </si>
-  <si>
-    <t>HD021621</t>
-  </si>
-  <si>
     <t>360 lạc long quân phường 5 (phường hòa bình)</t>
   </si>
   <si>
-    <t>HD020691</t>
+    <t>NGAY 19-5</t>
+  </si>
+  <si>
+    <t>Nguyễn Trương Phương Oanh</t>
+  </si>
+  <si>
+    <t>HD021780</t>
+  </si>
+  <si>
+    <t>19-05-2026</t>
+  </si>
+  <si>
+    <t>HD021999</t>
+  </si>
+  <si>
+    <t>AT 19-05</t>
+  </si>
+  <si>
+    <t>Bảo Ngân</t>
+  </si>
+  <si>
+    <t>HD021981</t>
+  </si>
+  <si>
+    <t>62 đường 36, Khu đô thị Vạn Phúc</t>
+  </si>
+  <si>
+    <t>YẾN</t>
+  </si>
+  <si>
+    <t>HD022130</t>
+  </si>
+  <si>
+    <t>HD021937</t>
+  </si>
+  <si>
+    <t>HD021909</t>
+  </si>
+  <si>
+    <t>HD022145</t>
+  </si>
+  <si>
+    <t>Trang Gpe / Wang Yu Hua</t>
+  </si>
+  <si>
+    <t>HD021970</t>
+  </si>
+  <si>
+    <t>Thiều Phương Nhi</t>
+  </si>
+  <si>
+    <t>HD022153</t>
+  </si>
+  <si>
+    <t>115 Phan Huy Thực, P.Tân Hưng</t>
+  </si>
+  <si>
+    <t>HD021917</t>
+  </si>
+  <si>
+    <t>Khả Hân</t>
+  </si>
+  <si>
+    <t>HD021776</t>
+  </si>
+  <si>
+    <t>10 Tạ Hiện Cát Lái</t>
+  </si>
+  <si>
+    <t>HD022106</t>
+  </si>
+  <si>
+    <t>Nguyễn Võ Thụy Hương (Hoàng Ngân)</t>
+  </si>
+  <si>
+    <t>HD022099</t>
+  </si>
+  <si>
+    <t>Châu Nguyễn</t>
+  </si>
+  <si>
+    <t>HD021967</t>
+  </si>
+  <si>
+    <t>chung cu eco green block H</t>
+  </si>
+  <si>
+    <t>Hiền Hiền</t>
+  </si>
+  <si>
+    <t>HD022103</t>
+  </si>
+  <si>
+    <t>163/25/42 Tô Hiến Thành p13</t>
+  </si>
+  <si>
+    <t>HD022152</t>
+  </si>
+  <si>
+    <t>362/26 lê văn lương, tân hưng</t>
+  </si>
+  <si>
+    <t>Ngọc Trang</t>
+  </si>
+  <si>
+    <t>HD022158</t>
+  </si>
+  <si>
+    <t>Foxshop 28 Lê Văn Duyệt, P1</t>
+  </si>
+  <si>
+    <t>HD021846</t>
+  </si>
+  <si>
+    <t>Ivy Tran</t>
+  </si>
+  <si>
+    <t>HD021976</t>
+  </si>
+  <si>
+    <t>128/3 Nguyễn Sơn, Phú Thọ Hoà</t>
+  </si>
+  <si>
+    <t>HD022101</t>
+  </si>
+  <si>
+    <t>khun leang 092559972</t>
+  </si>
+  <si>
+    <t>HD021974</t>
+  </si>
+  <si>
+    <t>nhà xe khải nam</t>
+  </si>
+  <si>
+    <t>Ivy Nguyen</t>
+  </si>
+  <si>
+    <t>HD022104</t>
+  </si>
+  <si>
+    <t>296 gia phú p1</t>
+  </si>
+  <si>
+    <t>BELLA TRẦN</t>
+  </si>
+  <si>
+    <t>66đường 17 p10</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc Thương</t>
+  </si>
+  <si>
+    <t>HD022114</t>
+  </si>
+  <si>
+    <t>23/53 Nơ Trang Long, p7</t>
+  </si>
+  <si>
+    <t>Số 192 Trần Bá Giao, Phường 5</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thương Hoài</t>
+  </si>
+  <si>
+    <t>32/4/17 khu phố 3, đường 21, phường Cát Lái</t>
+  </si>
+  <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
+    <t>Số 21 đường 10, khu Khang Điền, P.Phước Long B</t>
+  </si>
+  <si>
+    <t>LEMONA</t>
+  </si>
+  <si>
+    <t>NT Hải Yến</t>
+  </si>
+  <si>
+    <t>123 khu dân cư Tân Tiến, Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>GENY</t>
+  </si>
+  <si>
+    <t>B12 Đ. Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>chung cư botanica premier block C2 Hồng Hà</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Hà Vy</t>
+  </si>
+  <si>
+    <t>30/8 trịnh đình thảo p. Hòa Thạnh</t>
+  </si>
+  <si>
+    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà</t>
+  </si>
+  <si>
+    <t>Eny Nguyen</t>
+  </si>
+  <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phú, phường Tân Tạo</t>
   </si>
 </sst>
 </file>
@@ -12350,10 +12558,12 @@
   <dimension ref="A1:P41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="39.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="64.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -12428,7 +12638,7 @@
         <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1470</v>
+        <v>1404</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>440</v>
@@ -12443,7 +12653,7 @@
         <v>30</v>
       </c>
       <c r="I3" s="6">
-        <f t="shared" ref="I3" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I41" si="0">G3-H3</f>
         <v>-30</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -12453,7 +12663,7 @@
         <v>24</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12464,7 +12674,7 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>263</v>
@@ -12479,7 +12689,7 @@
         <v>60</v>
       </c>
       <c r="I4" s="3">
-        <f>G4-H4</f>
+        <f t="shared" si="0"/>
         <v>-60</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -12489,7 +12699,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12515,7 +12725,7 @@
         <v>30</v>
       </c>
       <c r="I5" s="3">
-        <f>G5-H5</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -12525,7 +12735,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12551,17 +12761,17 @@
         <v>30</v>
       </c>
       <c r="I6" s="8">
-        <f>G6-H6</f>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12572,10 +12782,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1469</v>
+        <v>1408</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1468</v>
+        <v>1409</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>102</v>
@@ -12587,7 +12797,7 @@
         <v>30</v>
       </c>
       <c r="I7" s="6">
-        <f t="shared" ref="I7:I41" si="1">G7-H7</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J7" s="6" t="s">
@@ -12597,7 +12807,7 @@
         <v>24</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12623,7 +12833,7 @@
         <v>35</v>
       </c>
       <c r="I8" s="3">
-        <f t="shared" ref="I8" si="2">G8-H8</f>
+        <f t="shared" si="0"/>
         <v>560</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -12633,7 +12843,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12644,7 +12854,7 @@
         <v>1366</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1493</v>
+        <v>1410</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>1368</v>
@@ -12659,17 +12869,17 @@
         <v>30</v>
       </c>
       <c r="I9" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>138</v>
@@ -12680,10 +12890,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1407</v>
+        <v>1411</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1495</v>
+        <v>1412</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>763</v>
@@ -12698,17 +12908,17 @@
         <v>30</v>
       </c>
       <c r="I10" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12716,13 +12926,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1408</v>
+        <v>1413</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1467</v>
+        <v>1415</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>102</v>
@@ -12734,7 +12944,7 @@
         <v>25</v>
       </c>
       <c r="I11" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J11" s="6" t="s">
@@ -12744,7 +12954,7 @@
         <v>24</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12755,7 +12965,7 @@
         <v>1078</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1410</v>
+        <v>1416</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>1080</v>
@@ -12770,17 +12980,17 @@
         <v>30</v>
       </c>
       <c r="I12" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -12788,13 +12998,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>1411</v>
+        <v>1417</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>1412</v>
+        <v>1418</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>1478</v>
+        <v>1419</v>
       </c>
       <c r="F13" s="10" t="s">
         <v>149</v>
@@ -12806,7 +13016,7 @@
         <v>30</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J13" s="5" t="s">
@@ -12816,7 +13026,7 @@
         <v>24</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12824,13 +13034,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1413</v>
+        <v>1420</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1414</v>
+        <v>1421</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1415</v>
+        <v>1422</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>186</v>
@@ -12842,7 +13052,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1050</v>
       </c>
       <c r="J14" s="6" t="s">
@@ -12852,7 +13062,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -12863,7 +13073,7 @@
         <v>537</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1416</v>
+        <v>1423</v>
       </c>
       <c r="E15" s="6" t="s">
         <v>539</v>
@@ -12878,7 +13088,7 @@
         <v>25</v>
       </c>
       <c r="I15" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1040</v>
       </c>
       <c r="J15" s="6" t="s">
@@ -12888,7 +13098,7 @@
         <v>24</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12896,13 +13106,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1417</v>
+        <v>1424</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1418</v>
+        <v>1425</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>1419</v>
+        <v>1426</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>131</v>
@@ -12914,17 +13124,17 @@
         <v>30</v>
       </c>
       <c r="I16" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="17" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -12932,10 +13142,10 @@
         <v>18</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>1420</v>
+        <v>1427</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1421</v>
+        <v>1428</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>630</v>
@@ -12950,17 +13160,17 @@
         <v>25</v>
       </c>
       <c r="I17" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K17" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="18" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12968,13 +13178,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>1422</v>
+        <v>1429</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>1423</v>
+        <v>1430</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>1424</v>
+        <v>1431</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>48</v>
@@ -12986,7 +13196,7 @@
         <v>30</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>860</v>
       </c>
       <c r="J18" s="3" t="s">
@@ -12996,7 +13206,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="19" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13007,7 +13217,7 @@
         <v>966</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>1425</v>
+        <v>1432</v>
       </c>
       <c r="E19" s="3" t="s">
         <v>968</v>
@@ -13022,7 +13232,7 @@
         <v>30</v>
       </c>
       <c r="I19" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J19" s="3" t="s">
@@ -13032,7 +13242,7 @@
         <v>24</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="20" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13040,13 +13250,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>1426</v>
+        <v>1433</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>1427</v>
+        <v>1434</v>
       </c>
       <c r="E20" s="8" t="s">
-        <v>1428</v>
+        <v>1435</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>22</v>
@@ -13058,17 +13268,17 @@
         <v>30</v>
       </c>
       <c r="I20" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J20" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K20" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="21" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -13076,13 +13286,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1429</v>
+        <v>1436</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1430</v>
+        <v>1437</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1466</v>
+        <v>1438</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>98</v>
@@ -13094,7 +13304,7 @@
         <v>25</v>
       </c>
       <c r="I21" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -13104,7 +13314,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>138</v>
@@ -13115,13 +13325,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>1431</v>
+        <v>1439</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>1432</v>
+        <v>1440</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>1482</v>
+        <v>1441</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>48</v>
@@ -13133,7 +13343,7 @@
         <v>30</v>
       </c>
       <c r="I22" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>990</v>
       </c>
       <c r="J22" s="3" t="s">
@@ -13143,7 +13353,7 @@
         <v>24</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="23" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13151,13 +13361,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1433</v>
+        <v>1442</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1434</v>
+        <v>1443</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>1435</v>
+        <v>1444</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>22</v>
@@ -13169,17 +13379,17 @@
         <v>30</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="24" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13187,13 +13397,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1436</v>
+        <v>1445</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1437</v>
+        <v>1446</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1438</v>
+        <v>1447</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>77</v>
@@ -13205,7 +13415,7 @@
         <v>30</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-30</v>
       </c>
       <c r="J24" s="3" t="s">
@@ -13215,7 +13425,7 @@
         <v>24</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="25" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13223,10 +13433,10 @@
         <v>18</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1488</v>
+        <v>1448</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>1489</v>
+        <v>1449</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>52</v>
@@ -13238,17 +13448,17 @@
         <v>35</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-35</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="M25" s="8" t="s">
         <v>138</v>
@@ -13259,13 +13469,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>1439</v>
+        <v>1450</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>1440</v>
+        <v>1451</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>1441</v>
+        <v>1452</v>
       </c>
       <c r="F26" s="10" t="s">
         <v>149</v>
@@ -13277,7 +13487,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>570</v>
       </c>
       <c r="J26" s="5" t="s">
@@ -13287,7 +13497,7 @@
         <v>24</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="27" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13295,13 +13505,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1480</v>
+        <v>1453</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>1442</v>
+        <v>1454</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1443</v>
+        <v>1455</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>70</v>
@@ -13313,7 +13523,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>270</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -13323,7 +13533,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="M27" s="3" t="s">
         <v>138</v>
@@ -13334,13 +13544,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>1472</v>
+        <v>1456</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1473</v>
+        <v>1457</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>1474</v>
+        <v>1458</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>63</v>
@@ -13352,7 +13562,7 @@
         <v>25</v>
       </c>
       <c r="I28" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J28" s="6" t="s">
@@ -13362,7 +13572,7 @@
         <v>24</v>
       </c>
       <c r="L28" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="29" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13370,13 +13580,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1485</v>
+        <v>1459</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>1486</v>
+        <v>1460</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>1487</v>
+        <v>1461</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>81</v>
@@ -13388,7 +13598,7 @@
         <v>20</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1170</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -13398,7 +13608,7 @@
         <v>24</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="30" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13409,10 +13619,10 @@
         <v>1228</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>1444</v>
+        <v>1462</v>
       </c>
       <c r="E30" s="8" t="s">
-        <v>1490</v>
+        <v>1463</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>41</v>
@@ -13424,17 +13634,17 @@
         <v>30</v>
       </c>
       <c r="I30" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>950</v>
       </c>
       <c r="J30" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K30" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L30" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="31" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13442,13 +13652,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1445</v>
+        <v>1464</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1446</v>
+        <v>1465</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>1447</v>
+        <v>1466</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>41</v>
@@ -13460,17 +13670,17 @@
         <v>30</v>
       </c>
       <c r="I31" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>350</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="32" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -13478,13 +13688,13 @@
         <v>18</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>1448</v>
+        <v>1467</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1449</v>
+        <v>1468</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>1471</v>
+        <v>1469</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>98</v>
@@ -13496,7 +13706,7 @@
         <v>25</v>
       </c>
       <c r="I32" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>740</v>
       </c>
       <c r="J32" s="6" t="s">
@@ -13506,7 +13716,7 @@
         <v>24</v>
       </c>
       <c r="L32" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="33" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -13514,13 +13724,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>63</v>
@@ -13532,7 +13742,7 @@
         <v>25</v>
       </c>
       <c r="I33" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>830</v>
       </c>
       <c r="J33" s="6" t="s">
@@ -13542,7 +13752,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="6" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="34" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13553,10 +13763,10 @@
         <v>458</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1450</v>
+        <v>1473</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1481</v>
+        <v>1474</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>70</v>
@@ -13568,7 +13778,7 @@
         <v>25</v>
       </c>
       <c r="I34" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>-25</v>
       </c>
       <c r="J34" s="3" t="s">
@@ -13578,7 +13788,7 @@
         <v>24</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="35" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13586,13 +13796,13 @@
         <v>18</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>1451</v>
+        <v>1475</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>1452</v>
+        <v>1476</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>1453</v>
+        <v>1477</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>70</v>
@@ -13604,7 +13814,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>860</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -13614,7 +13824,7 @@
         <v>24</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="36" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13622,13 +13832,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>1454</v>
+        <v>1478</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>1455</v>
+        <v>1479</v>
       </c>
       <c r="E36" s="8" t="s">
-        <v>1456</v>
+        <v>1480</v>
       </c>
       <c r="F36" s="9" t="s">
         <v>52</v>
@@ -13640,17 +13850,17 @@
         <v>35</v>
       </c>
       <c r="I36" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>660</v>
       </c>
       <c r="J36" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K36" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L36" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="M36" s="8" t="s">
         <v>288</v>
@@ -13661,13 +13871,13 @@
         <v>18</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>1491</v>
+        <v>1481</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>1457</v>
+        <v>1482</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1492</v>
+        <v>1483</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>52</v>
@@ -13679,17 +13889,17 @@
         <v>0</v>
       </c>
       <c r="I37" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>820</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K37" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="M37" s="8" t="s">
         <v>288</v>
@@ -13700,13 +13910,13 @@
         <v>18</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>1458</v>
+        <v>1484</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>70</v>
@@ -13718,7 +13928,7 @@
         <v>25</v>
       </c>
       <c r="I38" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>890</v>
       </c>
       <c r="J38" s="3" t="s">
@@ -13728,7 +13938,7 @@
         <v>24</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="39" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13736,13 +13946,13 @@
         <v>18</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>1459</v>
+        <v>1487</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>1460</v>
+        <v>1488</v>
       </c>
       <c r="E39" s="8" t="s">
-        <v>1461</v>
+        <v>1489</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>131</v>
@@ -13754,17 +13964,17 @@
         <v>30</v>
       </c>
       <c r="I39" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>950</v>
       </c>
       <c r="J39" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K39" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L39" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="40" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -13772,13 +13982,13 @@
         <v>18</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>1479</v>
+        <v>1490</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>1462</v>
+        <v>1491</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>1463</v>
+        <v>1492</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>70</v>
@@ -13790,7 +14000,7 @@
         <v>25</v>
       </c>
       <c r="I40" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>790</v>
       </c>
       <c r="J40" s="3" t="s">
@@ -13800,7 +14010,7 @@
         <v>24</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="41" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -13808,13 +14018,13 @@
         <v>18</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>1464</v>
+        <v>1493</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>1465</v>
+        <v>1494</v>
       </c>
       <c r="E41" s="8" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>239</v>
@@ -13826,17 +14036,1071 @@
         <v>25</v>
       </c>
       <c r="I41" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>960</v>
       </c>
       <c r="J41" s="8" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L41" s="8" t="s">
-        <v>1404</v>
+        <v>1405</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+  <dimension ref="A1:P29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <v>-20</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>1500</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>390</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G4" s="8">
+        <v>735</v>
+      </c>
+      <c r="H4" s="8">
+        <v>35</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1020</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G6" s="5">
+        <v>830</v>
+      </c>
+      <c r="H6" s="5">
+        <v>30</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="0"/>
+        <v>800</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="5" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1562</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="8">
+        <v>985</v>
+      </c>
+      <c r="H7" s="8">
+        <v>25</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>1508</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G8" s="8">
+        <v>860</v>
+      </c>
+      <c r="H8" s="8">
+        <v>30</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G9" s="6">
+        <v>1015</v>
+      </c>
+      <c r="H9" s="6">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1510</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="3">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>25</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>1514</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="8">
+        <v>850</v>
+      </c>
+      <c r="H11" s="8">
+        <v>30</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1560</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G12" s="8">
+        <v>1115</v>
+      </c>
+      <c r="H12" s="8">
+        <v>25</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1020</v>
+      </c>
+      <c r="H13" s="3">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>25</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1522</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="8">
+        <v>850</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1548</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>20</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1525</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1665</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>1640</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1563</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>1529</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G19" s="8">
+        <v>380</v>
+      </c>
+      <c r="H19" s="8">
+        <v>30</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1530</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>20</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>745</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>747</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1420</v>
+      </c>
+      <c r="H21" s="3">
+        <v>20</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1534</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1535</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1536</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>25</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>624</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>626</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="6">
+        <v>25</v>
+      </c>
+      <c r="H23" s="6">
+        <v>25</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>1499</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>1538</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>1539</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F24" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <v>25</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>1541</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>1543</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="8">
+        <v>765</v>
+      </c>
+      <c r="H25" s="8">
+        <v>25</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>1544</v>
+      </c>
+      <c r="E26" s="8" t="s">
+        <v>1545</v>
+      </c>
+      <c r="F26" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G26" s="8">
+        <v>40</v>
+      </c>
+      <c r="H26" s="8">
+        <v>40</v>
+      </c>
+      <c r="I26" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="8" t="s">
+        <v>1501</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>1557</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G27" s="6">
+        <v>0</v>
+      </c>
+      <c r="H27" s="6">
+        <v>50</v>
+      </c>
+      <c r="I27" s="6">
+        <f t="shared" si="0"/>
+        <v>-50</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>60</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>60</v>
+      </c>
+      <c r="I29" s="3">
+        <f t="shared" ref="I29" si="1">G29-H29</f>
+        <v>-60</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>1499</v>
       </c>
     </row>
   </sheetData>

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F5AF13F-AA3D-40BC-B3BC-72C65BF88C92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3870DF-F153-4CC6-8F1F-23A7C7D4D5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -28,6 +28,7 @@
     <sheet name="16-05" sheetId="17" r:id="rId13"/>
     <sheet name="18-05" sheetId="18" r:id="rId14"/>
     <sheet name="19-05" sheetId="19" r:id="rId15"/>
+    <sheet name="20-05" sheetId="20" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4793" uniqueCount="1565">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5075" uniqueCount="1642">
   <si>
     <t>THU 6</t>
   </si>
@@ -4549,6 +4550,9 @@
     <t>HD021780</t>
   </si>
   <si>
+    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
+  </si>
+  <si>
     <t>19-05-2026</t>
   </si>
   <si>
@@ -4573,21 +4577,36 @@
     <t>HD022130</t>
   </si>
   <si>
+    <t>Số 21 đường 10, khu Khang Điền, P.Phước Long B</t>
+  </si>
+  <si>
     <t>HD021937</t>
   </si>
   <si>
+    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà</t>
+  </si>
+  <si>
     <t>HD021909</t>
   </si>
   <si>
+    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phú, phường Tân Tạo</t>
+  </si>
+  <si>
     <t>HD022145</t>
   </si>
   <si>
+    <t>chung cư botanica premier block C2 Hồng Hà</t>
+  </si>
+  <si>
     <t>Trang Gpe / Wang Yu Hua</t>
   </si>
   <si>
     <t>HD021970</t>
   </si>
   <si>
+    <t>Số 192 Trần Bá Giao, Phường 5</t>
+  </si>
+  <si>
     <t>Thiều Phương Nhi</t>
   </si>
   <si>
@@ -4597,9 +4616,15 @@
     <t>115 Phan Huy Thực, P.Tân Hưng</t>
   </si>
   <si>
+    <t>Nguyễn Thị Hà Vy</t>
+  </si>
+  <si>
     <t>HD021917</t>
   </si>
   <si>
+    <t>30/8 trịnh đình thảo p. Hòa Thạnh</t>
+  </si>
+  <si>
     <t>Khả Hân</t>
   </si>
   <si>
@@ -4609,9 +4634,15 @@
     <t>10 Tạ Hiện Cát Lái</t>
   </si>
   <si>
+    <t>Nguyễn Thị Thương Hoài</t>
+  </si>
+  <si>
     <t>HD022106</t>
   </si>
   <si>
+    <t>32/4/17 khu phố 3, đường 21, phường Cát Lái</t>
+  </si>
+  <si>
     <t>Nguyễn Võ Thụy Hương (Hoàng Ngân)</t>
   </si>
   <si>
@@ -4627,6 +4658,15 @@
     <t>chung cu eco green block H</t>
   </si>
   <si>
+    <t>Phạm Ngọc Thương</t>
+  </si>
+  <si>
+    <t>HD022114</t>
+  </si>
+  <si>
+    <t>23/53 Nơ Trang Long, p7</t>
+  </si>
+  <si>
     <t>Hiền Hiền</t>
   </si>
   <si>
@@ -4636,6 +4676,9 @@
     <t>163/25/42 Tô Hiến Thành p13</t>
   </si>
   <si>
+    <t>Eny Nguyen</t>
+  </si>
+  <si>
     <t>HD022152</t>
   </si>
   <si>
@@ -4690,61 +4733,250 @@
     <t>66đường 17 p10</t>
   </si>
   <si>
-    <t>Phạm Ngọc Thương</t>
-  </si>
-  <si>
-    <t>HD022114</t>
-  </si>
-  <si>
-    <t>23/53 Nơ Trang Long, p7</t>
-  </si>
-  <si>
-    <t>Số 192 Trần Bá Giao, Phường 5</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Thương Hoài</t>
-  </si>
-  <si>
-    <t>32/4/17 khu phố 3, đường 21, phường Cát Lái</t>
-  </si>
-  <si>
-    <t>125/42/2 Bùi Đình Tuý, phường 14</t>
-  </si>
-  <si>
-    <t>Số 21 đường 10, khu Khang Điền, P.Phước Long B</t>
+    <t>GENY</t>
+  </si>
+  <si>
+    <t>B12 Đ. Bạch Đằng, Phường 2</t>
+  </si>
+  <si>
+    <t>NT Hải Yến</t>
+  </si>
+  <si>
+    <t>123 khu dân cư Tân Tiến, Tân Thới Hiệp</t>
   </si>
   <si>
     <t>LEMONA</t>
   </si>
   <si>
-    <t>NT Hải Yến</t>
-  </si>
-  <si>
-    <t>123 khu dân cư Tân Tiến, Tân Thới Hiệp</t>
-  </si>
-  <si>
-    <t>GENY</t>
-  </si>
-  <si>
-    <t>B12 Đ. Bạch Đằng, Phường 2</t>
-  </si>
-  <si>
-    <t>chung cư botanica premier block C2 Hồng Hà</t>
-  </si>
-  <si>
-    <t>Nguyễn Thị Hà Vy</t>
-  </si>
-  <si>
-    <t>30/8 trịnh đình thảo p. Hòa Thạnh</t>
-  </si>
-  <si>
-    <t>Trường Ruby Hồng Ngọc, số 4 Lê Quát, Phường Tân Thới Hoà</t>
-  </si>
-  <si>
-    <t>Eny Nguyen</t>
-  </si>
-  <si>
-    <t>Chung cư Tecco, block C, đường Nguyễn Cửu Phú, phường Tân Tạo</t>
+    <t>NGAY 20-5</t>
+  </si>
+  <si>
+    <t>AT 20-05</t>
+  </si>
+  <si>
+    <t>20-05-2026</t>
+  </si>
+  <si>
+    <t>Jess-9244</t>
+  </si>
+  <si>
+    <t>VICKY TRẦN</t>
+  </si>
+  <si>
+    <t>hsu_myat to</t>
+  </si>
+  <si>
+    <t>Bé Hiền - fb Yudy Phạm</t>
+  </si>
+  <si>
+    <t>HD022410</t>
+  </si>
+  <si>
+    <t>336/20 nguyễn văn luông p12</t>
+  </si>
+  <si>
+    <t>Trần Lê Trâm Anh</t>
+  </si>
+  <si>
+    <t>HD022426</t>
+  </si>
+  <si>
+    <t>179/13A hoà bình</t>
+  </si>
+  <si>
+    <t>Mr Quốc - VTS-64591HCR</t>
+  </si>
+  <si>
+    <t>HD022211</t>
+  </si>
+  <si>
+    <t>HD022200</t>
+  </si>
+  <si>
+    <t>Vincom đồng khởi, 45 lý tự trọng, căn hộ 2604</t>
+  </si>
+  <si>
+    <t>Thanh Yến</t>
+  </si>
+  <si>
+    <t>HD022266</t>
+  </si>
+  <si>
+    <t>HƯƠNG</t>
+  </si>
+  <si>
+    <t>HD022382</t>
+  </si>
+  <si>
+    <t>Vận</t>
+  </si>
+  <si>
+    <t>HD022293</t>
+  </si>
+  <si>
+    <t>HD022279</t>
+  </si>
+  <si>
+    <t>Ý nhi</t>
+  </si>
+  <si>
+    <t>HD022414</t>
+  </si>
+  <si>
+    <t>53 phạm ngọc thạch p6</t>
+  </si>
+  <si>
+    <t>CUS19950/pelpanhaketya</t>
+  </si>
+  <si>
+    <t>HD022206</t>
+  </si>
+  <si>
+    <t>270B Lý thường kiệt, khu phố 1, Phường 6</t>
+  </si>
+  <si>
+    <t>Alice Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022396</t>
+  </si>
+  <si>
+    <t>Amsumalin Abu</t>
+  </si>
+  <si>
+    <t>HD022399</t>
+  </si>
+  <si>
+    <t>03 trương quốc dung p8</t>
+  </si>
+  <si>
+    <t>HD022286</t>
+  </si>
+  <si>
+    <t>HD022377</t>
+  </si>
+  <si>
+    <t>50/26 thanh xuân 24 thới an</t>
+  </si>
+  <si>
+    <t>HD022240</t>
+  </si>
+  <si>
+    <t>Mỹ Phượng</t>
+  </si>
+  <si>
+    <t>HD022263</t>
+  </si>
+  <si>
+    <t>Huyentran Nguyen</t>
+  </si>
+  <si>
+    <t>HD022374</t>
+  </si>
+  <si>
+    <t>86-88 pasteur</t>
+  </si>
+  <si>
+    <t>linh</t>
+  </si>
+  <si>
+    <t>HD022244</t>
+  </si>
+  <si>
+    <t>358/2/2 cmt8</t>
+  </si>
+  <si>
+    <t>Any</t>
+  </si>
+  <si>
+    <t>HD022412</t>
+  </si>
+  <si>
+    <t>HD022275</t>
+  </si>
+  <si>
+    <t>HD022267</t>
+  </si>
+  <si>
+    <t>HD022402</t>
+  </si>
+  <si>
+    <t>Thương</t>
+  </si>
+  <si>
+    <t>HD022196</t>
+  </si>
+  <si>
+    <t>Moon Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022375</t>
+  </si>
+  <si>
+    <t>ms Linh</t>
+  </si>
+  <si>
+    <t>141A đường số 1 phường Thông Tây Hội</t>
+  </si>
+  <si>
+    <t>Đắc Hội Express 127/17 bình lợi p13</t>
+  </si>
+  <si>
+    <t>275/14B1 Dạng Nguyên Cẩn, Phường Phú Lâm</t>
+  </si>
+  <si>
+    <t>179/13A hoà bình Phường Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Tháp RS6, chung cư Richstar 2, số 239 Hoà Bình, phường Phú Thạnh</t>
+  </si>
+  <si>
+    <t>1414 huỳnh tấn phát p phú mỹ</t>
+  </si>
+  <si>
+    <t>nguyen lý</t>
+  </si>
+  <si>
+    <t>62/7h ấp 3 xã xuaabn thơi thượng</t>
+  </si>
+  <si>
+    <t>101 đông hưng thuận42 phường tân hưng thuận</t>
+  </si>
+  <si>
+    <t>Lyly My</t>
+  </si>
+  <si>
+    <t>Ngoc_Ann tiktok gingeri 16:39</t>
+  </si>
+  <si>
+    <t>HD022381</t>
+  </si>
+  <si>
+    <t>1/7 nguyễn văn yên tân thới hoà</t>
+  </si>
+  <si>
+    <t>188/4 đường thới an 16 phường thới an</t>
+  </si>
+  <si>
+    <t>16 kim ngân, khu dân cư phong phu 4, xã phong phú</t>
+  </si>
+  <si>
+    <t>7g đường số 8 tân hưng</t>
+  </si>
+  <si>
+    <t>181 đường số 79 phường tân quy</t>
+  </si>
+  <si>
+    <t>HD022255</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building Số G5, Đường C22, Phường 12</t>
+  </si>
+  <si>
+    <t>HD022406</t>
+  </si>
+  <si>
+    <t>2A/14, Nguyễn Thị Minh Khai, P. Đakao</t>
   </si>
 </sst>
 </file>
@@ -14059,10 +14291,12 @@
   <dimension ref="A1:P29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -14139,7 +14373,7 @@
         <v>1498</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>1552</v>
+        <v>1499</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>81</v>
@@ -14151,7 +14385,7 @@
         <v>20</v>
       </c>
       <c r="I3" s="3">
-        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I29" si="0">G3-H3</f>
         <v>-20</v>
       </c>
       <c r="J3" s="3" t="s">
@@ -14161,7 +14395,7 @@
         <v>24</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14172,7 +14406,7 @@
         <v>388</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="E4" s="8" t="s">
         <v>390</v>
@@ -14191,13 +14425,13 @@
         <v>700</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14205,13 +14439,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>77</v>
@@ -14233,7 +14467,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -14241,13 +14475,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>1553</v>
+        <v>1508</v>
       </c>
       <c r="F6" s="10" t="s">
         <v>149</v>
@@ -14269,7 +14503,7 @@
         <v>24</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14280,10 +14514,10 @@
         <v>891</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1562</v>
+        <v>1510</v>
       </c>
       <c r="F7" s="9" t="s">
         <v>85</v>
@@ -14299,13 +14533,13 @@
         <v>960</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14316,10 +14550,10 @@
         <v>767</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1508</v>
+        <v>1511</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1564</v>
+        <v>1512</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>102</v>
@@ -14335,13 +14569,13 @@
         <v>830</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14352,10 +14586,10 @@
         <v>445</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1509</v>
+        <v>1513</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1559</v>
+        <v>1514</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>102</v>
@@ -14377,7 +14611,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14385,13 +14619,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>1510</v>
+        <v>1515</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1511</v>
+        <v>1516</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>1549</v>
+        <v>1517</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>70</v>
@@ -14413,7 +14647,7 @@
         <v>24</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14421,13 +14655,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>1512</v>
+        <v>1518</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1513</v>
+        <v>1519</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>1514</v>
+        <v>1520</v>
       </c>
       <c r="F11" s="9" t="s">
         <v>131</v>
@@ -14443,13 +14677,13 @@
         <v>820</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14457,13 +14691,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>1560</v>
+        <v>1521</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>1515</v>
+        <v>1522</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>1561</v>
+        <v>1523</v>
       </c>
       <c r="F12" s="9" t="s">
         <v>85</v>
@@ -14479,13 +14713,13 @@
         <v>1090</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14493,13 +14727,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1516</v>
+        <v>1524</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1517</v>
+        <v>1525</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1518</v>
+        <v>1526</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>48</v>
@@ -14521,7 +14755,7 @@
         <v>24</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14529,13 +14763,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>1550</v>
+        <v>1527</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>1519</v>
+        <v>1528</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>1551</v>
+        <v>1529</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>48</v>
@@ -14557,7 +14791,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14565,10 +14799,10 @@
         <v>18</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1520</v>
+        <v>1530</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1521</v>
+        <v>1531</v>
       </c>
       <c r="E15" s="8" t="s">
         <v>207</v>
@@ -14587,13 +14821,13 @@
         <v>-25</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14601,13 +14835,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1522</v>
+        <v>1532</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1523</v>
+        <v>1533</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>1524</v>
+        <v>1534</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>131</v>
@@ -14623,13 +14857,13 @@
         <v>820</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14637,13 +14871,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>1546</v>
+        <v>1535</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>1547</v>
+        <v>1536</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>1548</v>
+        <v>1537</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>81</v>
@@ -14665,7 +14899,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14673,13 +14907,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1525</v>
+        <v>1538</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1526</v>
+        <v>1539</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1527</v>
+        <v>1540</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>308</v>
@@ -14701,7 +14935,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14709,13 +14943,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1563</v>
+        <v>1541</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1528</v>
+        <v>1542</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1529</v>
+        <v>1543</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>131</v>
@@ -14731,13 +14965,13 @@
         <v>350</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14745,13 +14979,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>1530</v>
+        <v>1544</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1531</v>
+        <v>1545</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1532</v>
+        <v>1546</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>81</v>
@@ -14773,7 +15007,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="21" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -14784,7 +15018,7 @@
         <v>745</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1533</v>
+        <v>1547</v>
       </c>
       <c r="E21" s="3" t="s">
         <v>747</v>
@@ -14809,7 +15043,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14817,13 +15051,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1534</v>
+        <v>1548</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1535</v>
+        <v>1549</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1536</v>
+        <v>1550</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>85</v>
@@ -14839,13 +15073,13 @@
         <v>-25</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -14856,7 +15090,7 @@
         <v>624</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1537</v>
+        <v>1551</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>626</v>
@@ -14881,7 +15115,7 @@
         <v>24</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>138</v>
@@ -14892,13 +15126,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>1538</v>
+        <v>1552</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1539</v>
+        <v>1553</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>1540</v>
+        <v>1554</v>
       </c>
       <c r="F24" s="7" t="s">
         <v>59</v>
@@ -14920,7 +15154,7 @@
         <v>24</v>
       </c>
       <c r="L24" s="6" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14928,13 +15162,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1541</v>
+        <v>1555</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>1542</v>
+        <v>1556</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>1543</v>
+        <v>1557</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>127</v>
@@ -14950,13 +15184,13 @@
         <v>740</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -14967,10 +15201,10 @@
         <v>18</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1544</v>
+        <v>1558</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>1545</v>
+        <v>1559</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>127</v>
@@ -14986,13 +15220,13 @@
         <v>0</v>
       </c>
       <c r="J26" s="8" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="K26" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15003,10 +15237,10 @@
         <v>18</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="F27" s="7" t="s">
         <v>102</v>
@@ -15028,7 +15262,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="6" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15039,10 +15273,10 @@
         <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1555</v>
+        <v>1562</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1556</v>
+        <v>1563</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>29</v>
@@ -15064,7 +15298,7 @@
         <v>24</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="29" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15075,7 +15309,7 @@
         <v>18</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>1554</v>
+        <v>1564</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>511</v>
@@ -15090,7 +15324,7 @@
         <v>60</v>
       </c>
       <c r="I29" s="3">
-        <f t="shared" ref="I29" si="1">G29-H29</f>
+        <f t="shared" si="0"/>
         <v>-60</v>
       </c>
       <c r="J29" s="3" t="s">
@@ -15100,7 +15334,1265 @@
         <v>24</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>1499</v>
+        <v>1500</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+  <dimension ref="A1:Q34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="60.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="3">
+        <v>30</v>
+      </c>
+      <c r="H3" s="3">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I33" si="0">G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G4" s="8">
+        <v>0</v>
+      </c>
+      <c r="H4" s="8">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1622</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>35</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>-35</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1570</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>1641</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1571</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G8" s="8">
+        <v>1875</v>
+      </c>
+      <c r="H8" s="8">
+        <v>25</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="0"/>
+        <v>1850</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>1575</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>1576</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G9" s="8">
+        <v>895</v>
+      </c>
+      <c r="H9" s="8">
+        <v>25</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1577</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="8">
+        <v>810</v>
+      </c>
+      <c r="H10" s="8">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>777</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>1580</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G11" s="6">
+        <v>0</v>
+      </c>
+      <c r="H11" s="6">
+        <v>25</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>1638</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>1639</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G12" s="6">
+        <v>25</v>
+      </c>
+      <c r="H12" s="6">
+        <v>25</v>
+      </c>
+      <c r="I12" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>1581</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>1634</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="8">
+        <v>850</v>
+      </c>
+      <c r="H13" s="8">
+        <v>30</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>1636</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0</v>
+      </c>
+      <c r="H14" s="8">
+        <v>30</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1586</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1625</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G15" s="8">
+        <v>375</v>
+      </c>
+      <c r="H15" s="8">
+        <v>25</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1627</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1628</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G16" s="8">
+        <v>825</v>
+      </c>
+      <c r="H16" s="8">
+        <v>35</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>1588</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>1589</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>1590</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1591</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1592</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>1593</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G18" s="6">
+        <v>0</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1594</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="8">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8">
+        <v>30</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>1598</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <v>20</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>1624</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="8">
+        <v>770</v>
+      </c>
+      <c r="H21" s="8">
+        <v>0</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1630</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1530</v>
+      </c>
+      <c r="H22" s="8">
+        <v>30</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>1500</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>1602</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G23" s="6">
+        <v>875</v>
+      </c>
+      <c r="H23" s="6">
+        <v>25</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>1626</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="8">
+        <v>1020</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>1605</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>1606</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>1607</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1015</v>
+      </c>
+      <c r="H25" s="6">
+        <v>25</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>1608</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>1609</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>1610</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G26" s="6">
+        <v>915</v>
+      </c>
+      <c r="H26" s="6">
+        <v>25</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1629</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
+      </c>
+      <c r="H27" s="8">
+        <v>30</v>
+      </c>
+      <c r="I27" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1620</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1621</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="3">
+        <v>595</v>
+      </c>
+      <c r="H28" s="3">
+        <v>25</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>1614</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>1480</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G29" s="8">
+        <v>695</v>
+      </c>
+      <c r="H29" s="8">
+        <v>35</v>
+      </c>
+      <c r="I29" s="8">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>1615</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G30" s="5">
+        <v>900</v>
+      </c>
+      <c r="H30" s="5">
+        <v>30</v>
+      </c>
+      <c r="I30" s="5">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J30" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="5" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1616</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G31" s="8">
+        <v>2710</v>
+      </c>
+      <c r="H31" s="8">
+        <v>35</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" si="0"/>
+        <v>2675</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>1618</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>1619</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>1635</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G32" s="8">
+        <v>1685</v>
+      </c>
+      <c r="H32" s="8">
+        <v>35</v>
+      </c>
+      <c r="I32" s="8">
+        <f t="shared" si="0"/>
+        <v>1650</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>1631</v>
+      </c>
+      <c r="D33" s="8" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G33" s="8">
+        <v>855</v>
+      </c>
+      <c r="H33" s="8">
+        <v>25</v>
+      </c>
+      <c r="I33" s="8">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J33" s="8" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="8" t="s">
+        <v>1567</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>1503</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>1504</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>1505</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G34" s="11">
+        <v>1020</v>
+      </c>
+      <c r="H34" s="11">
+        <v>30</v>
+      </c>
+      <c r="I34" s="11">
+        <v>990</v>
+      </c>
+      <c r="J34" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="11" t="s">
+        <v>1500</v>
+      </c>
+      <c r="M34" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N34" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O34" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P34" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q34" s="11">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E3870DF-F153-4CC6-8F1F-23A7C7D4D5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7966C60-AF95-46DC-9E75-2EDAF6FB8348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="18-05" sheetId="18" r:id="rId14"/>
     <sheet name="19-05" sheetId="19" r:id="rId15"/>
     <sheet name="20-05" sheetId="20" r:id="rId16"/>
+    <sheet name="21-05" sheetId="21" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5075" uniqueCount="1642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5425" uniqueCount="1745">
   <si>
     <t>THU 6</t>
   </si>
@@ -4751,21 +4752,33 @@
     <t>NGAY 20-5</t>
   </si>
   <si>
+    <t>20-05-2026</t>
+  </si>
+  <si>
+    <t>Jess-9244</t>
+  </si>
+  <si>
+    <t>275/14B1 Dạng Nguyên Cẩn, Phường Phú Lâm</t>
+  </si>
+  <si>
     <t>AT 20-05</t>
   </si>
   <si>
-    <t>20-05-2026</t>
-  </si>
-  <si>
-    <t>Jess-9244</t>
-  </si>
-  <si>
     <t>VICKY TRẦN</t>
   </si>
   <si>
+    <t>Đắc Hội Express 127/17 bình lợi p13</t>
+  </si>
+  <si>
     <t>hsu_myat to</t>
   </si>
   <si>
+    <t>HD022406</t>
+  </si>
+  <si>
+    <t>2A/14, Nguyễn Thị Minh Khai, P. Đakao</t>
+  </si>
+  <si>
     <t>Bé Hiền - fb Yudy Phạm</t>
   </si>
   <si>
@@ -4796,27 +4809,48 @@
     <t>Vincom đồng khởi, 45 lý tự trọng, căn hộ 2604</t>
   </si>
   <si>
+    <t>HD022255</t>
+  </si>
+  <si>
+    <t>Tòa nhà C22 Building Số G5, Đường C22, Phường 12</t>
+  </si>
+  <si>
     <t>Thanh Yến</t>
   </si>
   <si>
     <t>HD022266</t>
   </si>
   <si>
+    <t>188/4 đường thới an 16 phường thới an</t>
+  </si>
+  <si>
     <t>HƯƠNG</t>
   </si>
   <si>
     <t>HD022382</t>
   </si>
   <si>
+    <t>7g đường số 8 tân hưng</t>
+  </si>
+  <si>
     <t>Vận</t>
   </si>
   <si>
     <t>HD022293</t>
   </si>
   <si>
+    <t>Tháp RS6, chung cư Richstar 2, số 239 Hoà Bình, phường Phú Thạnh</t>
+  </si>
+  <si>
+    <t>nguyen lý</t>
+  </si>
+  <si>
     <t>HD022279</t>
   </si>
   <si>
+    <t>62/7h ấp 3 xã xuaabn thơi thượng</t>
+  </si>
+  <si>
     <t>Ý nhi</t>
   </si>
   <si>
@@ -4853,6 +4887,12 @@
     <t>HD022286</t>
   </si>
   <si>
+    <t>179/13A hoà bình Phường Hiệp Tân</t>
+  </si>
+  <si>
+    <t>Lyly My</t>
+  </si>
+  <si>
     <t>HD022377</t>
   </si>
   <si>
@@ -4868,6 +4908,9 @@
     <t>HD022263</t>
   </si>
   <si>
+    <t>1414 huỳnh tấn phát p phú mỹ</t>
+  </si>
+  <si>
     <t>Huyentran Nguyen</t>
   </si>
   <si>
@@ -4892,9 +4935,18 @@
     <t>HD022412</t>
   </si>
   <si>
+    <t>101 đông hưng thuận42 phường tân hưng thuận</t>
+  </si>
+  <si>
+    <t>ms Linh</t>
+  </si>
+  <si>
     <t>HD022275</t>
   </si>
   <si>
+    <t>141A đường số 1 phường Thông Tây Hội</t>
+  </si>
+  <si>
     <t>HD022267</t>
   </si>
   <si>
@@ -4907,43 +4959,16 @@
     <t>HD022196</t>
   </si>
   <si>
+    <t>181 đường số 79 phường tân quy</t>
+  </si>
+  <si>
     <t>Moon Nguyễn</t>
   </si>
   <si>
     <t>HD022375</t>
   </si>
   <si>
-    <t>ms Linh</t>
-  </si>
-  <si>
-    <t>141A đường số 1 phường Thông Tây Hội</t>
-  </si>
-  <si>
-    <t>Đắc Hội Express 127/17 bình lợi p13</t>
-  </si>
-  <si>
-    <t>275/14B1 Dạng Nguyên Cẩn, Phường Phú Lâm</t>
-  </si>
-  <si>
-    <t>179/13A hoà bình Phường Hiệp Tân</t>
-  </si>
-  <si>
-    <t>Tháp RS6, chung cư Richstar 2, số 239 Hoà Bình, phường Phú Thạnh</t>
-  </si>
-  <si>
-    <t>1414 huỳnh tấn phát p phú mỹ</t>
-  </si>
-  <si>
-    <t>nguyen lý</t>
-  </si>
-  <si>
-    <t>62/7h ấp 3 xã xuaabn thơi thượng</t>
-  </si>
-  <si>
-    <t>101 đông hưng thuận42 phường tân hưng thuận</t>
-  </si>
-  <si>
-    <t>Lyly My</t>
+    <t>16 kim ngân, khu dân cư phong phu 4, xã phong phú</t>
   </si>
   <si>
     <t>Ngoc_Ann tiktok gingeri 16:39</t>
@@ -4955,28 +4980,313 @@
     <t>1/7 nguyễn văn yên tân thới hoà</t>
   </si>
   <si>
-    <t>188/4 đường thới an 16 phường thới an</t>
-  </si>
-  <si>
-    <t>16 kim ngân, khu dân cư phong phu 4, xã phong phú</t>
-  </si>
-  <si>
-    <t>7g đường số 8 tân hưng</t>
-  </si>
-  <si>
-    <t>181 đường số 79 phường tân quy</t>
-  </si>
-  <si>
-    <t>HD022255</t>
-  </si>
-  <si>
-    <t>Tòa nhà C22 Building Số G5, Đường C22, Phường 12</t>
-  </si>
-  <si>
-    <t>HD022406</t>
-  </si>
-  <si>
-    <t>2A/14, Nguyễn Thị Minh Khai, P. Đakao</t>
+    <t>NGAY 21-5</t>
+  </si>
+  <si>
+    <t>AT 21-05</t>
+  </si>
+  <si>
+    <t>21-05-2026</t>
+  </si>
+  <si>
+    <t>Anh Trúc Huỳnh</t>
+  </si>
+  <si>
+    <t>HD022586</t>
+  </si>
+  <si>
+    <t>HD022495</t>
+  </si>
+  <si>
+    <t>BN182 miki chouchou Fb.</t>
+  </si>
+  <si>
+    <t>HD022533</t>
+  </si>
+  <si>
+    <t>Hana Le</t>
+  </si>
+  <si>
+    <t>HD022573</t>
+  </si>
+  <si>
+    <t>Giap Anh Tuyet</t>
+  </si>
+  <si>
+    <t>HD022508</t>
+  </si>
+  <si>
+    <t>Bùi Vĩ Thương</t>
+  </si>
+  <si>
+    <t>HD022636</t>
+  </si>
+  <si>
+    <t>3273 phạm thế hiển, p7</t>
+  </si>
+  <si>
+    <t>HD022429</t>
+  </si>
+  <si>
+    <t>HD022628</t>
+  </si>
+  <si>
+    <t>My Yến</t>
+  </si>
+  <si>
+    <t>HD022525</t>
+  </si>
+  <si>
+    <t>Hải Yến</t>
+  </si>
+  <si>
+    <t>HD003936</t>
+  </si>
+  <si>
+    <t>319/17 lê văn thọ p9</t>
+  </si>
+  <si>
+    <t>Hoang Linh Le</t>
+  </si>
+  <si>
+    <t>HD022460</t>
+  </si>
+  <si>
+    <t>Chị Oanh</t>
+  </si>
+  <si>
+    <t>HD022599</t>
+  </si>
+  <si>
+    <t>291 hùng vương phương an đông</t>
+  </si>
+  <si>
+    <t>HD022451</t>
+  </si>
+  <si>
+    <t>58E cao thắng,p5 (Viện chăm sóc da aperio)</t>
+  </si>
+  <si>
+    <t>Linh Ngô</t>
+  </si>
+  <si>
+    <t>HD022618</t>
+  </si>
+  <si>
+    <t>Lan Phạm</t>
+  </si>
+  <si>
+    <t>HD022621</t>
+  </si>
+  <si>
+    <t>685 âu cơ p tân thành - lô C</t>
+  </si>
+  <si>
+    <t>Sorinna items PhnomPenh ( Meng Kheang customer )</t>
+  </si>
+  <si>
+    <t>HD022445</t>
+  </si>
+  <si>
+    <t>301 phạm ngũ lão</t>
+  </si>
+  <si>
+    <t>01우준</t>
+  </si>
+  <si>
+    <t>HD022601</t>
+  </si>
+  <si>
+    <t>HD022341</t>
+  </si>
+  <si>
+    <t>352/4g lê văn quới, bình hưng hoà A</t>
+  </si>
+  <si>
+    <t>thuy vy</t>
+  </si>
+  <si>
+    <t>HD022620</t>
+  </si>
+  <si>
+    <t>HD022604</t>
+  </si>
+  <si>
+    <t>Mỹ Vinh</t>
+  </si>
+  <si>
+    <t>HD022560</t>
+  </si>
+  <si>
+    <t>HD022503</t>
+  </si>
+  <si>
+    <t>HD022383</t>
+  </si>
+  <si>
+    <t>Nguyễn Yến Nhi</t>
+  </si>
+  <si>
+    <t>HD022491</t>
+  </si>
+  <si>
+    <t>Khánh Thư Nguyen</t>
+  </si>
+  <si>
+    <t>HD022626</t>
+  </si>
+  <si>
+    <t>88 dien Hồng phường 1</t>
+  </si>
+  <si>
+    <t>chủ mau - fb Hana Ngo</t>
+  </si>
+  <si>
+    <t>HD022615</t>
+  </si>
+  <si>
+    <t>Quỳnh Nhi</t>
+  </si>
+  <si>
+    <t>HD022493</t>
+  </si>
+  <si>
+    <t>Mỹ ý</t>
+  </si>
+  <si>
+    <t>HD022613</t>
+  </si>
+  <si>
+    <t>HD022430</t>
+  </si>
+  <si>
+    <t>HD022342</t>
+  </si>
+  <si>
+    <t>NHƯ- Khanh sale- airmy</t>
+  </si>
+  <si>
+    <t>HD022551</t>
+  </si>
+  <si>
+    <t>144C Trần Thị Trọng, Phường 15</t>
+  </si>
+  <si>
+    <t>Nguyễn Thanh Ngân</t>
+  </si>
+  <si>
+    <t>HD022575</t>
+  </si>
+  <si>
+    <t>159c /18a dạ nam, chánh hưng</t>
+  </si>
+  <si>
+    <t>Huỳnh Mẫn</t>
+  </si>
+  <si>
+    <t>HD022522</t>
+  </si>
+  <si>
+    <t>1362 tỉnh lộ 10 tân tạo</t>
+  </si>
+  <si>
+    <t>VVI EVA</t>
+  </si>
+  <si>
+    <t>Toà Aster - Urban green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thái Hiệp</t>
+  </si>
+  <si>
+    <t>334/33/1C Chu văn an, phường 12</t>
+  </si>
+  <si>
+    <t>Số 64 dg 38 hiep binh chanh</t>
+  </si>
+  <si>
+    <t>Đảo kim cương phường bình trưng tây</t>
+  </si>
+  <si>
+    <t>PHƯƠNG DUNG</t>
+  </si>
+  <si>
+    <t>23/4A đường 48 khu phố 6 hiệp bình chánh</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Kim Hoàng</t>
+  </si>
+  <si>
+    <t>265 Nơ Trang Long, phường Bình Lợi Trung</t>
+  </si>
+  <si>
+    <t>HD022442</t>
+  </si>
+  <si>
+    <t>314 Điện Biên Phủ, Phường Vườn Lài</t>
+  </si>
+  <si>
+    <t>Aqua1 vinhome bason bến nghé</t>
+  </si>
+  <si>
+    <t>Thuy Thuy</t>
+  </si>
+  <si>
+    <t>141 Hùng Vương phường 4</t>
+  </si>
+  <si>
+    <t>người nhận Hồng Sơn fb Duong Hyun</t>
+  </si>
+  <si>
+    <t>135 Bạch Đằng, phường Tân Sơn Hòa (Phường 2) (CÔNG TY LÊ GIA EXPRESS)</t>
+  </si>
+  <si>
+    <t>320/14 nguyễn văn linh phường bình thuận</t>
+  </si>
+  <si>
+    <t>Lý Thanh Tâm</t>
+  </si>
+  <si>
+    <t>HD022564</t>
+  </si>
+  <si>
+    <t>71/6/16 lê tấn bê an lạc</t>
+  </si>
+  <si>
+    <t>007 Lô B, Đường C6, Chung cư Tây Thạnh</t>
+  </si>
+  <si>
+    <t>90 a lê lăng Phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Tháp v3 Chung cư sun rise city south 23 nguyễn hữu thọ tân hưng</t>
+  </si>
+  <si>
+    <t>67 Trang từ phường 14</t>
+  </si>
+  <si>
+    <t>Phạm Thị Minh Tuyền</t>
+  </si>
+  <si>
+    <t>180/1T QL1A Tân Phú</t>
+  </si>
+  <si>
+    <t>Pé Thỏ</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bửu f6 Chung cư the pegasuite1 (zone1)</t>
+  </si>
+  <si>
+    <t>HD022455</t>
+  </si>
+  <si>
+    <t>427/22 le van quoi binh tri dong A</t>
+  </si>
+  <si>
+    <t>chung cư Ruby - cổng 2, đường Tân Thắng, P. Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD020811</t>
   </si>
 </sst>
 </file>
@@ -5055,7 +5365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5071,6 +5381,9 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6599,7 +6912,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I56" si="1">G35-H35</f>
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -15347,10 +15660,12 @@
   <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="27.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="60.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -15450,7 +15765,7 @@
         <v>24</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15461,10 +15776,10 @@
         <v>18</v>
       </c>
       <c r="C4" s="8" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E4" s="8" t="s">
         <v>1568</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>1623</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>127</v>
@@ -15480,13 +15795,13 @@
         <v>-30</v>
       </c>
       <c r="J4" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15522,7 +15837,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -15533,10 +15848,10 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1622</v>
+        <v>1571</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>81</v>
@@ -15558,7 +15873,7 @@
         <v>24</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15566,13 +15881,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1640</v>
+        <v>1573</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>1641</v>
+        <v>1574</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>63</v>
@@ -15594,7 +15909,7 @@
         <v>24</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15602,13 +15917,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1571</v>
+        <v>1575</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1572</v>
+        <v>1576</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1573</v>
+        <v>1577</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>127</v>
@@ -15624,13 +15939,13 @@
         <v>1850</v>
       </c>
       <c r="J8" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15638,13 +15953,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1575</v>
+        <v>1579</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1576</v>
+        <v>1580</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>85</v>
@@ -15660,13 +15975,13 @@
         <v>870</v>
       </c>
       <c r="J9" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>1567</v>
       </c>
       <c r="M9" s="8" t="s">
         <v>288</v>
@@ -15677,10 +15992,10 @@
         <v>18</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>1577</v>
+        <v>1581</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1578</v>
+        <v>1582</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>1278</v>
@@ -15699,13 +16014,13 @@
         <v>780</v>
       </c>
       <c r="J10" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15716,10 +16031,10 @@
         <v>777</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1579</v>
+        <v>1583</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>1580</v>
+        <v>1584</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>63</v>
@@ -15741,7 +16056,7 @@
         <v>24</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15752,10 +16067,10 @@
         <v>1058</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1638</v>
+        <v>1585</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>1639</v>
+        <v>1586</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>102</v>
@@ -15777,7 +16092,7 @@
         <v>24</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15785,13 +16100,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>1581</v>
+        <v>1587</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>1582</v>
+        <v>1588</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>1634</v>
+        <v>1589</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>29</v>
@@ -15807,13 +16122,13 @@
         <v>820</v>
       </c>
       <c r="J13" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15821,13 +16136,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>1583</v>
+        <v>1590</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>1584</v>
+        <v>1591</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>1636</v>
+        <v>1592</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>131</v>
@@ -15843,13 +16158,13 @@
         <v>-30</v>
       </c>
       <c r="J14" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15857,13 +16172,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1585</v>
+        <v>1593</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1586</v>
+        <v>1594</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1625</v>
+        <v>1595</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>85</v>
@@ -15879,13 +16194,13 @@
         <v>350</v>
       </c>
       <c r="J15" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -15893,13 +16208,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>1627</v>
+        <v>1596</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>1587</v>
+        <v>1597</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>1628</v>
+        <v>1598</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>1335</v>
@@ -15915,13 +16230,13 @@
         <v>790</v>
       </c>
       <c r="J16" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="17" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15929,13 +16244,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1588</v>
+        <v>1599</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1589</v>
+        <v>1600</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1590</v>
+        <v>1601</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>98</v>
@@ -15957,7 +16272,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="18" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -15965,13 +16280,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1591</v>
+        <v>1602</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1592</v>
+        <v>1603</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1593</v>
+        <v>1604</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>102</v>
@@ -15993,7 +16308,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="19" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -16001,10 +16316,10 @@
         <v>18</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1594</v>
+        <v>1605</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1595</v>
+        <v>1606</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>1281</v>
@@ -16023,13 +16338,13 @@
         <v>-30</v>
       </c>
       <c r="J19" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="20" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -16037,13 +16352,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1596</v>
+        <v>1607</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1597</v>
+        <v>1608</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1598</v>
+        <v>1609</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>355</v>
@@ -16065,7 +16380,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="21" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -16073,13 +16388,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>1574</v>
+        <v>1578</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>1599</v>
+        <v>1610</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>1624</v>
+        <v>1611</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>85</v>
@@ -16095,13 +16410,13 @@
         <v>770</v>
       </c>
       <c r="J21" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21" s="8" t="s">
-        <v>1567</v>
       </c>
       <c r="M21" s="8" t="s">
         <v>288</v>
@@ -16112,13 +16427,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1630</v>
+        <v>1612</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1600</v>
+        <v>1613</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1601</v>
+        <v>1614</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>29</v>
@@ -16134,13 +16449,13 @@
         <v>1500</v>
       </c>
       <c r="J22" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L22" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="23" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -16151,7 +16466,7 @@
         <v>558</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1602</v>
+        <v>1615</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>560</v>
@@ -16176,7 +16491,7 @@
         <v>24</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="24" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -16184,13 +16499,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1603</v>
+        <v>1616</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1604</v>
+        <v>1617</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
       <c r="F24" s="9" t="s">
         <v>131</v>
@@ -16206,13 +16521,13 @@
         <v>990</v>
       </c>
       <c r="J24" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L24" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="25" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -16220,13 +16535,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1605</v>
+        <v>1619</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1606</v>
+        <v>1620</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1607</v>
+        <v>1621</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>63</v>
@@ -16248,7 +16563,7 @@
         <v>24</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="26" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -16256,13 +16571,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>1608</v>
+        <v>1622</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1609</v>
+        <v>1623</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>1610</v>
+        <v>1624</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>98</v>
@@ -16284,7 +16599,7 @@
         <v>24</v>
       </c>
       <c r="L26" s="6" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="27" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -16292,13 +16607,13 @@
         <v>18</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>1611</v>
+        <v>1625</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1612</v>
+        <v>1626</v>
       </c>
       <c r="E27" s="8" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>29</v>
@@ -16314,13 +16629,13 @@
         <v>-30</v>
       </c>
       <c r="J27" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K27" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L27" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="28" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -16328,13 +16643,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1620</v>
+        <v>1628</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>1613</v>
+        <v>1629</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>1621</v>
+        <v>1630</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>70</v>
@@ -16356,7 +16671,7 @@
         <v>24</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
       <c r="M28" s="3" t="s">
         <v>145</v>
@@ -16370,7 +16685,7 @@
         <v>1478</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>1614</v>
+        <v>1631</v>
       </c>
       <c r="E29" s="8" t="s">
         <v>1480</v>
@@ -16389,13 +16704,13 @@
         <v>660</v>
       </c>
       <c r="J29" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K29" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L29" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="30" spans="2:13" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -16406,7 +16721,7 @@
         <v>1148</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>1615</v>
+        <v>1632</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>1150</v>
@@ -16431,7 +16746,7 @@
         <v>24</v>
       </c>
       <c r="L30" s="5" t="s">
-        <v>1567</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="31" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -16439,13 +16754,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1616</v>
+        <v>1633</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1617</v>
+        <v>1634</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>131</v>
@@ -16461,13 +16776,13 @@
         <v>2675</v>
       </c>
       <c r="J31" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K31" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L31" s="8" t="s">
-        <v>1567</v>
       </c>
       <c r="M31" s="8" t="s">
         <v>145</v>
@@ -16478,13 +16793,13 @@
         <v>18</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1618</v>
+        <v>1636</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>1619</v>
+        <v>1637</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>52</v>
@@ -16500,13 +16815,13 @@
         <v>1650</v>
       </c>
       <c r="J32" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L32" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="33" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -16514,13 +16829,13 @@
         <v>18</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>1631</v>
+        <v>1639</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>1632</v>
+        <v>1640</v>
       </c>
       <c r="E33" s="8" t="s">
-        <v>1633</v>
+        <v>1641</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>85</v>
@@ -16536,13 +16851,13 @@
         <v>830</v>
       </c>
       <c r="J33" s="8" t="s">
+        <v>1569</v>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="8" t="s">
         <v>1566</v>
-      </c>
-      <c r="K33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="L33" s="8" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="34" spans="2:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -16592,6 +16907,1579 @@
         <v>266</v>
       </c>
       <c r="Q34" s="11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="49.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="76.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>1732</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3" s="8">
+        <v>850</v>
+      </c>
+      <c r="H3" s="8">
+        <v>30</v>
+      </c>
+      <c r="I3" s="8">
+        <f t="shared" ref="I3:I42" si="0">G3-H3</f>
+        <v>820</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1645</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1646</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1500</v>
+      </c>
+      <c r="H4" s="3">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>1470</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>1728</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="6">
+        <v>4400</v>
+      </c>
+      <c r="H5" s="6">
+        <v>35</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" ref="I5" si="1">G5-H5</f>
+        <v>4365</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>1644</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1648</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1649</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1714</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="3">
+        <v>30</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1650</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1651</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1742</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7" s="8">
+        <v>470</v>
+      </c>
+      <c r="H7" s="8">
+        <v>30</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>1733</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G8" s="8">
+        <v>0</v>
+      </c>
+      <c r="H8" s="8">
+        <v>25</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>1654</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>1655</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>1656</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="8">
+        <v>850</v>
+      </c>
+      <c r="H9" s="8">
+        <v>30</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1657</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G10" s="3">
+        <v>720</v>
+      </c>
+      <c r="H10" s="3">
+        <v>30</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>1510</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G11" s="8">
+        <v>915</v>
+      </c>
+      <c r="H11" s="8">
+        <v>25</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1715</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G12" s="3">
+        <v>510</v>
+      </c>
+      <c r="H12" s="3">
+        <v>20</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1661</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1662</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1663</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>25</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>1664</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>1665</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>1723</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G14" s="6">
+        <v>515</v>
+      </c>
+      <c r="H14" s="6">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>1667</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>1668</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="6">
+        <v>895</v>
+      </c>
+      <c r="H15" s="6">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>1722</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G16" s="6">
+        <v>710</v>
+      </c>
+      <c r="H16" s="6">
+        <v>20</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>1725</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>1669</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>1670</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="6">
+        <v>515</v>
+      </c>
+      <c r="H17" s="6">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>1671</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>1672</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>1734</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G18" s="8">
+        <v>1855</v>
+      </c>
+      <c r="H18" s="8">
+        <v>25</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="0"/>
+        <v>1830</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1673</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>1674</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>1675</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G19" s="8">
+        <v>795</v>
+      </c>
+      <c r="H19" s="8">
+        <v>25</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>1678</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <v>25</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>1679</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1680</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>1717</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="3">
+        <v>850</v>
+      </c>
+      <c r="H21" s="3">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="22" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1681</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1682</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1120</v>
+      </c>
+      <c r="H22" s="8">
+        <v>30</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="23" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1683</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1684</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1743</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="8">
+        <v>0</v>
+      </c>
+      <c r="H23" s="8">
+        <v>25</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="24" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>1332</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>1685</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>1334</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G24" s="8">
+        <v>775</v>
+      </c>
+      <c r="H24" s="8">
+        <v>35</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>740</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="25" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>1686</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>1687</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>1724</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G25" s="6">
+        <v>915</v>
+      </c>
+      <c r="H25" s="6">
+        <v>25</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="26" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>1688</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1713</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="3">
+        <v>520</v>
+      </c>
+      <c r="H26" s="3">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="27" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G27" s="8">
+        <v>710</v>
+      </c>
+      <c r="H27" s="8">
+        <v>30</v>
+      </c>
+      <c r="I27" s="8">
+        <f t="shared" si="0"/>
+        <v>680</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>1690</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>1691</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>1735</v>
+      </c>
+      <c r="F28" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" s="8">
+        <v>520</v>
+      </c>
+      <c r="H28" s="8">
+        <v>30</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="29" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>1739</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>1740</v>
+      </c>
+      <c r="F29" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G29" s="8">
+        <v>0</v>
+      </c>
+      <c r="H29" s="8">
+        <v>30</v>
+      </c>
+      <c r="I29" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="30" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G30" s="3">
+        <v>800</v>
+      </c>
+      <c r="H30" s="3">
+        <v>20</v>
+      </c>
+      <c r="I30" s="3">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="31" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1695</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>1696</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>1736</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>25</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="32" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>1697</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>1698</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>1738</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G32" s="8">
+        <v>520</v>
+      </c>
+      <c r="H32" s="8">
+        <v>30</v>
+      </c>
+      <c r="I32" s="8">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1699</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1700</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G33" s="3">
+        <v>0</v>
+      </c>
+      <c r="H33" s="3">
+        <v>25</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>1720</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>1721</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G34" s="3">
+        <v>850</v>
+      </c>
+      <c r="H34" s="3">
+        <v>20</v>
+      </c>
+      <c r="I34" s="3">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>1267</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>1702</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>1729</v>
+      </c>
+      <c r="F35" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G35" s="8">
+        <v>990</v>
+      </c>
+      <c r="H35" s="8">
+        <v>30</v>
+      </c>
+      <c r="I35" s="8">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J35" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1703</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>1704</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1705</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0</v>
+      </c>
+      <c r="H36" s="3">
+        <v>25</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>1708</v>
+      </c>
+      <c r="F37" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G37" s="8">
+        <v>1020</v>
+      </c>
+      <c r="H37" s="8">
+        <v>30</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>1709</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>1710</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>1711</v>
+      </c>
+      <c r="F38" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G38" s="8">
+        <v>860</v>
+      </c>
+      <c r="H38" s="8">
+        <v>30</v>
+      </c>
+      <c r="I38" s="8">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>1712</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>1726</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" s="6">
+        <v>30</v>
+      </c>
+      <c r="H39" s="6">
+        <v>30</v>
+      </c>
+      <c r="I39" s="6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="6" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" s="8">
+        <v>30</v>
+      </c>
+      <c r="H40" s="8">
+        <v>30</v>
+      </c>
+      <c r="I40" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J40" s="8" t="s">
+        <v>1643</v>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G41" s="3">
+        <v>0</v>
+      </c>
+      <c r="H41" s="3">
+        <v>40</v>
+      </c>
+      <c r="I41" s="3">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>1719</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>30</v>
+      </c>
+      <c r="I42" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E43" s="15" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F43" s="16">
+        <v>7</v>
+      </c>
+      <c r="G43" s="16">
+        <v>810</v>
+      </c>
+      <c r="H43" s="16">
+        <v>30</v>
+      </c>
+      <c r="I43" s="16">
+        <f>G43-H43</f>
+        <v>780</v>
+      </c>
+      <c r="J43" s="15" t="s">
+        <v>1131</v>
+      </c>
+      <c r="K43" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="15" t="s">
+        <v>1124</v>
+      </c>
+      <c r="M43" s="17" t="s">
+        <v>264</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="O43" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="P43" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q43" s="15">
         <v>1</v>
       </c>
     </row>
@@ -18892,7 +20780,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I55" si="1">G35-H35</f>
         <v>2090</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -26075,7 +27963,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I58" si="1">G35-H35</f>
         <v>-30</v>
       </c>
       <c r="J35" s="8" t="s">

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7966C60-AF95-46DC-9E75-2EDAF6FB8348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB8076F-6EF0-49AA-B0C2-284D9AE24792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -30,6 +30,8 @@
     <sheet name="19-05" sheetId="19" r:id="rId15"/>
     <sheet name="20-05" sheetId="20" r:id="rId16"/>
     <sheet name="21-05" sheetId="21" r:id="rId17"/>
+    <sheet name="22-05" sheetId="22" r:id="rId18"/>
+    <sheet name="23-05" sheetId="23" r:id="rId19"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5425" uniqueCount="1745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5893" uniqueCount="1871">
   <si>
     <t>THU 6</t>
   </si>
@@ -4983,6 +4985,15 @@
     <t>NGAY 21-5</t>
   </si>
   <si>
+    <t>Lý Thanh Tâm</t>
+  </si>
+  <si>
+    <t>HD022564</t>
+  </si>
+  <si>
+    <t>71/6/16 lê tấn bê an lạc</t>
+  </si>
+  <si>
     <t>AT 21-05</t>
   </si>
   <si>
@@ -4995,27 +5006,45 @@
     <t>HD022586</t>
   </si>
   <si>
+    <t>Số 64 dg 38 hiep binh chanh</t>
+  </si>
+  <si>
+    <t>người nhận Hồng Sơn fb Duong Hyun</t>
+  </si>
+  <si>
     <t>HD022495</t>
   </si>
   <si>
+    <t>135 Bạch Đằng, phường Tân Sơn Hòa (Phường 2) (CÔNG TY LÊ GIA EXPRESS)</t>
+  </si>
+  <si>
     <t>BN182 miki chouchou Fb.</t>
   </si>
   <si>
     <t>HD022533</t>
   </si>
   <si>
+    <t>163 Đường Trương Thị Hoa, phường Tân Thái Hiệp</t>
+  </si>
+  <si>
     <t>Hana Le</t>
   </si>
   <si>
     <t>HD022573</t>
   </si>
   <si>
+    <t>427/22 le van quoi binh tri dong A</t>
+  </si>
+  <si>
     <t>Giap Anh Tuyet</t>
   </si>
   <si>
     <t>HD022508</t>
   </si>
   <si>
+    <t>007 Lô B, Đường C6, Chung cư Tây Thạnh</t>
+  </si>
+  <si>
     <t>Bùi Vĩ Thương</t>
   </si>
   <si>
@@ -5037,6 +5066,9 @@
     <t>HD022525</t>
   </si>
   <si>
+    <t>334/33/1C Chu văn an, phường 12</t>
+  </si>
+  <si>
     <t>Hải Yến</t>
   </si>
   <si>
@@ -5052,6 +5084,9 @@
     <t>HD022460</t>
   </si>
   <si>
+    <t>314 Điện Biên Phủ, Phường Vườn Lài</t>
+  </si>
+  <si>
     <t>Chị Oanh</t>
   </si>
   <si>
@@ -5061,6 +5096,12 @@
     <t>291 hùng vương phương an đông</t>
   </si>
   <si>
+    <t>HD022442</t>
+  </si>
+  <si>
+    <t>Thuy Thuy</t>
+  </si>
+  <si>
     <t>HD022451</t>
   </si>
   <si>
@@ -5073,6 +5114,9 @@
     <t>HD022618</t>
   </si>
   <si>
+    <t>90 a lê lăng Phú thọ hoà</t>
+  </si>
+  <si>
     <t>Lan Phạm</t>
   </si>
   <si>
@@ -5097,6 +5141,12 @@
     <t>HD022601</t>
   </si>
   <si>
+    <t>Đảo kim cương phường bình trưng tây</t>
+  </si>
+  <si>
+    <t>Phạm Thị Minh Tuyền</t>
+  </si>
+  <si>
     <t>HD022341</t>
   </si>
   <si>
@@ -5109,6 +5159,9 @@
     <t>HD022620</t>
   </si>
   <si>
+    <t>chung cư Ruby - cổng 2, đường Tân Thắng, P. Tân Sơn Nhì</t>
+  </si>
+  <si>
     <t>HD022604</t>
   </si>
   <si>
@@ -5118,9 +5171,15 @@
     <t>HD022560</t>
   </si>
   <si>
+    <t>Aqua1 vinhome bason bến nghé</t>
+  </si>
+  <si>
     <t>HD022503</t>
   </si>
   <si>
+    <t>Toà Aster - Urban green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
     <t>HD022383</t>
   </si>
   <si>
@@ -5130,6 +5189,18 @@
     <t>HD022491</t>
   </si>
   <si>
+    <t>Tháp v3 Chung cư sun rise city south 23 nguyễn hữu thọ tân hưng</t>
+  </si>
+  <si>
+    <t>Pé Thỏ</t>
+  </si>
+  <si>
+    <t>HD022455</t>
+  </si>
+  <si>
+    <t>1002 tạ quang bửu f6 Chung cư the pegasuite1 (zone1)</t>
+  </si>
+  <si>
     <t>Khánh Thư Nguyen</t>
   </si>
   <si>
@@ -5145,24 +5216,39 @@
     <t>HD022615</t>
   </si>
   <si>
+    <t>67 Trang từ phường 14</t>
+  </si>
+  <si>
     <t>Quỳnh Nhi</t>
   </si>
   <si>
     <t>HD022493</t>
   </si>
   <si>
+    <t>180/1T QL1A Tân Phú</t>
+  </si>
+  <si>
     <t>Mỹ ý</t>
   </si>
   <si>
     <t>HD022613</t>
   </si>
   <si>
+    <t>Nguyễn Thị Kim Hoàng</t>
+  </si>
+  <si>
     <t>HD022430</t>
   </si>
   <si>
+    <t>265 Nơ Trang Long, phường Bình Lợi Trung</t>
+  </si>
+  <si>
     <t>HD022342</t>
   </si>
   <si>
+    <t>320/14 nguyễn văn linh phường bình thuận</t>
+  </si>
+  <si>
     <t>NHƯ- Khanh sale- airmy</t>
   </si>
   <si>
@@ -5193,19 +5279,7 @@
     <t>VVI EVA</t>
   </si>
   <si>
-    <t>Toà Aster - Urban green (đối diện Vạn Phúc)</t>
-  </si>
-  <si>
-    <t>163 Đường Trương Thị Hoa, phường Tân Thái Hiệp</t>
-  </si>
-  <si>
-    <t>334/33/1C Chu văn an, phường 12</t>
-  </si>
-  <si>
-    <t>Số 64 dg 38 hiep binh chanh</t>
-  </si>
-  <si>
-    <t>Đảo kim cương phường bình trưng tây</t>
+    <t>141 Hùng Vương phường 4</t>
   </si>
   <si>
     <t>PHƯƠNG DUNG</t>
@@ -5214,79 +5288,385 @@
     <t>23/4A đường 48 khu phố 6 hiệp bình chánh</t>
   </si>
   <si>
-    <t>Nguyễn Thị Kim Hoàng</t>
-  </si>
-  <si>
-    <t>265 Nơ Trang Long, phường Bình Lợi Trung</t>
-  </si>
-  <si>
-    <t>HD022442</t>
-  </si>
-  <si>
-    <t>314 Điện Biên Phủ, Phường Vườn Lài</t>
-  </si>
-  <si>
-    <t>Aqua1 vinhome bason bến nghé</t>
-  </si>
-  <si>
-    <t>Thuy Thuy</t>
-  </si>
-  <si>
-    <t>141 Hùng Vương phường 4</t>
-  </si>
-  <si>
-    <t>người nhận Hồng Sơn fb Duong Hyun</t>
-  </si>
-  <si>
-    <t>135 Bạch Đằng, phường Tân Sơn Hòa (Phường 2) (CÔNG TY LÊ GIA EXPRESS)</t>
-  </si>
-  <si>
-    <t>320/14 nguyễn văn linh phường bình thuận</t>
-  </si>
-  <si>
-    <t>Lý Thanh Tâm</t>
-  </si>
-  <si>
-    <t>HD022564</t>
-  </si>
-  <si>
-    <t>71/6/16 lê tấn bê an lạc</t>
-  </si>
-  <si>
-    <t>007 Lô B, Đường C6, Chung cư Tây Thạnh</t>
-  </si>
-  <si>
-    <t>90 a lê lăng Phú thọ hoà</t>
-  </si>
-  <si>
-    <t>Tháp v3 Chung cư sun rise city south 23 nguyễn hữu thọ tân hưng</t>
-  </si>
-  <si>
-    <t>67 Trang từ phường 14</t>
-  </si>
-  <si>
-    <t>Phạm Thị Minh Tuyền</t>
-  </si>
-  <si>
-    <t>180/1T QL1A Tân Phú</t>
-  </si>
-  <si>
-    <t>Pé Thỏ</t>
-  </si>
-  <si>
-    <t>1002 tạ quang bửu f6 Chung cư the pegasuite1 (zone1)</t>
-  </si>
-  <si>
-    <t>HD022455</t>
-  </si>
-  <si>
-    <t>427/22 le van quoi binh tri dong A</t>
-  </si>
-  <si>
-    <t>chung cư Ruby - cổng 2, đường Tân Thắng, P. Tân Sơn Nhì</t>
-  </si>
-  <si>
     <t>HD020811</t>
+  </si>
+  <si>
+    <t>NGAY 22-5</t>
+  </si>
+  <si>
+    <t>HD022893</t>
+  </si>
+  <si>
+    <t>22-05-2026</t>
+  </si>
+  <si>
+    <t>Đỗ Linh Chi</t>
+  </si>
+  <si>
+    <t>HD022673</t>
+  </si>
+  <si>
+    <t>86/36/3 Phố Quang, Phường Tân Sơn Hòa</t>
+  </si>
+  <si>
+    <t>Quỳnh Như</t>
+  </si>
+  <si>
+    <t>HD022888</t>
+  </si>
+  <si>
+    <t>66/68, Phổ Quang, Phường 2</t>
+  </si>
+  <si>
+    <t>Diễm</t>
+  </si>
+  <si>
+    <t>HD022790</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 3</t>
+  </si>
+  <si>
+    <t>HD022758</t>
+  </si>
+  <si>
+    <t>AT 22-05</t>
+  </si>
+  <si>
+    <t>Trần Hương</t>
+  </si>
+  <si>
+    <t>HD022721</t>
+  </si>
+  <si>
+    <t>339 lê văn quới phường bình trị đông A</t>
+  </si>
+  <si>
+    <t>VTS-36588MNG</t>
+  </si>
+  <si>
+    <t>HD022692</t>
+  </si>
+  <si>
+    <t>w3360</t>
+  </si>
+  <si>
+    <t>HD022791</t>
+  </si>
+  <si>
+    <t>624 Lê thị riêng,thới an</t>
+  </si>
+  <si>
+    <t>HD022655</t>
+  </si>
+  <si>
+    <t>Heng Roza</t>
+  </si>
+  <si>
+    <t>EV38382</t>
+  </si>
+  <si>
+    <t>315/18/6 Nguyễn Thị Tú, BHHB</t>
+  </si>
+  <si>
+    <t>Nguyễn Loan</t>
+  </si>
+  <si>
+    <t>HD022726</t>
+  </si>
+  <si>
+    <t>91/33 nguyên hồng</t>
+  </si>
+  <si>
+    <t>Minh Hải zalo cẩm ngân</t>
+  </si>
+  <si>
+    <t>HD022896</t>
+  </si>
+  <si>
+    <t>Dung Dung</t>
+  </si>
+  <si>
+    <t>HD022794</t>
+  </si>
+  <si>
+    <t>125/191 nguyễn thị tần p2</t>
+  </si>
+  <si>
+    <t>Như Huỳnh</t>
+  </si>
+  <si>
+    <t>HD022787</t>
+  </si>
+  <si>
+    <t>16 đường 69 Tân Hưng</t>
+  </si>
+  <si>
+    <t>Hạnh Hạnh</t>
+  </si>
+  <si>
+    <t>HD022865</t>
+  </si>
+  <si>
+    <t>334 tô hiến thành p14 Chung cư kingdom101 block a</t>
+  </si>
+  <si>
+    <t>GUBY Fb Trương Ngọc</t>
+  </si>
+  <si>
+    <t>số 201/12 mã văn lò, P, bình trị đông a</t>
+  </si>
+  <si>
+    <t>HD022757</t>
+  </si>
+  <si>
+    <t>Nguyễn Chi</t>
+  </si>
+  <si>
+    <t>HD022759</t>
+  </si>
+  <si>
+    <t>51-53 duong số 57c f tân tạo</t>
+  </si>
+  <si>
+    <t>HD022866</t>
+  </si>
+  <si>
+    <t>Hương Quỳnh (Nhượng)</t>
+  </si>
+  <si>
+    <t>HD022886</t>
+  </si>
+  <si>
+    <t>15/3 Lê Văn Huân, P13</t>
+  </si>
+  <si>
+    <t>Ngọc Tiên</t>
+  </si>
+  <si>
+    <t>HD022897</t>
+  </si>
+  <si>
+    <t>59 trần hưng đạo p tân thành</t>
+  </si>
+  <si>
+    <t>Phạm Thùy Đan</t>
+  </si>
+  <si>
+    <t>HD022634</t>
+  </si>
+  <si>
+    <t>83/25b đường Hoà Hưng p12</t>
+  </si>
+  <si>
+    <t>HD022895</t>
+  </si>
+  <si>
+    <t>1123 quốc lộ la, tân tạo, chung cư an gia the star</t>
+  </si>
+  <si>
+    <t>Nguyễn Kim Ann</t>
+  </si>
+  <si>
+    <t>HD022824</t>
+  </si>
+  <si>
+    <t>Linh Chi Nguyễn</t>
+  </si>
+  <si>
+    <t>HD022915</t>
+  </si>
+  <si>
+    <t>54/24 đường 281 lý thường kiệt phường 15</t>
+  </si>
+  <si>
+    <t>Ivy Huyền</t>
+  </si>
+  <si>
+    <t>Số 5 Nhất Chi Mai phường 13</t>
+  </si>
+  <si>
+    <t>NGAY 23-5</t>
+  </si>
+  <si>
+    <t>HD023142</t>
+  </si>
+  <si>
+    <t>404 VÕ VĂN TẦN</t>
+  </si>
+  <si>
+    <t>23-05-2026</t>
+  </si>
+  <si>
+    <t>Bảo Như</t>
+  </si>
+  <si>
+    <t>HD023066</t>
+  </si>
+  <si>
+    <t>e208 nguyễn hữu cảnh p22 toà nhà landmark 3</t>
+  </si>
+  <si>
+    <t>HD023055</t>
+  </si>
+  <si>
+    <t>AT 23-05</t>
+  </si>
+  <si>
+    <t>HD023069</t>
+  </si>
+  <si>
+    <t>HƯNG (hàng của Huyền Jendy)</t>
+  </si>
+  <si>
+    <t>HD023099</t>
+  </si>
+  <si>
+    <t>borameyyy</t>
+  </si>
+  <si>
+    <t>HD023106</t>
+  </si>
+  <si>
+    <t>oanh fb Duong Tram</t>
+  </si>
+  <si>
+    <t>HD023118</t>
+  </si>
+  <si>
+    <t>HD023108</t>
+  </si>
+  <si>
+    <t>TONY ĐI ÚC</t>
+  </si>
+  <si>
+    <t>HD023116</t>
+  </si>
+  <si>
+    <t>965/16/11 QUANG TRUNG</t>
+  </si>
+  <si>
+    <t>HD022813</t>
+  </si>
+  <si>
+    <t>Trinh Trần</t>
+  </si>
+  <si>
+    <t>HD022990</t>
+  </si>
+  <si>
+    <t>Lê Chi</t>
+  </si>
+  <si>
+    <t>HD023140</t>
+  </si>
+  <si>
+    <t>270 quốc lộ 50 p6</t>
+  </si>
+  <si>
+    <t>Ngọc Nhi</t>
+  </si>
+  <si>
+    <t>HD023141</t>
+  </si>
+  <si>
+    <t>HD023115</t>
+  </si>
+  <si>
+    <t>Mai Chi</t>
+  </si>
+  <si>
+    <t>Phương Trang</t>
+  </si>
+  <si>
+    <t>HD023132</t>
+  </si>
+  <si>
+    <t>Như Ý Nguyễn</t>
+  </si>
+  <si>
+    <t>HD023113</t>
+  </si>
+  <si>
+    <t>24 Yên Thế, Phường 2</t>
+  </si>
+  <si>
+    <t>Cúc Phan</t>
+  </si>
+  <si>
+    <t>HD023112</t>
+  </si>
+  <si>
+    <t>A 12 liên ấp 1-2 vĩnh lộc b</t>
+  </si>
+  <si>
+    <t>HD023096</t>
+  </si>
+  <si>
+    <t>HD023127</t>
+  </si>
+  <si>
+    <t>183/26 nguyễn hữu cảnh, f22</t>
+  </si>
+  <si>
+    <t>NGÂN HÀ</t>
+  </si>
+  <si>
+    <t>HÀ VY</t>
+  </si>
+  <si>
+    <t>CAYLA</t>
+  </si>
+  <si>
+    <t>HD023121</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, thới an</t>
+  </si>
+  <si>
+    <t>92 nguyễn hữu cảnh p.22 (cc sg pearl toà sapphire 1)</t>
+  </si>
+  <si>
+    <t>Trang Lê (note nhận đồ giúp chang)</t>
+  </si>
+  <si>
+    <t>482/10/26 nơ trang Long, p13</t>
+  </si>
+  <si>
+    <t>HD023045</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
+  </si>
+  <si>
+    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
+  </si>
+  <si>
+    <t>Express M Village Nguyễn Du, Phòng 602</t>
+  </si>
+  <si>
+    <t>346 bến vân đồn p1 Chung cư goldview a2</t>
+  </si>
+  <si>
+    <t>41 Lê Quang Chiểu, Hiệp Tân</t>
+  </si>
+  <si>
+    <t>22A truong dinh</t>
+  </si>
+  <si>
+    <t>363 Hùng Vương, An Đông</t>
+  </si>
+  <si>
+    <t>HD023061</t>
+  </si>
+  <si>
+    <t>215 nguyễn thị minh khai</t>
+  </si>
+  <si>
+    <t>189b/a29 công quỳnh phường nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>40 đường 53 p10</t>
   </si>
 </sst>
 </file>
@@ -5316,7 +5696,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5352,6 +5732,16 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD0D0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -5381,9 +5771,9 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6912,7 +7302,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I56" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -16920,10 +17310,12 @@
   <dimension ref="A1:Q43"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="49.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="76.85546875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -16994,13 +17386,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>1730</v>
+        <v>1643</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>1731</v>
+        <v>1644</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>1732</v>
+        <v>1645</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>22</v>
@@ -17012,17 +17404,17 @@
         <v>30</v>
       </c>
       <c r="I3" s="8">
-        <f t="shared" ref="I3:I42" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I43" si="0">G3-H3</f>
         <v>820</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -17030,13 +17422,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1716</v>
+        <v>1650</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>77</v>
@@ -17058,7 +17450,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -17066,13 +17458,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1727</v>
+        <v>1651</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1647</v>
+        <v>1652</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>1728</v>
+        <v>1653</v>
       </c>
       <c r="F5" s="6" t="s">
         <v>102</v>
@@ -17084,7 +17476,7 @@
         <v>35</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" ref="I5" si="1">G5-H5</f>
+        <f t="shared" si="0"/>
         <v>4365</v>
       </c>
       <c r="J5" s="6" t="s">
@@ -17094,7 +17486,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="M5" s="6" t="s">
         <v>145</v>
@@ -17105,13 +17497,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>1648</v>
+        <v>1654</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>1649</v>
+        <v>1655</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>1714</v>
+        <v>1656</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>29</v>
@@ -17133,7 +17525,7 @@
         <v>24</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17141,13 +17533,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>1650</v>
+        <v>1657</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>1651</v>
+        <v>1658</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>1742</v>
+        <v>1659</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>22</v>
@@ -17163,13 +17555,13 @@
         <v>440</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K7" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L7" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17177,13 +17569,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>1652</v>
+        <v>1660</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>1653</v>
+        <v>1661</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>1733</v>
+        <v>1662</v>
       </c>
       <c r="F8" s="8" t="s">
         <v>85</v>
@@ -17199,13 +17591,13 @@
         <v>-25</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K8" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L8" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17213,13 +17605,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>1654</v>
+        <v>1663</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>1655</v>
+        <v>1664</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>1656</v>
+        <v>1665</v>
       </c>
       <c r="F9" s="8" t="s">
         <v>41</v>
@@ -17235,13 +17627,13 @@
         <v>820</v>
       </c>
       <c r="J9" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K9" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -17252,7 +17644,7 @@
         <v>966</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>1657</v>
+        <v>1666</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>968</v>
@@ -17277,7 +17669,7 @@
         <v>24</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17288,7 +17680,7 @@
         <v>891</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>1658</v>
+        <v>1667</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>1510</v>
@@ -17307,13 +17699,13 @@
         <v>890</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L11" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -17321,13 +17713,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1659</v>
+        <v>1668</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1660</v>
+        <v>1669</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1715</v>
+        <v>1670</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>81</v>
@@ -17349,7 +17741,7 @@
         <v>24</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -17357,13 +17749,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>1661</v>
+        <v>1671</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1662</v>
+        <v>1672</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>1663</v>
+        <v>1673</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>70</v>
@@ -17385,7 +17777,7 @@
         <v>24</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -17393,13 +17785,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1664</v>
+        <v>1674</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1665</v>
+        <v>1675</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1723</v>
+        <v>1676</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>308</v>
@@ -17421,7 +17813,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -17429,13 +17821,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1666</v>
+        <v>1677</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1667</v>
+        <v>1678</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>1668</v>
+        <v>1679</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>59</v>
@@ -17457,7 +17849,7 @@
         <v>24</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -17468,7 +17860,7 @@
         <v>1225</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1722</v>
+        <v>1680</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>1227</v>
@@ -17493,7 +17885,7 @@
         <v>24</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="17" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -17501,13 +17893,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1725</v>
+        <v>1681</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1669</v>
+        <v>1682</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1670</v>
+        <v>1683</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>98</v>
@@ -17529,7 +17921,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17537,13 +17929,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>1671</v>
+        <v>1684</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>1672</v>
+        <v>1685</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>1734</v>
+        <v>1686</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>85</v>
@@ -17559,13 +17951,13 @@
         <v>1830</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="19" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17573,13 +17965,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>1673</v>
+        <v>1687</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>1674</v>
+        <v>1688</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>1675</v>
+        <v>1689</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>85</v>
@@ -17595,13 +17987,13 @@
         <v>770</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="20" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -17609,13 +18001,13 @@
         <v>18</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1676</v>
+        <v>1690</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1677</v>
+        <v>1691</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>1678</v>
+        <v>1692</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>63</v>
@@ -17637,7 +18029,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="6" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="21" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -17645,13 +18037,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>1679</v>
+        <v>1693</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>1680</v>
+        <v>1694</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>1717</v>
+        <v>1695</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>48</v>
@@ -17673,7 +18065,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="22" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17681,13 +18073,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1737</v>
+        <v>1696</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1681</v>
+        <v>1697</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1682</v>
+        <v>1698</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>22</v>
@@ -17703,13 +18095,13 @@
         <v>1090</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="23" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17717,13 +18109,13 @@
         <v>18</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>1683</v>
+        <v>1699</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1684</v>
+        <v>1700</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>1743</v>
+        <v>1701</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>85</v>
@@ -17739,13 +18131,13 @@
         <v>-25</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="24" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17756,7 +18148,7 @@
         <v>1332</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>1685</v>
+        <v>1702</v>
       </c>
       <c r="E24" s="8" t="s">
         <v>1334</v>
@@ -17775,13 +18167,13 @@
         <v>740</v>
       </c>
       <c r="J24" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K24" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="25" spans="2:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -17789,13 +18181,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>1686</v>
+        <v>1703</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1687</v>
+        <v>1704</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>1724</v>
+        <v>1705</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>63</v>
@@ -17817,7 +18209,7 @@
         <v>24</v>
       </c>
       <c r="L25" s="6" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="26" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -17828,10 +18220,10 @@
         <v>150</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>1688</v>
+        <v>1706</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>1713</v>
+        <v>1707</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>77</v>
@@ -17853,7 +18245,7 @@
         <v>24</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="27" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17864,7 +18256,7 @@
         <v>1267</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>1689</v>
+        <v>1708</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>1269</v>
@@ -17883,13 +18275,13 @@
         <v>680</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K27" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L27" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="28" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17897,13 +18289,13 @@
         <v>18</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>1690</v>
+        <v>1709</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>1691</v>
+        <v>1710</v>
       </c>
       <c r="E28" s="8" t="s">
-        <v>1735</v>
+        <v>1711</v>
       </c>
       <c r="F28" s="8" t="s">
         <v>131</v>
@@ -17919,13 +18311,13 @@
         <v>490</v>
       </c>
       <c r="J28" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K28" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L28" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="29" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -17933,13 +18325,13 @@
         <v>18</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>1739</v>
+        <v>1712</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>1741</v>
+        <v>1713</v>
       </c>
       <c r="E29" s="8" t="s">
-        <v>1740</v>
+        <v>1714</v>
       </c>
       <c r="F29" s="8" t="s">
         <v>41</v>
@@ -17955,13 +18347,13 @@
         <v>-30</v>
       </c>
       <c r="J29" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K29" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L29" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="30" spans="2:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -17969,13 +18361,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>1692</v>
+        <v>1715</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>1693</v>
+        <v>1716</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>1694</v>
+        <v>1717</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>81</v>
@@ -17997,7 +18389,7 @@
         <v>24</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="31" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -18005,13 +18397,13 @@
         <v>18</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>1695</v>
+        <v>1718</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>1696</v>
+        <v>1719</v>
       </c>
       <c r="E31" s="8" t="s">
-        <v>1736</v>
+        <v>1720</v>
       </c>
       <c r="F31" s="8" t="s">
         <v>59</v>
@@ -18027,13 +18419,13 @@
         <v>-25</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K31" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L31" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="32" spans="2:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -18041,13 +18433,13 @@
         <v>18</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>1697</v>
+        <v>1721</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>1698</v>
+        <v>1722</v>
       </c>
       <c r="E32" s="8" t="s">
-        <v>1738</v>
+        <v>1723</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>149</v>
@@ -18063,13 +18455,13 @@
         <v>490</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K32" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L32" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18077,10 +18469,10 @@
         <v>18</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>1699</v>
+        <v>1724</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>1700</v>
+        <v>1725</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>688</v>
@@ -18105,7 +18497,7 @@
         <v>24</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="34" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18113,13 +18505,13 @@
         <v>18</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>1720</v>
+        <v>1726</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>1701</v>
+        <v>1727</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>1721</v>
+        <v>1728</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>81</v>
@@ -18141,7 +18533,7 @@
         <v>24</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="35" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -18152,10 +18544,10 @@
         <v>1267</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>1702</v>
+        <v>1729</v>
       </c>
       <c r="E35" s="8" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="F35" s="8" t="s">
         <v>131</v>
@@ -18171,13 +18563,13 @@
         <v>960</v>
       </c>
       <c r="J35" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K35" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L35" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="36" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18185,13 +18577,13 @@
         <v>18</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>1703</v>
+        <v>1731</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>1704</v>
+        <v>1732</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>1705</v>
+        <v>1733</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>102</v>
@@ -18213,7 +18605,7 @@
         <v>24</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="37" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -18221,13 +18613,13 @@
         <v>18</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>1706</v>
+        <v>1734</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>1707</v>
+        <v>1735</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1708</v>
+        <v>1736</v>
       </c>
       <c r="F37" s="8" t="s">
         <v>41</v>
@@ -18243,13 +18635,13 @@
         <v>990</v>
       </c>
       <c r="J37" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K37" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L37" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="38" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -18257,13 +18649,13 @@
         <v>18</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>1709</v>
+        <v>1737</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>1710</v>
+        <v>1738</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1711</v>
+        <v>1739</v>
       </c>
       <c r="F38" s="8" t="s">
         <v>22</v>
@@ -18279,13 +18671,13 @@
         <v>830</v>
       </c>
       <c r="J38" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K38" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L38" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="39" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -18296,10 +18688,10 @@
         <v>18</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>1712</v>
+        <v>1740</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>1726</v>
+        <v>1741</v>
       </c>
       <c r="F39" s="6" t="s">
         <v>59</v>
@@ -18321,7 +18713,7 @@
         <v>24</v>
       </c>
       <c r="L39" s="6" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="40" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -18351,13 +18743,13 @@
         <v>0</v>
       </c>
       <c r="J40" s="8" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="K40" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L40" s="8" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="41" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18393,7 +18785,7 @@
         <v>24</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="42" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -18404,10 +18796,10 @@
         <v>18</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>1718</v>
+        <v>1742</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>1719</v>
+        <v>1743</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>77</v>
@@ -18429,58 +18821,2158 @@
         <v>24</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>1644</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C43" s="15" t="s">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="11" t="s">
         <v>1136</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="11" t="s">
         <v>1744</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="11" t="s">
         <v>1138</v>
       </c>
-      <c r="F43" s="16">
+      <c r="F43" s="15">
         <v>7</v>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="15">
         <v>810</v>
       </c>
-      <c r="H43" s="16">
+      <c r="H43" s="15">
         <v>30</v>
       </c>
-      <c r="I43" s="16">
-        <f>G43-H43</f>
+      <c r="I43" s="15">
+        <f t="shared" si="0"/>
         <v>780</v>
       </c>
-      <c r="J43" s="15" t="s">
+      <c r="J43" s="11" t="s">
         <v>1131</v>
       </c>
-      <c r="K43" s="15" t="s">
-        <v>24</v>
-      </c>
-      <c r="L43" s="15" t="s">
+      <c r="K43" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="11" t="s">
         <v>1124</v>
       </c>
-      <c r="M43" s="17" t="s">
+      <c r="M43" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="N43" s="17" t="s">
+      <c r="N43" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="O43" s="17" t="s">
+      <c r="O43" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="P43" s="17" t="s">
+      <c r="P43" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="Q43" s="15">
+      <c r="Q43" s="11">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="58.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="3">
+        <v>910</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <v>890</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1748</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>1749</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>1750</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>25</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1752</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>1753</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1595</v>
+      </c>
+      <c r="H5" s="6">
+        <v>25</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="0"/>
+        <v>1570</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>1755</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>1756</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1155</v>
+      </c>
+      <c r="H6" s="3">
+        <v>25</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>1130</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1757</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="8">
+        <v>855</v>
+      </c>
+      <c r="H7" s="8">
+        <v>35</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>1760</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>1761</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="8">
+        <v>400</v>
+      </c>
+      <c r="H8" s="8">
+        <v>30</v>
+      </c>
+      <c r="I8" s="8">
+        <f t="shared" si="0"/>
+        <v>370</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9" s="8">
+        <v>1710</v>
+      </c>
+      <c r="H9" s="8">
+        <v>30</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="0"/>
+        <v>1680</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1765</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1766</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="8">
+        <v>330</v>
+      </c>
+      <c r="H11" s="8">
+        <v>30</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>300</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>1747</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>1769</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>1770</v>
+      </c>
+      <c r="F12" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>30</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K12" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1771</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1772</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1773</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3">
+        <v>915</v>
+      </c>
+      <c r="H13" s="3">
+        <v>25</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>864</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="8">
+        <v>860</v>
+      </c>
+      <c r="H14" s="8">
+        <v>30</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1776</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1777</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1778</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="8">
+        <v>690</v>
+      </c>
+      <c r="H15" s="8">
+        <v>30</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="8">
+        <v>920</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>1782</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>1783</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>1784</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G17" s="6">
+        <v>915</v>
+      </c>
+      <c r="H17" s="6">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>785</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G18" s="8">
+        <v>820</v>
+      </c>
+      <c r="H18" s="8">
+        <v>30</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>1747</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>1787</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>1786</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="8">
+        <v>660</v>
+      </c>
+      <c r="H19" s="8">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>1747</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>1790</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="8">
+        <v>510</v>
+      </c>
+      <c r="H20" s="8">
+        <v>30</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="3">
+        <v>2520</v>
+      </c>
+      <c r="H21" s="3">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>2490</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1793</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1794</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
+      </c>
+      <c r="H22" s="3">
+        <v>25</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1795</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1796</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1797</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="8">
+        <v>915</v>
+      </c>
+      <c r="H23" s="8">
+        <v>25</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>1798</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>1799</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>1800</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G24" s="6">
+        <v>1225</v>
+      </c>
+      <c r="H24" s="6">
+        <v>25</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="0"/>
+        <v>1200</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>865</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>1801</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>1802</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G25" s="8">
+        <v>850</v>
+      </c>
+      <c r="H25" s="8">
+        <v>30</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>1804</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G26" s="6">
+        <v>855</v>
+      </c>
+      <c r="H26" s="6">
+        <v>25</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1805</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1806</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1807</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="G27" s="8">
+        <v>865</v>
+      </c>
+      <c r="H27" s="8">
+        <v>25</v>
+      </c>
+      <c r="I27" s="8">
+        <f t="shared" si="0"/>
+        <v>840</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>1758</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1808</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>1809</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="3">
+        <v>40</v>
+      </c>
+      <c r="H28" s="3">
+        <v>40</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>1551</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>626</v>
+      </c>
+      <c r="F29" s="11">
+        <v>1</v>
+      </c>
+      <c r="G29" s="11">
+        <v>25</v>
+      </c>
+      <c r="H29" s="11">
+        <v>25</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>1500</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+  <dimension ref="A1:P28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="57.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1810</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>1811</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1812</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G3" s="6">
+        <v>1855</v>
+      </c>
+      <c r="H3" s="6">
+        <v>25</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <v>1830</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="3">
+        <v>810</v>
+      </c>
+      <c r="H4" s="3">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>1612</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="8">
+        <v>785</v>
+      </c>
+      <c r="H5" s="8">
+        <v>30</v>
+      </c>
+      <c r="I5" s="8">
+        <f t="shared" si="0"/>
+        <v>755</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>1819</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1550</v>
+      </c>
+      <c r="H6" s="8">
+        <v>30</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="0"/>
+        <v>1520</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>1821</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>1733</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="3">
+        <v>845</v>
+      </c>
+      <c r="H7" s="3">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1822</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1823</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>1862</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1824</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1825</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>1863</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>891</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>1826</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>1864</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>25</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>1855</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1828</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1829</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>1830</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="3">
+        <v>920</v>
+      </c>
+      <c r="H13" s="3">
+        <v>30</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>1831</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>1832</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0</v>
+      </c>
+      <c r="H14" s="6">
+        <v>25</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G15" s="8">
+        <v>820</v>
+      </c>
+      <c r="H15" s="8">
+        <v>30</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1836</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1837</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1856</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" s="3">
+        <v>500</v>
+      </c>
+      <c r="H16" s="3">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>927</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>1838</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>1866</v>
+      </c>
+      <c r="F17" s="7">
+        <v>5</v>
+      </c>
+      <c r="G17" s="6">
+        <v>0</v>
+      </c>
+      <c r="H17" s="6">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6">
+        <v>-25</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>1839</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>1867</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>1868</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="6">
+        <v>845</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>1841</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G19" s="6">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6">
+        <v>25</v>
+      </c>
+      <c r="I19" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>1859</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>1860</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="3">
+        <v>25</v>
+      </c>
+      <c r="H20" s="3">
+        <v>25</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1813</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>1842</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>1843</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>1844</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6">
+        <v>25</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G22" s="8">
+        <v>1025</v>
+      </c>
+      <c r="H22" s="8">
+        <v>35</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G23" s="8">
+        <v>820</v>
+      </c>
+      <c r="H23" s="8">
+        <v>30</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>1813</v>
+      </c>
+      <c r="M23" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1850</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
+        <v>20</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>1870</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="8">
+        <v>1400</v>
+      </c>
+      <c r="H25" s="8">
+        <v>30</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="0"/>
+        <v>1370</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>1818</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="3">
+        <v>30</v>
+      </c>
+      <c r="H26" s="3">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>1852</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>1858</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="3">
+        <v>1575</v>
+      </c>
+      <c r="H27" s="3">
+        <v>25</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>1550</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>40</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>1813</v>
       </c>
     </row>
   </sheetData>
@@ -20780,7 +23272,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I55" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>2090</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -27963,7 +30455,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" ref="I35:I58" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>-30</v>
       </c>
       <c r="J35" s="8" t="s">

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CB8076F-6EF0-49AA-B0C2-284D9AE24792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DF3EDC-0EFD-4B8D-B6CA-60663BD1634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -32,6 +32,9 @@
     <sheet name="21-05" sheetId="21" r:id="rId17"/>
     <sheet name="22-05" sheetId="22" r:id="rId18"/>
     <sheet name="23-05" sheetId="23" r:id="rId19"/>
+    <sheet name="25-05" sheetId="24" r:id="rId20"/>
+    <sheet name="26-05" sheetId="25" r:id="rId21"/>
+    <sheet name="27-05" sheetId="26" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5893" uniqueCount="1871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6814" uniqueCount="2113">
   <si>
     <t>THU 6</t>
   </si>
@@ -5489,6 +5492,9 @@
     <t>NGAY 23-5</t>
   </si>
   <si>
+    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
+  </si>
+  <si>
     <t>HD023142</t>
   </si>
   <si>
@@ -5528,15 +5534,30 @@
     <t>HD023106</t>
   </si>
   <si>
+    <t>Express M Village Nguyễn Du, Phòng 602</t>
+  </si>
+  <si>
     <t>oanh fb Duong Tram</t>
   </si>
   <si>
     <t>HD023118</t>
   </si>
   <si>
+    <t>346 bến vân đồn p1 Chung cư goldview a2</t>
+  </si>
+  <si>
     <t>HD023108</t>
   </si>
   <si>
+    <t>41 Lê Quang Chiểu, Hiệp Tân</t>
+  </si>
+  <si>
+    <t>HD023121</t>
+  </si>
+  <si>
+    <t>624 Lê Thị Riêng, thới an</t>
+  </si>
+  <si>
     <t>TONY ĐI ÚC</t>
   </si>
   <si>
@@ -5555,6 +5576,9 @@
     <t>HD022990</t>
   </si>
   <si>
+    <t>22A truong dinh</t>
+  </si>
+  <si>
     <t>Lê Chi</t>
   </si>
   <si>
@@ -5570,18 +5594,39 @@
     <t>HD023141</t>
   </si>
   <si>
+    <t>92 nguyễn hữu cảnh p.22 (cc sg pearl toà sapphire 1)</t>
+  </si>
+  <si>
     <t>HD023115</t>
   </si>
   <si>
+    <t>363 Hùng Vương, An Đông</t>
+  </si>
+  <si>
     <t>Mai Chi</t>
   </si>
   <si>
+    <t>HD023061</t>
+  </si>
+  <si>
+    <t>215 nguyễn thị minh khai</t>
+  </si>
+  <si>
     <t>Phương Trang</t>
   </si>
   <si>
     <t>HD023132</t>
   </si>
   <si>
+    <t>189b/a29 công quỳnh phường nguyễn cư trinh</t>
+  </si>
+  <si>
+    <t>HD023045</t>
+  </si>
+  <si>
+    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
+  </si>
+  <si>
     <t>Như Ý Nguyễn</t>
   </si>
   <si>
@@ -5603,6 +5648,9 @@
     <t>HD023096</t>
   </si>
   <si>
+    <t>Trang Lê (note nhận đồ giúp chang)</t>
+  </si>
+  <si>
     <t>HD023127</t>
   </si>
   <si>
@@ -5612,61 +5660,742 @@
     <t>NGÂN HÀ</t>
   </si>
   <si>
+    <t>40 đường 53 p10</t>
+  </si>
+  <si>
     <t>HÀ VY</t>
   </si>
   <si>
+    <t>482/10/26 nơ trang Long, p13</t>
+  </si>
+  <si>
     <t>CAYLA</t>
   </si>
   <si>
-    <t>HD023121</t>
-  </si>
-  <si>
-    <t>624 Lê Thị Riêng, thới an</t>
-  </si>
-  <si>
-    <t>92 nguyễn hữu cảnh p.22 (cc sg pearl toà sapphire 1)</t>
-  </si>
-  <si>
-    <t>Trang Lê (note nhận đồ giúp chang)</t>
-  </si>
-  <si>
-    <t>482/10/26 nơ trang Long, p13</t>
-  </si>
-  <si>
-    <t>HD023045</t>
-  </si>
-  <si>
-    <t>22/31/4 đường số 21, Phường 8 (phường Thông Tây Hội mới)</t>
-  </si>
-  <si>
-    <t>thanh (NHẬN HÀNG CHO TRÀ LY)</t>
-  </si>
-  <si>
-    <t>Express M Village Nguyễn Du, Phòng 602</t>
-  </si>
-  <si>
-    <t>346 bến vân đồn p1 Chung cư goldview a2</t>
-  </si>
-  <si>
-    <t>41 Lê Quang Chiểu, Hiệp Tân</t>
-  </si>
-  <si>
-    <t>22A truong dinh</t>
-  </si>
-  <si>
-    <t>363 Hùng Vương, An Đông</t>
-  </si>
-  <si>
-    <t>HD023061</t>
-  </si>
-  <si>
-    <t>215 nguyễn thị minh khai</t>
-  </si>
-  <si>
-    <t>189b/a29 công quỳnh phường nguyễn cư trinh</t>
-  </si>
-  <si>
-    <t>40 đường 53 p10</t>
+    <t>NGAY 25-5</t>
+  </si>
+  <si>
+    <t>HD023484</t>
+  </si>
+  <si>
+    <t>25-05-2026</t>
+  </si>
+  <si>
+    <t>Hồng Vân</t>
+  </si>
+  <si>
+    <t>HD023071</t>
+  </si>
+  <si>
+    <t>233 đồng khởi phường sài gòn</t>
+  </si>
+  <si>
+    <t>HD023217</t>
+  </si>
+  <si>
+    <t>Em hồng thuỷ, hàng của chị AMyp</t>
+  </si>
+  <si>
+    <t>HD023235</t>
+  </si>
+  <si>
+    <t>38 Giải Phóng, phường 4</t>
+  </si>
+  <si>
+    <t>Trần Mai Phương</t>
+  </si>
+  <si>
+    <t>HD023562</t>
+  </si>
+  <si>
+    <t>442 Tô Ký- Tân Chánh Hiệp</t>
+  </si>
+  <si>
+    <t>AT 25-05</t>
+  </si>
+  <si>
+    <t>HD022967</t>
+  </si>
+  <si>
+    <t>672 đường 3/2 P14</t>
+  </si>
+  <si>
+    <t>Zy Ka</t>
+  </si>
+  <si>
+    <t>HD023410</t>
+  </si>
+  <si>
+    <t>9 nguyễn trường tộ, p12</t>
+  </si>
+  <si>
+    <t>Thơm Thơm</t>
+  </si>
+  <si>
+    <t>HD023336</t>
+  </si>
+  <si>
+    <t>119 nguyễn văn công p. Hạnh thông</t>
+  </si>
+  <si>
+    <t>HD023204</t>
+  </si>
+  <si>
+    <t>Phương Thảo TA</t>
+  </si>
+  <si>
+    <t>HD023551</t>
+  </si>
+  <si>
+    <t>HD022939</t>
+  </si>
+  <si>
+    <t>Chung cư aview KDC 13C ấp 5 xã phong phú</t>
+  </si>
+  <si>
+    <t>Nguyễn Phùng Thảo Như - fb Karen Van</t>
+  </si>
+  <si>
+    <t>HD023580</t>
+  </si>
+  <si>
+    <t>799/2 Nguyễn kiệm p3</t>
+  </si>
+  <si>
+    <t>QP</t>
+  </si>
+  <si>
+    <t>HD021978</t>
+  </si>
+  <si>
+    <t>Số 28 KDC Nam Long, Thạnh Lộc</t>
+  </si>
+  <si>
+    <t>HD023578</t>
+  </si>
+  <si>
+    <t>Linh Phạm</t>
+  </si>
+  <si>
+    <t>HD023385</t>
+  </si>
+  <si>
+    <t>80/17 miếu gò xoài bình hưng hoà a</t>
+  </si>
+  <si>
+    <t>Thanh Hoài Hoàng</t>
+  </si>
+  <si>
+    <t>HD023530</t>
+  </si>
+  <si>
+    <t>7-9 Hải Thượng Lãn Ông, P chợ lớn</t>
+  </si>
+  <si>
+    <t>Khánh Ly</t>
+  </si>
+  <si>
+    <t>HD023225</t>
+  </si>
+  <si>
+    <t>67 Đg số 6, Kp4, phường Bình Trưng Tây</t>
+  </si>
+  <si>
+    <t>Chế Vân</t>
+  </si>
+  <si>
+    <t>HD023327</t>
+  </si>
+  <si>
+    <t>140b nguyễn văn trỗi p8</t>
+  </si>
+  <si>
+    <t>Minh Thoan</t>
+  </si>
+  <si>
+    <t>HD023208</t>
+  </si>
+  <si>
+    <t>195 tân hương p phú thọ hoà</t>
+  </si>
+  <si>
+    <t>HD023568</t>
+  </si>
+  <si>
+    <t>Thanh Nhàn</t>
+  </si>
+  <si>
+    <t>HD023483</t>
+  </si>
+  <si>
+    <t>59 trần hưng đạo, p.tân thành</t>
+  </si>
+  <si>
+    <t>HD023291</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí, phú thuận)</t>
+  </si>
+  <si>
+    <t>HD023507</t>
+  </si>
+  <si>
+    <t>Vũ Thị Hà</t>
+  </si>
+  <si>
+    <t>HD023340</t>
+  </si>
+  <si>
+    <t>20 Vũ Tông Phan, phường bình trưng</t>
+  </si>
+  <si>
+    <t>Phương Anna</t>
+  </si>
+  <si>
+    <t>HD023553</t>
+  </si>
+  <si>
+    <t>258/77/2 dương bá trạc, P2</t>
+  </si>
+  <si>
+    <t>HD023457</t>
+  </si>
+  <si>
+    <t>Số 2 đường 75, khu phố 2, tân phong</t>
+  </si>
+  <si>
+    <t>HD022968</t>
+  </si>
+  <si>
+    <t>Gia Hue</t>
+  </si>
+  <si>
+    <t>HD023414</t>
+  </si>
+  <si>
+    <t>24 tân hoà đông p14</t>
+  </si>
+  <si>
+    <t>HD023330</t>
+  </si>
+  <si>
+    <t>Lê Nhật Tâm</t>
+  </si>
+  <si>
+    <t>HD023331</t>
+  </si>
+  <si>
+    <t>271 Mã Lò phường Bình Trị Đông</t>
+  </si>
+  <si>
+    <t>HD023455</t>
+  </si>
+  <si>
+    <t>433/11/2 Lê Đức Thọ, Phường Gò Vấp (phường 17 cũ)</t>
+  </si>
+  <si>
+    <t>Phạm Tuyết</t>
+  </si>
+  <si>
+    <t>HD023561</t>
+  </si>
+  <si>
+    <t>Chung Cư Gia Phú (lô A),cuối Hẻm 219 đường Số 5, Khu Phố 7, Phường Bình Hưng Hòa</t>
+  </si>
+  <si>
+    <t>HD023569</t>
+  </si>
+  <si>
+    <t>Hồ Thanh Phương</t>
+  </si>
+  <si>
+    <t>HD023466</t>
+  </si>
+  <si>
+    <t>158/56/21 Phạm Văn Chiêu, phường 8</t>
+  </si>
+  <si>
+    <t>Julia Julia</t>
+  </si>
+  <si>
+    <t>HD023227</t>
+  </si>
+  <si>
+    <t>lô z01-02-03a KCN trong KCX tân thuận, phường tân thuận đông</t>
+  </si>
+  <si>
+    <t>HD023565</t>
+  </si>
+  <si>
+    <t>Số 242, Tân Kỳ Tân Quý, Phường Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD023334</t>
+  </si>
+  <si>
+    <t>Tiger Nhỏ _ Gia Huy</t>
+  </si>
+  <si>
+    <t>HD023468</t>
+  </si>
+  <si>
+    <t>2/11 đường Thiên Phước, phường 9</t>
+  </si>
+  <si>
+    <t>HD023354</t>
+  </si>
+  <si>
+    <t>Khuê</t>
+  </si>
+  <si>
+    <t>HD021688</t>
+  </si>
+  <si>
+    <t>38/9 thích quảng đức p15</t>
+  </si>
+  <si>
+    <t>HD023415</t>
+  </si>
+  <si>
+    <t>Hang</t>
+  </si>
+  <si>
+    <t>HD023317</t>
+  </si>
+  <si>
+    <t>75/2A nguyễn sỹ sách,p.15 cũ(tân sơn mới)</t>
+  </si>
+  <si>
+    <t>0967000176</t>
+  </si>
+  <si>
+    <t>HD023380</t>
+  </si>
+  <si>
+    <t>8/5b đỗ văn dậy</t>
+  </si>
+  <si>
+    <t>NGỌC DIỆP - fb Jenny Uyên</t>
+  </si>
+  <si>
+    <t>HD023210</t>
+  </si>
+  <si>
+    <t>30 trịnh đình thảo chung cư trung đông plaza</t>
+  </si>
+  <si>
+    <t>Anna Nguyen</t>
+  </si>
+  <si>
+    <t>HD023476</t>
+  </si>
+  <si>
+    <t>12a Nguyễn hữu thọ Phước kiểng Cc the park resident tòa b5</t>
+  </si>
+  <si>
+    <t>HD023571</t>
+  </si>
+  <si>
+    <t>Scenic Valley 1, Cổng Số 2, Kdc Phú Mỹ Hưng, Phường Tân Phú</t>
+  </si>
+  <si>
+    <t>Trần Thị Anh Đào</t>
+  </si>
+  <si>
+    <t>HD023440</t>
+  </si>
+  <si>
+    <t>333/35 Lý Thái Tổ, Phường 9</t>
+  </si>
+  <si>
+    <t>Nguyễn thị ánh ngọc</t>
+  </si>
+  <si>
+    <t>HD023541</t>
+  </si>
+  <si>
+    <t>B1805-B1806 block B ecogreen 39B nguyễn văn linh - tân thuận tây</t>
+  </si>
+  <si>
+    <t>(Tuấn) Nhận Dùm Xiaomei</t>
+  </si>
+  <si>
+    <t>HD023332</t>
+  </si>
+  <si>
+    <t>77/8/2 đường số 1, khu phố ông nhiêu, phường long trường</t>
+  </si>
+  <si>
+    <t>NGAY 26-5</t>
+  </si>
+  <si>
+    <t>NGUYÊN NGUYÊN</t>
+  </si>
+  <si>
+    <t>12 TÔN ĐẢN P13</t>
+  </si>
+  <si>
+    <t>26-05-2026</t>
+  </si>
+  <si>
+    <t>AT 26-05</t>
+  </si>
+  <si>
+    <t>NGÂN KIM</t>
+  </si>
+  <si>
+    <t>T8-20 mahattan vinhomes grand park, phường long bình</t>
+  </si>
+  <si>
+    <t>66 đường 17 p10</t>
+  </si>
+  <si>
+    <t>Nga Nga</t>
+  </si>
+  <si>
+    <t>HD023717</t>
+  </si>
+  <si>
+    <t>29b Nguyễn đình chiểu dakao</t>
+  </si>
+  <si>
+    <t>Minh Thư</t>
+  </si>
+  <si>
+    <t>HD023706</t>
+  </si>
+  <si>
+    <t>6/24 tân chánh hiệp 36, p trung mỹ tây</t>
+  </si>
+  <si>
+    <t>Trang Angels</t>
+  </si>
+  <si>
+    <t>HD023627</t>
+  </si>
+  <si>
+    <t>nhà 20 đường 2B phường Tân mỹ</t>
+  </si>
+  <si>
+    <t>Kỳ Kỳ</t>
+  </si>
+  <si>
+    <t>HD023748</t>
+  </si>
+  <si>
+    <t>Trường Tiểu học Vinschool Grand Park, Vinhome Grand Park</t>
+  </si>
+  <si>
+    <t>Nhi Le</t>
+  </si>
+  <si>
+    <t>HD023579</t>
+  </si>
+  <si>
+    <t>743/11/10 hong bang p6</t>
+  </si>
+  <si>
+    <t>Linh Mỹ</t>
+  </si>
+  <si>
+    <t>HD023715</t>
+  </si>
+  <si>
+    <t>50/2/8 đường số 2, phường 3</t>
+  </si>
+  <si>
+    <t>HDO1779701391142_472517</t>
+  </si>
+  <si>
+    <t>169/15 đường số 11 phường bình hưng hoà</t>
+  </si>
+  <si>
+    <t>Ngọc Thư</t>
+  </si>
+  <si>
+    <t>HD023656</t>
+  </si>
+  <si>
+    <t>400cd lê hồng phong p1</t>
+  </si>
+  <si>
+    <t>이 우준</t>
+  </si>
+  <si>
+    <t>HD023636</t>
+  </si>
+  <si>
+    <t>HD023631</t>
+  </si>
+  <si>
+    <t>Linh P Pham</t>
+  </si>
+  <si>
+    <t>HD023630</t>
+  </si>
+  <si>
+    <t>HD023620</t>
+  </si>
+  <si>
+    <t>129/34 Nguyễn Văn Công, phường 3, Phường Gò Vấp</t>
+  </si>
+  <si>
+    <t>Thanh Thanh</t>
+  </si>
+  <si>
+    <t>HD023734</t>
+  </si>
+  <si>
+    <t>Cozrum Homes Premier Residences 135/4 Nguyễn Cửu Vân, P.Gia Định</t>
+  </si>
+  <si>
+    <t>Kim ngân</t>
+  </si>
+  <si>
+    <t>HD023657</t>
+  </si>
+  <si>
+    <t>50 An Dương Vương,P.9</t>
+  </si>
+  <si>
+    <t>Huyền Trang Trần</t>
+  </si>
+  <si>
+    <t>39/34 dạ nam</t>
+  </si>
+  <si>
+    <t>Truc Le</t>
+  </si>
+  <si>
+    <t>HD023726</t>
+  </si>
+  <si>
+    <t>69 đường số 2 khu phố 1 p tam bình</t>
+  </si>
+  <si>
+    <t>Annie Annie</t>
+  </si>
+  <si>
+    <t>HD023732</t>
+  </si>
+  <si>
+    <t>110 đường 14 Him Lam tân hưng</t>
+  </si>
+  <si>
+    <t>Nguyen Minh Thu</t>
+  </si>
+  <si>
+    <t>HD023677</t>
+  </si>
+  <si>
+    <t>Số 2 đường số 51 p bình trưng đông</t>
+  </si>
+  <si>
+    <t>Thảo Ngân</t>
+  </si>
+  <si>
+    <t>HD023768</t>
+  </si>
+  <si>
+    <t>44/139 trần bình trọng</t>
+  </si>
+  <si>
+    <t>BN1356</t>
+  </si>
+  <si>
+    <t>HD023491</t>
+  </si>
+  <si>
+    <t>HD023733</t>
+  </si>
+  <si>
+    <t>32/11 Bùi Đình Tuý f12</t>
+  </si>
+  <si>
+    <t>FB HOÀNG THỦY</t>
+  </si>
+  <si>
+    <t>HD023619</t>
+  </si>
+  <si>
+    <t>86/36/3 PHỔ QUANG TÂN SƠN HÒA</t>
+  </si>
+  <si>
+    <t>NGAY 27-5</t>
+  </si>
+  <si>
+    <t>Nhận hộ fb Nguyễn Hà</t>
+  </si>
+  <si>
+    <t>AT 27-05</t>
+  </si>
+  <si>
+    <t>27-05-2026</t>
+  </si>
+  <si>
+    <t>HD023794</t>
+  </si>
+  <si>
+    <t>ng nhận QP</t>
+  </si>
+  <si>
+    <t>HD023827</t>
+  </si>
+  <si>
+    <t>số 28 khu kdc nam long thạnh lộc</t>
+  </si>
+  <si>
+    <t>HUYỀN NGUYỄN</t>
+  </si>
+  <si>
+    <t>HD023936</t>
+  </si>
+  <si>
+    <t>Giang Phạm</t>
+  </si>
+  <si>
+    <t>HD023787</t>
+  </si>
+  <si>
+    <t>136 hoàng hoa thám, p7</t>
+  </si>
+  <si>
+    <t>HD023906</t>
+  </si>
+  <si>
+    <t>77-89 nam kỳ khởi nghĩa bến thành</t>
+  </si>
+  <si>
+    <t>KimVy Phương Anh</t>
+  </si>
+  <si>
+    <t>HD023841</t>
+  </si>
+  <si>
+    <t>214/B14A nguyễn trãi, cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>HD023837</t>
+  </si>
+  <si>
+    <t>Can 32.07 - the Pegasuite 1- số 1002 tạ quang bửu, phường 5</t>
+  </si>
+  <si>
+    <t>HD023572</t>
+  </si>
+  <si>
+    <t>HD023905</t>
+  </si>
+  <si>
+    <t>HD023917</t>
+  </si>
+  <si>
+    <t>195 tân hương P phú thọ hoà</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Ngọc Hân</t>
+  </si>
+  <si>
+    <t>HD023783</t>
+  </si>
+  <si>
+    <t>512 phạm thế hiển p4</t>
+  </si>
+  <si>
+    <t>W24130 Miki (Chou)</t>
+  </si>
+  <si>
+    <t>HD023903</t>
+  </si>
+  <si>
+    <t>624 Lê thị riêng, thới an</t>
+  </si>
+  <si>
+    <t>Thiên An</t>
+  </si>
+  <si>
+    <t>Thao Thanh Nguyen</t>
+  </si>
+  <si>
+    <t>HD023781</t>
+  </si>
+  <si>
+    <t>53 trần đình xu p cầu kho</t>
+  </si>
+  <si>
+    <t>S$3164-Mrskill)</t>
+  </si>
+  <si>
+    <t>Khánh Như</t>
+  </si>
+  <si>
+    <t>HD023944</t>
+  </si>
+  <si>
+    <t>688/23/1c Hương Lộ 2, phường Bình Trị Đông A</t>
+  </si>
+  <si>
+    <t>HD023838</t>
+  </si>
+  <si>
+    <t>Hoàng Trang</t>
+  </si>
+  <si>
+    <t>HD023850</t>
+  </si>
+  <si>
+    <t>cô Loan fb Trịnh Trâm</t>
+  </si>
+  <si>
+    <t>HD023930</t>
+  </si>
+  <si>
+    <t>NHƯ THẢO</t>
+  </si>
+  <si>
+    <t>Ellie Quach</t>
+  </si>
+  <si>
+    <t>SỈ HƯƠNG TRẦN</t>
+  </si>
+  <si>
+    <t>HD023711</t>
+  </si>
+  <si>
+    <t>Thúy Nguyễn</t>
+  </si>
+  <si>
+    <t>598/10 điện biên phủ, p.22</t>
+  </si>
+  <si>
+    <t>8A Sông thương, Phường 2</t>
+  </si>
+  <si>
+    <t>GIA HUY nhận hộ ELIS NGUYỄN (singapore)</t>
+  </si>
+  <si>
+    <t>Số 8 Ba Vì, P4</t>
+  </si>
+  <si>
+    <t>259 đường 9a kdc Trung Sơn, Bình Hưng</t>
+  </si>
+  <si>
+    <t>HD022602</t>
+  </si>
+  <si>
+    <t>674 đường số 2, Phường 13</t>
+  </si>
+  <si>
+    <t>124/18/12 võ văn hát p long trường</t>
+  </si>
+  <si>
+    <t>1041/80/3/5 trần xuân soạn phường tân hưng</t>
+  </si>
+  <si>
+    <t>HD023884</t>
+  </si>
+  <si>
+    <t>D aqua 301 bình động, phú định</t>
   </si>
 </sst>
 </file>
@@ -5696,7 +6425,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5742,6 +6471,12 @@
         <fgColor rgb="FFFFD0D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -5755,7 +6490,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -5774,6 +6509,9 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -19961,10 +20699,12 @@
   <dimension ref="A1:P28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="32.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="57.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -20036,13 +20776,13 @@
         <v>18</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>1861</v>
+        <v>1811</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>98</v>
@@ -20054,7 +20794,7 @@
         <v>25</v>
       </c>
       <c r="I3" s="6">
-        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <f t="shared" ref="I3:I16" si="0">G3-H3</f>
         <v>1830</v>
       </c>
       <c r="J3" s="6" t="s">
@@ -20064,7 +20804,7 @@
         <v>24</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20072,13 +20812,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>81</v>
@@ -20100,7 +20840,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -20111,7 +20851,7 @@
         <v>1612</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="E5" s="8" t="s">
         <v>1614</v>
@@ -20130,13 +20870,13 @@
         <v>755</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K5" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="M5" s="8" t="s">
         <v>138</v>
@@ -20150,7 +20890,7 @@
         <v>115</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="E6" s="8" t="s">
         <v>117</v>
@@ -20169,13 +20909,13 @@
         <v>1520</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K6" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L6" s="8" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20183,10 +20923,10 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>1733</v>
@@ -20211,7 +20951,7 @@
         <v>24</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -20219,13 +20959,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>1862</v>
+        <v>1825</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>63</v>
@@ -20247,7 +20987,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -20255,13 +20995,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>1863</v>
+        <v>1828</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>186</v>
@@ -20283,7 +21023,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -20294,10 +21034,10 @@
         <v>891</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>1864</v>
+        <v>1830</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>85</v>
@@ -20313,13 +21053,13 @@
         <v>-25</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20330,10 +21070,10 @@
         <v>53</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>1854</v>
+        <v>1831</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>1855</v>
+        <v>1832</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>29</v>
@@ -20355,7 +21095,7 @@
         <v>24</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20363,13 +21103,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>1827</v>
+        <v>1833</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>1828</v>
+        <v>1834</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>1829</v>
+        <v>1835</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>70</v>
@@ -20391,7 +21131,7 @@
         <v>24</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20402,7 +21142,7 @@
         <v>1396</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>1830</v>
+        <v>1836</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>1398</v>
@@ -20427,7 +21167,7 @@
         <v>24</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -20435,13 +21175,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1831</v>
+        <v>1837</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1832</v>
+        <v>1838</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>1865</v>
+        <v>1839</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>98</v>
@@ -20463,7 +21203,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -20471,13 +21211,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>1833</v>
+        <v>1840</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>1834</v>
+        <v>1841</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>1835</v>
+        <v>1842</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>41</v>
@@ -20493,13 +21233,13 @@
         <v>790</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K15" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L15" s="8" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20507,13 +21247,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>1836</v>
+        <v>1843</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>1837</v>
+        <v>1844</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>1856</v>
+        <v>1845</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>81</v>
@@ -20535,7 +21275,7 @@
         <v>24</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="17" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -20546,10 +21286,10 @@
         <v>927</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1838</v>
+        <v>1846</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>1866</v>
+        <v>1847</v>
       </c>
       <c r="F17" s="7">
         <v>5</v>
@@ -20570,7 +21310,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="18" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -20578,13 +21318,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1839</v>
+        <v>1848</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1867</v>
+        <v>1849</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>1868</v>
+        <v>1850</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>98</v>
@@ -20596,7 +21336,7 @@
         <v>25</v>
       </c>
       <c r="I18" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I18:I28" si="1">G18-H18</f>
         <v>820</v>
       </c>
       <c r="J18" s="6" t="s">
@@ -20606,7 +21346,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="19" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -20614,13 +21354,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1840</v>
+        <v>1851</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1841</v>
+        <v>1852</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>1869</v>
+        <v>1853</v>
       </c>
       <c r="F19" s="7" t="s">
         <v>63</v>
@@ -20632,7 +21372,7 @@
         <v>25</v>
       </c>
       <c r="I19" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="J19" s="6" t="s">
@@ -20642,7 +21382,7 @@
         <v>24</v>
       </c>
       <c r="L19" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="20" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20653,10 +21393,10 @@
         <v>1754</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>1859</v>
+        <v>1854</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>1860</v>
+        <v>1855</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>70</v>
@@ -20668,7 +21408,7 @@
         <v>25</v>
       </c>
       <c r="I20" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J20" s="3" t="s">
@@ -20678,7 +21418,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="M20" s="3" t="s">
         <v>138</v>
@@ -20689,13 +21429,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1842</v>
+        <v>1856</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1843</v>
+        <v>1857</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>1844</v>
+        <v>1858</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>102</v>
@@ -20707,7 +21447,7 @@
         <v>25</v>
       </c>
       <c r="I21" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-25</v>
       </c>
       <c r="J21" s="6" t="s">
@@ -20717,7 +21457,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="22" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -20725,13 +21465,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>1845</v>
+        <v>1859</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>1846</v>
+        <v>1860</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>1847</v>
+        <v>1861</v>
       </c>
       <c r="F22" s="9" t="s">
         <v>52</v>
@@ -20743,17 +21483,17 @@
         <v>35</v>
       </c>
       <c r="I22" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>990</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="23" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -20764,7 +21504,7 @@
         <v>1779</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>1848</v>
+        <v>1862</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>1781</v>
@@ -20779,17 +21519,17 @@
         <v>30</v>
       </c>
       <c r="I23" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>790</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="M23" s="8" t="s">
         <v>145</v>
@@ -20800,13 +21540,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>1857</v>
+        <v>1863</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>1849</v>
+        <v>1864</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>1850</v>
+        <v>1865</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>81</v>
@@ -20818,7 +21558,7 @@
         <v>20</v>
       </c>
       <c r="I24" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-20</v>
       </c>
       <c r="J24" s="3" t="s">
@@ -20828,7 +21568,7 @@
         <v>24</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="25" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -20839,10 +21579,10 @@
         <v>18</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>1851</v>
+        <v>1866</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>1870</v>
+        <v>1867</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>127</v>
@@ -20854,17 +21594,17 @@
         <v>30</v>
       </c>
       <c r="I25" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1370</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="26" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20890,7 +21630,7 @@
         <v>30</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="J26" s="3" t="s">
@@ -20900,7 +21640,7 @@
         <v>24</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="27" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20911,10 +21651,10 @@
         <v>18</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>1852</v>
+        <v>1868</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>1858</v>
+        <v>1869</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>81</v>
@@ -20926,7 +21666,7 @@
         <v>25</v>
       </c>
       <c r="I27" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1550</v>
       </c>
       <c r="J27" s="3" t="s">
@@ -20936,7 +21676,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="28" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -20947,7 +21687,7 @@
         <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>1853</v>
+        <v>1870</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>511</v>
@@ -20962,7 +21702,7 @@
         <v>40</v>
       </c>
       <c r="I28" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-40</v>
       </c>
       <c r="J28" s="3" t="s">
@@ -20972,7 +21712,7 @@
         <v>24</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
     </row>
   </sheetData>
@@ -21995,6 +22735,4126 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+  <dimension ref="A1:P55"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="36.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="62.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I34" si="0">G3-H3</f>
+        <v>-20</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>1876</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>25</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>1225</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>1227</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1100</v>
+      </c>
+      <c r="H5" s="6">
+        <v>20</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>1878</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>1879</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>1880</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="6">
+        <v>995</v>
+      </c>
+      <c r="H6" s="6">
+        <v>25</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="8">
+        <v>820</v>
+      </c>
+      <c r="H7" s="8">
+        <v>30</v>
+      </c>
+      <c r="I7" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G8" s="6">
+        <v>770</v>
+      </c>
+      <c r="H8" s="6">
+        <v>0</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G9" s="6">
+        <v>845</v>
+      </c>
+      <c r="H9" s="6">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1855</v>
+      </c>
+      <c r="H10" s="3">
+        <v>25</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>1830</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>1893</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="8">
+        <v>470</v>
+      </c>
+      <c r="H11" s="8">
+        <v>30</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>1895</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="8">
+        <v>505</v>
+      </c>
+      <c r="H12" s="8">
+        <v>25</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>1751</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>1897</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="8">
+        <v>5640</v>
+      </c>
+      <c r="H13" s="8">
+        <v>55</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
+        <v>5585</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1898</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>1899</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1900</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G14" s="3">
+        <v>785</v>
+      </c>
+      <c r="H14" s="3">
+        <v>25</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>1901</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>1902</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>1903</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="8">
+        <v>0</v>
+      </c>
+      <c r="H15" s="8">
+        <v>30</v>
+      </c>
+      <c r="I15" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1208</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>1904</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1210</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="8">
+        <v>850</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>1905</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>1906</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>1907</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="8">
+        <v>690</v>
+      </c>
+      <c r="H17" s="8">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>1908</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>1910</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G18" s="8">
+        <v>845</v>
+      </c>
+      <c r="H18" s="8">
+        <v>25</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>1911</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>1912</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>1913</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1110</v>
+      </c>
+      <c r="H19" s="3">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G20" s="6">
+        <v>1010</v>
+      </c>
+      <c r="H20" s="6">
+        <v>20</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>1919</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G21" s="8">
+        <v>465</v>
+      </c>
+      <c r="H21" s="8">
+        <v>25</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1863</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1865</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="3">
+        <v>60</v>
+      </c>
+      <c r="H22" s="3">
+        <v>20</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="0"/>
+        <v>40</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>1921</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>1922</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>1923</v>
+      </c>
+      <c r="F23" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23" s="8">
+        <v>845</v>
+      </c>
+      <c r="H23" s="8">
+        <v>25</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="24" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>1925</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="8">
+        <v>990</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>960</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="25" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>1926</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G25" s="3">
+        <v>850</v>
+      </c>
+      <c r="H25" s="3">
+        <v>0</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="26" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>1927</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>1928</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1929</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G26" s="3">
+        <v>880</v>
+      </c>
+      <c r="H26" s="3">
+        <v>30</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="27" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>1931</v>
+      </c>
+      <c r="E27" s="8" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G27" s="8">
+        <v>1710</v>
+      </c>
+      <c r="H27" s="8">
+        <v>30</v>
+      </c>
+      <c r="I27" s="8">
+        <f t="shared" si="0"/>
+        <v>1680</v>
+      </c>
+      <c r="J27" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="28" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>767</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E28" s="8" t="s">
+        <v>1934</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G28" s="8">
+        <v>1260</v>
+      </c>
+      <c r="H28" s="8">
+        <v>30</v>
+      </c>
+      <c r="I28" s="8">
+        <f t="shared" si="0"/>
+        <v>1230</v>
+      </c>
+      <c r="J28" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="29" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>1575</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>1935</v>
+      </c>
+      <c r="E29" s="8" t="s">
+        <v>1577</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G29" s="8">
+        <v>1735</v>
+      </c>
+      <c r="H29" s="8">
+        <v>25</v>
+      </c>
+      <c r="I29" s="8">
+        <f t="shared" si="0"/>
+        <v>1710</v>
+      </c>
+      <c r="J29" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K29" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="30" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>1936</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>1937</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>1938</v>
+      </c>
+      <c r="F30" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G30" s="8">
+        <v>995</v>
+      </c>
+      <c r="H30" s="8">
+        <v>25</v>
+      </c>
+      <c r="I30" s="8">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="31" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1022</v>
+      </c>
+      <c r="D31" s="8" t="s">
+        <v>1939</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G31" s="8">
+        <v>470</v>
+      </c>
+      <c r="H31" s="8">
+        <v>30</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="32" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D32" s="8" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E32" s="8" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G32" s="8">
+        <v>520</v>
+      </c>
+      <c r="H32" s="8">
+        <v>30</v>
+      </c>
+      <c r="I32" s="8">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J32" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L32" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="33" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>1944</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G33" s="3">
+        <v>995</v>
+      </c>
+      <c r="H33" s="3">
+        <v>25</v>
+      </c>
+      <c r="I33" s="3">
+        <f t="shared" si="0"/>
+        <v>970</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="34" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D34" s="8" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>1947</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G34" s="8">
+        <v>0</v>
+      </c>
+      <c r="H34" s="8">
+        <v>30</v>
+      </c>
+      <c r="I34" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J34" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K34" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="35" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G35" s="3">
+        <v>725</v>
+      </c>
+      <c r="H35" s="3">
+        <v>25</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <v>700</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="36" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>1951</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G36" s="3">
+        <v>845</v>
+      </c>
+      <c r="H36" s="3">
+        <v>25</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="37" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>1953</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>1954</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G37" s="8">
+        <v>810</v>
+      </c>
+      <c r="H37" s="8">
+        <v>30</v>
+      </c>
+      <c r="I37" s="8">
+        <f t="shared" si="1"/>
+        <v>780</v>
+      </c>
+      <c r="J37" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L37" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="38" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38" s="8">
+        <v>795</v>
+      </c>
+      <c r="H38" s="8">
+        <v>25</v>
+      </c>
+      <c r="I38" s="8">
+        <f t="shared" si="1"/>
+        <v>770</v>
+      </c>
+      <c r="J38" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="39" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>1957</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G39" s="8">
+        <v>995</v>
+      </c>
+      <c r="H39" s="8">
+        <v>25</v>
+      </c>
+      <c r="I39" s="8">
+        <f t="shared" si="1"/>
+        <v>970</v>
+      </c>
+      <c r="J39" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L39" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="40" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G40" s="6">
+        <v>0</v>
+      </c>
+      <c r="H40" s="6">
+        <v>25</v>
+      </c>
+      <c r="I40" s="6">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J40" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L40" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="41" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>1837</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>1839</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G41" s="6">
+        <v>2230</v>
+      </c>
+      <c r="H41" s="6">
+        <v>25</v>
+      </c>
+      <c r="I41" s="6">
+        <f t="shared" si="1"/>
+        <v>2205</v>
+      </c>
+      <c r="J41" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L41" s="6" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>1962</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G42" s="6">
+        <v>390</v>
+      </c>
+      <c r="H42" s="6">
+        <v>20</v>
+      </c>
+      <c r="I42" s="6">
+        <f t="shared" si="1"/>
+        <v>370</v>
+      </c>
+      <c r="J42" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L42" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="43" spans="2:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>704</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>1886</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G43" s="6">
+        <v>845</v>
+      </c>
+      <c r="H43" s="6">
+        <v>25</v>
+      </c>
+      <c r="I43" s="6">
+        <f t="shared" si="1"/>
+        <v>820</v>
+      </c>
+      <c r="J43" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L43" s="6" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="44" spans="2:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>1966</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G44" s="3">
+        <v>715</v>
+      </c>
+      <c r="H44" s="3">
+        <v>25</v>
+      </c>
+      <c r="I44" s="3">
+        <f t="shared" si="1"/>
+        <v>690</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="45" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C45" s="18" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G45" s="8">
+        <v>865</v>
+      </c>
+      <c r="H45" s="8">
+        <v>35</v>
+      </c>
+      <c r="I45" s="8">
+        <f t="shared" si="1"/>
+        <v>830</v>
+      </c>
+      <c r="J45" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="46" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>1972</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>1973</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>1974</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G46" s="8">
+        <v>0</v>
+      </c>
+      <c r="H46" s="8">
+        <v>25</v>
+      </c>
+      <c r="I46" s="8">
+        <f t="shared" si="1"/>
+        <v>-25</v>
+      </c>
+      <c r="J46" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="47" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>1975</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>1977</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G47" s="8">
+        <v>2760</v>
+      </c>
+      <c r="H47" s="8">
+        <v>35</v>
+      </c>
+      <c r="I47" s="8">
+        <f t="shared" si="1"/>
+        <v>2725</v>
+      </c>
+      <c r="J47" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K47" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="48" spans="2:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>1979</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G48" s="8">
+        <v>820</v>
+      </c>
+      <c r="H48" s="8">
+        <v>30</v>
+      </c>
+      <c r="I48" s="8">
+        <f t="shared" si="1"/>
+        <v>790</v>
+      </c>
+      <c r="J48" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K48" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L48" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>1980</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>1981</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>1982</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G49" s="6">
+        <v>465</v>
+      </c>
+      <c r="H49" s="6">
+        <v>25</v>
+      </c>
+      <c r="I49" s="6">
+        <f t="shared" si="1"/>
+        <v>440</v>
+      </c>
+      <c r="J49" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L49" s="6" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F50" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G50" s="8">
+        <v>810</v>
+      </c>
+      <c r="H50" s="8">
+        <v>30</v>
+      </c>
+      <c r="I50" s="8">
+        <f t="shared" si="1"/>
+        <v>780</v>
+      </c>
+      <c r="J50" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L50" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>1986</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>1987</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>1988</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="G51" s="8">
+        <v>0</v>
+      </c>
+      <c r="H51" s="8">
+        <v>30</v>
+      </c>
+      <c r="I51" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J51" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K51" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G52" s="3">
+        <v>2450</v>
+      </c>
+      <c r="H52" s="3">
+        <v>30</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="1"/>
+        <v>2420</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G53" s="3">
+        <v>370</v>
+      </c>
+      <c r="H53" s="3">
+        <v>30</v>
+      </c>
+      <c r="I53" s="3">
+        <f t="shared" si="1"/>
+        <v>340</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>956</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G54" s="8">
+        <v>0</v>
+      </c>
+      <c r="H54" s="8">
+        <v>30</v>
+      </c>
+      <c r="I54" s="8">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J54" s="8" t="s">
+        <v>1884</v>
+      </c>
+      <c r="K54" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>1307</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G55" s="3">
+        <v>0</v>
+      </c>
+      <c r="H55" s="3">
+        <v>30</v>
+      </c>
+      <c r="I55" s="3">
+        <f t="shared" si="1"/>
+        <v>-30</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
+  <dimension ref="A1:Q31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="69.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>1990</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>1991</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="G3" s="6">
+        <v>30</v>
+      </c>
+      <c r="H3" s="6">
+        <v>30</v>
+      </c>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I29" si="0">G3-H3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="8">
+        <v>30</v>
+      </c>
+      <c r="H4" s="8">
+        <v>30</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1995</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G5" s="5">
+        <v>1545</v>
+      </c>
+      <c r="H5" s="5">
+        <v>35</v>
+      </c>
+      <c r="I5" s="5">
+        <f t="shared" si="0"/>
+        <v>1510</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="5" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>1996</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G6" s="8">
+        <v>0</v>
+      </c>
+      <c r="H6" s="8">
+        <v>30</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>30</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>1999</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6">
+        <v>855</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>2000</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>2001</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>2002</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="8">
+        <v>2270</v>
+      </c>
+      <c r="H9" s="8">
+        <v>30</v>
+      </c>
+      <c r="I9" s="8">
+        <f t="shared" si="0"/>
+        <v>2240</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>1992</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>2003</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>2004</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>2005</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G10" s="8">
+        <v>2110</v>
+      </c>
+      <c r="H10" s="8">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>2080</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>1992</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>2007</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="G11" s="5">
+        <v>880</v>
+      </c>
+      <c r="H11" s="5">
+        <v>30</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J11" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>2010</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>2011</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>25</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>2013</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>2014</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>25</v>
+      </c>
+      <c r="I13" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>2015</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>2016</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G14" s="8">
+        <v>380</v>
+      </c>
+      <c r="H14" s="8">
+        <v>30</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>350</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>2017</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>2018</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>2019</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G15" s="6">
+        <v>1145</v>
+      </c>
+      <c r="H15" s="6">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>2020</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1695</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="3">
+        <v>510</v>
+      </c>
+      <c r="H16" s="3">
+        <v>30</v>
+      </c>
+      <c r="I16" s="3">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G17" s="8">
+        <v>510</v>
+      </c>
+      <c r="H17" s="8">
+        <v>30</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="0"/>
+        <v>480</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="3">
+        <v>870</v>
+      </c>
+      <c r="H18" s="3">
+        <v>20</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>2025</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="3">
+        <v>685</v>
+      </c>
+      <c r="H19" s="3">
+        <v>25</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2027</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2029</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" s="3">
+        <v>740</v>
+      </c>
+      <c r="H20" s="3">
+        <v>20</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>720</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="6">
+        <v>1015</v>
+      </c>
+      <c r="H21" s="6">
+        <v>25</v>
+      </c>
+      <c r="I21" s="6">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>2033</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>30</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>1992</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>2037</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="3">
+        <v>920</v>
+      </c>
+      <c r="H23" s="3">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>2039</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>2040</v>
+      </c>
+      <c r="F24" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G24" s="8">
+        <v>920</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>1993</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>2041</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>2043</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G25" s="3">
+        <v>2410</v>
+      </c>
+      <c r="H25" s="3">
+        <v>30</v>
+      </c>
+      <c r="I25" s="3">
+        <f t="shared" si="0"/>
+        <v>2380</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>1992</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>2045</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>2046</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26" s="6">
+        <v>1115</v>
+      </c>
+      <c r="H26" s="6">
+        <v>25</v>
+      </c>
+      <c r="I26" s="6">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G27" s="3">
+        <v>0</v>
+      </c>
+      <c r="H27" s="3">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>2049</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>2050</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="3">
+        <v>890</v>
+      </c>
+      <c r="H28" s="3">
+        <v>20</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>870</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>2051</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>2053</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G29" s="6">
+        <v>0</v>
+      </c>
+      <c r="H29" s="6">
+        <v>25</v>
+      </c>
+      <c r="I29" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>1992</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" s="19" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>1651</v>
+      </c>
+      <c r="D30" s="19" t="s">
+        <v>1652</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>1653</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="G30" s="20">
+        <v>4400</v>
+      </c>
+      <c r="H30" s="20">
+        <v>35</v>
+      </c>
+      <c r="I30" s="20">
+        <v>4365</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>1647</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="O30" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="P30" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q30" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F31" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0</v>
+      </c>
+      <c r="H31" s="11">
+        <v>35</v>
+      </c>
+      <c r="I31" s="11">
+        <v>-35</v>
+      </c>
+      <c r="J31" s="11" t="s">
+        <v>1407</v>
+      </c>
+      <c r="K31" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="11" t="s">
+        <v>1405</v>
+      </c>
+      <c r="M31" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="N31" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="O31" s="19" t="s">
+        <v>265</v>
+      </c>
+      <c r="P31" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q31" s="11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1500-000000000000}">
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>1313</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1765</v>
+      </c>
+      <c r="H3" s="3">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I26" si="0">G3-H3</f>
+        <v>1740</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2101</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G4" s="3">
+        <v>940</v>
+      </c>
+      <c r="H4" s="3">
+        <v>20</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>920</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2061</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>2105</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="6">
+        <v>310</v>
+      </c>
+      <c r="H6" s="6">
+        <v>25</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="0"/>
+        <v>285</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2064</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>2065</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>2066</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G7" s="3">
+        <v>680</v>
+      </c>
+      <c r="H7" s="3">
+        <v>20</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>593</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>2067</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>2068</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6">
+        <v>805</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>2069</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>2071</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="6">
+        <v>845</v>
+      </c>
+      <c r="H9" s="6">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>1754</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>2073</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G10" s="8">
+        <v>810</v>
+      </c>
+      <c r="H10" s="8">
+        <v>30</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>780</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>1411</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="8">
+        <v>0</v>
+      </c>
+      <c r="H11" s="8">
+        <v>30</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>2075</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G12" s="8">
+        <v>0</v>
+      </c>
+      <c r="H12" s="8">
+        <v>30</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>1917</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="8">
+        <v>0</v>
+      </c>
+      <c r="H13" s="8">
+        <v>25</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>2078</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>2080</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="8">
+        <v>470</v>
+      </c>
+      <c r="H14" s="8">
+        <v>30</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>440</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="3">
+        <v>0</v>
+      </c>
+      <c r="H15" s="3">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>2111</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>2112</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="8">
+        <v>740</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>2057</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G17" s="6">
+        <v>845</v>
+      </c>
+      <c r="H17" s="6">
+        <v>25</v>
+      </c>
+      <c r="I17" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>2088</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>2108</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G18" s="8">
+        <v>0</v>
+      </c>
+      <c r="H18" s="8">
+        <v>25</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="8">
+        <v>850</v>
+      </c>
+      <c r="H19" s="8">
+        <v>30</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>2092</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G20" s="6">
+        <v>0</v>
+      </c>
+      <c r="H20" s="6">
+        <v>25</v>
+      </c>
+      <c r="I20" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>2093</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G21" s="8">
+        <v>820</v>
+      </c>
+      <c r="H21" s="8">
+        <v>30</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>2109</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="8">
+        <v>920</v>
+      </c>
+      <c r="H22" s="8">
+        <v>30</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>2097</v>
+      </c>
+      <c r="E23" s="8" t="s">
+        <v>2106</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="8">
+        <v>700</v>
+      </c>
+      <c r="H23" s="8">
+        <v>40</v>
+      </c>
+      <c r="I23" s="8">
+        <f t="shared" si="0"/>
+        <v>660</v>
+      </c>
+      <c r="J23" s="8" t="s">
+        <v>2056</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="8" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
+      <c r="H24" s="6">
+        <v>30</v>
+      </c>
+      <c r="I24" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>2103</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6">
+        <v>30</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>952</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="3">
+        <v>735</v>
+      </c>
+      <c r="H26" s="3">
+        <v>25</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>710</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P55"/>

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DF3EDC-0EFD-4B8D-B6CA-60663BD1634D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EFE784-8CA9-4FA5-BC8A-D6340B12189F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="7" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -35,6 +35,7 @@
     <sheet name="25-05" sheetId="24" r:id="rId20"/>
     <sheet name="26-05" sheetId="25" r:id="rId21"/>
     <sheet name="27-05" sheetId="26" r:id="rId22"/>
+    <sheet name="28-05" sheetId="27" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -57,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6814" uniqueCount="2113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7053" uniqueCount="2183">
   <si>
     <t>THU 6</t>
   </si>
@@ -6227,60 +6228,72 @@
     <t>Nhận hộ fb Nguyễn Hà</t>
   </si>
   <si>
+    <t>HD023711</t>
+  </si>
+  <si>
+    <t>27-05-2026</t>
+  </si>
+  <si>
+    <t>Thúy Nguyễn</t>
+  </si>
+  <si>
+    <t>HD023794</t>
+  </si>
+  <si>
+    <t>598/10 điện biên phủ, p.22</t>
+  </si>
+  <si>
+    <t>ng nhận QP</t>
+  </si>
+  <si>
+    <t>HD023827</t>
+  </si>
+  <si>
+    <t>số 28 khu kdc nam long thạnh lộc</t>
+  </si>
+  <si>
+    <t>HUYỀN NGUYỄN</t>
+  </si>
+  <si>
+    <t>HD023936</t>
+  </si>
+  <si>
+    <t>Số 8 Ba Vì, P4</t>
+  </si>
+  <si>
+    <t>Giang Phạm</t>
+  </si>
+  <si>
+    <t>HD023787</t>
+  </si>
+  <si>
+    <t>136 hoàng hoa thám, p7</t>
+  </si>
+  <si>
+    <t>HD023906</t>
+  </si>
+  <si>
+    <t>77-89 nam kỳ khởi nghĩa bến thành</t>
+  </si>
+  <si>
+    <t>KimVy Phương Anh</t>
+  </si>
+  <si>
+    <t>HD023841</t>
+  </si>
+  <si>
+    <t>214/B14A nguyễn trãi, cầu ông lãnh</t>
+  </si>
+  <si>
+    <t>HD023837</t>
+  </si>
+  <si>
+    <t>Can 32.07 - the Pegasuite 1- số 1002 tạ quang bửu, phường 5</t>
+  </si>
+  <si>
     <t>AT 27-05</t>
   </si>
   <si>
-    <t>27-05-2026</t>
-  </si>
-  <si>
-    <t>HD023794</t>
-  </si>
-  <si>
-    <t>ng nhận QP</t>
-  </si>
-  <si>
-    <t>HD023827</t>
-  </si>
-  <si>
-    <t>số 28 khu kdc nam long thạnh lộc</t>
-  </si>
-  <si>
-    <t>HUYỀN NGUYỄN</t>
-  </si>
-  <si>
-    <t>HD023936</t>
-  </si>
-  <si>
-    <t>Giang Phạm</t>
-  </si>
-  <si>
-    <t>HD023787</t>
-  </si>
-  <si>
-    <t>136 hoàng hoa thám, p7</t>
-  </si>
-  <si>
-    <t>HD023906</t>
-  </si>
-  <si>
-    <t>77-89 nam kỳ khởi nghĩa bến thành</t>
-  </si>
-  <si>
-    <t>KimVy Phương Anh</t>
-  </si>
-  <si>
-    <t>HD023841</t>
-  </si>
-  <si>
-    <t>214/B14A nguyễn trãi, cầu ông lãnh</t>
-  </si>
-  <si>
-    <t>HD023837</t>
-  </si>
-  <si>
-    <t>Can 32.07 - the Pegasuite 1- số 1002 tạ quang bửu, phường 5</t>
-  </si>
-  <si>
     <t>HD023572</t>
   </si>
   <si>
@@ -6314,6 +6327,12 @@
     <t>Thiên An</t>
   </si>
   <si>
+    <t>HD023884</t>
+  </si>
+  <si>
+    <t>D aqua 301 bình động, phú định</t>
+  </si>
+  <si>
     <t>Thao Thanh Nguyen</t>
   </si>
   <si>
@@ -6326,6 +6345,12 @@
     <t>S$3164-Mrskill)</t>
   </si>
   <si>
+    <t>HD022602</t>
+  </si>
+  <si>
+    <t>674 đường số 2, Phường 13</t>
+  </si>
+  <si>
     <t>Khánh Như</t>
   </si>
   <si>
@@ -6335,6 +6360,9 @@
     <t>688/23/1c Hương Lộ 2, phường Bình Trị Đông A</t>
   </si>
   <si>
+    <t>GIA HUY nhận hộ ELIS NGUYỄN (singapore)</t>
+  </si>
+  <si>
     <t>HD023838</t>
   </si>
   <si>
@@ -6344,58 +6372,241 @@
     <t>HD023850</t>
   </si>
   <si>
+    <t>1041/80/3/5 trần xuân soạn phường tân hưng</t>
+  </si>
+  <si>
     <t>cô Loan fb Trịnh Trâm</t>
   </si>
   <si>
     <t>HD023930</t>
   </si>
   <si>
+    <t>124/18/12 võ văn hát p long trường</t>
+  </si>
+  <si>
     <t>NHƯ THẢO</t>
   </si>
   <si>
+    <t>259 đường 9a kdc Trung Sơn, Bình Hưng</t>
+  </si>
+  <si>
     <t>Ellie Quach</t>
   </si>
   <si>
+    <t>8A Sông thương, Phường 2</t>
+  </si>
+  <si>
     <t>SỈ HƯƠNG TRẦN</t>
   </si>
   <si>
-    <t>HD023711</t>
-  </si>
-  <si>
-    <t>Thúy Nguyễn</t>
-  </si>
-  <si>
-    <t>598/10 điện biên phủ, p.22</t>
-  </si>
-  <si>
-    <t>8A Sông thương, Phường 2</t>
-  </si>
-  <si>
-    <t>GIA HUY nhận hộ ELIS NGUYỄN (singapore)</t>
-  </si>
-  <si>
-    <t>Số 8 Ba Vì, P4</t>
-  </si>
-  <si>
-    <t>259 đường 9a kdc Trung Sơn, Bình Hưng</t>
-  </si>
-  <si>
-    <t>HD022602</t>
-  </si>
-  <si>
-    <t>674 đường số 2, Phường 13</t>
-  </si>
-  <si>
-    <t>124/18/12 võ văn hát p long trường</t>
-  </si>
-  <si>
-    <t>1041/80/3/5 trần xuân soạn phường tân hưng</t>
-  </si>
-  <si>
-    <t>HD023884</t>
-  </si>
-  <si>
-    <t>D aqua 301 bình động, phú định</t>
+    <t>NGAY 28-5</t>
+  </si>
+  <si>
+    <t>Uyên Trần</t>
+  </si>
+  <si>
+    <t>HD024168</t>
+  </si>
+  <si>
+    <t>AT 28-05</t>
+  </si>
+  <si>
+    <t>28-05-2026</t>
+  </si>
+  <si>
+    <t>Thanh Vy</t>
+  </si>
+  <si>
+    <t>HD024163</t>
+  </si>
+  <si>
+    <t>Thảo My</t>
+  </si>
+  <si>
+    <t>HD024170</t>
+  </si>
+  <si>
+    <t>HD024033</t>
+  </si>
+  <si>
+    <t>Kelly Phan</t>
+  </si>
+  <si>
+    <t>HD024129</t>
+  </si>
+  <si>
+    <t>Tuệ Nhi</t>
+  </si>
+  <si>
+    <t>HD024045</t>
+  </si>
+  <si>
+    <t>92-94 nam kỳ khởi nghĩa- bến nghé</t>
+  </si>
+  <si>
+    <t>HD024006</t>
+  </si>
+  <si>
+    <t>24 Lê Thánh Tôn (BIDV), P.Bến Nghé</t>
+  </si>
+  <si>
+    <t>Linh fb Phan Thị Tuyết Nhung</t>
+  </si>
+  <si>
+    <t>HD023982</t>
+  </si>
+  <si>
+    <t>Nguyễn Châu Tuệ Lâm</t>
+  </si>
+  <si>
+    <t>HD024027</t>
+  </si>
+  <si>
+    <t>74/1h ds9 linh trung</t>
+  </si>
+  <si>
+    <t>Ngân</t>
+  </si>
+  <si>
+    <t>HD023968</t>
+  </si>
+  <si>
+    <t>Toà A2 Alnata diamond đường N1 Tân Sơn Nhì</t>
+  </si>
+  <si>
+    <t>HD024142</t>
+  </si>
+  <si>
+    <t>HD024157</t>
+  </si>
+  <si>
+    <t>HD023918</t>
+  </si>
+  <si>
+    <t>Minh Thư nhận hộ ( water) fb Thuỷ Vũ</t>
+  </si>
+  <si>
+    <t>HD024179</t>
+  </si>
+  <si>
+    <t>22, TÂN THỚI NHẤT 1B, Phường Tân Thới Nhất</t>
+  </si>
+  <si>
+    <t>Tất Phú</t>
+  </si>
+  <si>
+    <t>HD023941</t>
+  </si>
+  <si>
+    <t>Bệnh viện Nhi đồng 1: 532 Lý Thái Tổ, P10</t>
+  </si>
+  <si>
+    <t>HD24001</t>
+  </si>
+  <si>
+    <t>Trần Lan</t>
+  </si>
+  <si>
+    <t>HD024017</t>
+  </si>
+  <si>
+    <t>Cô Kiều Hương fb Vân Trần</t>
+  </si>
+  <si>
+    <t>HD023954</t>
+  </si>
+  <si>
+    <t>168A Trần Huy Liệu Phường 15</t>
+  </si>
+  <si>
+    <t>HD023966</t>
+  </si>
+  <si>
+    <t>12 nguyễn công trứ, thái bình</t>
+  </si>
+  <si>
+    <t>phạm minh phi_F3: Theer To Lao</t>
+  </si>
+  <si>
+    <t>Diễm Phúc</t>
+  </si>
+  <si>
+    <t>HD024175</t>
+  </si>
+  <si>
+    <t>314/138 đường âu dương lân, p3</t>
+  </si>
+  <si>
+    <t>Đậu Đậu</t>
+  </si>
+  <si>
+    <t>HD024181</t>
+  </si>
+  <si>
+    <t>106/4 phan van tri phường 12</t>
+  </si>
+  <si>
+    <t>HD024164</t>
+  </si>
+  <si>
+    <t>Linh Nga Anna</t>
+  </si>
+  <si>
+    <t>khả trinh</t>
+  </si>
+  <si>
+    <t>82/17/20đinh tiên hoàng p1</t>
+  </si>
+  <si>
+    <t>chị hương fb Kim Tien Pham</t>
+  </si>
+  <si>
+    <t>HD024093</t>
+  </si>
+  <si>
+    <t>33 đường số 6 p26</t>
+  </si>
+  <si>
+    <t>190 võ văn ngân</t>
+  </si>
+  <si>
+    <t>HD023972</t>
+  </si>
+  <si>
+    <t>433/11, Lê Đức Thọ, Phường 17</t>
+  </si>
+  <si>
+    <t>201 Đường Hoàng Hoa Thám, Phường 13</t>
+  </si>
+  <si>
+    <t>Nguyễn Trinh</t>
+  </si>
+  <si>
+    <t>29/10c trần thái tông</t>
+  </si>
+  <si>
+    <t>Toà Aster - Urbun Green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
+    <t>91/12 nguyễn thanh tuyền p1</t>
+  </si>
+  <si>
+    <t>240/6A lê thánh tôn phường bến thành</t>
+  </si>
+  <si>
+    <t>Thủy Heri</t>
+  </si>
+  <si>
+    <t>HD024145</t>
+  </si>
+  <si>
+    <t>184/17/35 bãi sậy phường bình tiên</t>
+  </si>
+  <si>
+    <t>137/84D âu dương lân - p2</t>
+  </si>
+  <si>
+    <t>20B Trần Văn Quang, Phường Bảy Hiền</t>
   </si>
 </sst>
 </file>
@@ -8040,7 +8251,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I56" si="1">G35-H35</f>
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -23996,7 +24207,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I55" si="1">G35-H35</f>
         <v>700</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -25914,10 +26125,12 @@
   <dimension ref="A1:P26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="21" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="55" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -25991,7 +26204,7 @@
         <v>2055</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>2100</v>
+        <v>2056</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>1313</v>
@@ -26024,13 +26237,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>2101</v>
+        <v>2058</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>2102</v>
+        <v>2060</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>81</v>
@@ -26060,13 +26273,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>29</v>
@@ -26096,13 +26309,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>2105</v>
+        <v>2066</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>102</v>
@@ -26132,13 +26345,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>81</v>
@@ -26171,10 +26384,10 @@
         <v>593</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>63</v>
@@ -26204,13 +26417,13 @@
         <v>18</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>63</v>
@@ -26243,10 +26456,10 @@
         <v>1754</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="F10" s="8" t="s">
         <v>41</v>
@@ -26262,7 +26475,7 @@
         <v>780</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>24</v>
@@ -26279,7 +26492,7 @@
         <v>1411</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>2074</v>
+        <v>2078</v>
       </c>
       <c r="E11" s="8" t="s">
         <v>763</v>
@@ -26298,7 +26511,7 @@
         <v>-30</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K11" s="8" t="s">
         <v>24</v>
@@ -26315,7 +26528,7 @@
         <v>1442</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>2075</v>
+        <v>2079</v>
       </c>
       <c r="E12" s="8" t="s">
         <v>1444</v>
@@ -26334,7 +26547,7 @@
         <v>-30</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K12" s="8" t="s">
         <v>24</v>
@@ -26351,10 +26564,10 @@
         <v>1917</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>2076</v>
+        <v>2080</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>2077</v>
+        <v>2081</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>85</v>
@@ -26370,7 +26583,7 @@
         <v>-25</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>24</v>
@@ -26384,13 +26597,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>2078</v>
+        <v>2082</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>2079</v>
+        <v>2083</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>2080</v>
+        <v>2084</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>41</v>
@@ -26406,7 +26619,7 @@
         <v>440</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>24</v>
@@ -26420,13 +26633,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2081</v>
+        <v>2085</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2082</v>
+        <v>2086</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>2083</v>
+        <v>2087</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>29</v>
@@ -26456,13 +26669,13 @@
         <v>18</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>2084</v>
+        <v>2088</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>2111</v>
+        <v>2089</v>
       </c>
       <c r="E16" s="8" t="s">
-        <v>2112</v>
+        <v>2090</v>
       </c>
       <c r="F16" s="9" t="s">
         <v>41</v>
@@ -26478,7 +26691,7 @@
         <v>710</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>24</v>
@@ -26495,13 +26708,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>2085</v>
+        <v>2091</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>2086</v>
+        <v>2092</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>2087</v>
+        <v>2093</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>63</v>
@@ -26531,13 +26744,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>2088</v>
+        <v>2094</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>2107</v>
+        <v>2095</v>
       </c>
       <c r="E18" s="8" t="s">
-        <v>2108</v>
+        <v>2096</v>
       </c>
       <c r="F18" s="8" t="s">
         <v>127</v>
@@ -26553,7 +26766,7 @@
         <v>-25</v>
       </c>
       <c r="J18" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K18" s="8" t="s">
         <v>24</v>
@@ -26567,13 +26780,13 @@
         <v>18</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>2089</v>
+        <v>2097</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>2090</v>
+        <v>2098</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>2091</v>
+        <v>2099</v>
       </c>
       <c r="F19" s="8" t="s">
         <v>22</v>
@@ -26589,7 +26802,7 @@
         <v>820</v>
       </c>
       <c r="J19" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K19" s="8" t="s">
         <v>24</v>
@@ -26603,10 +26816,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>2104</v>
+        <v>2100</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2092</v>
+        <v>2101</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>1415</v>
@@ -26639,13 +26852,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>2093</v>
+        <v>2102</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>2094</v>
+        <v>2103</v>
       </c>
       <c r="E21" s="8" t="s">
-        <v>2110</v>
+        <v>2104</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>131</v>
@@ -26661,7 +26874,7 @@
         <v>790</v>
       </c>
       <c r="J21" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K21" s="8" t="s">
         <v>24</v>
@@ -26675,13 +26888,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>2095</v>
+        <v>2105</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>2096</v>
+        <v>2106</v>
       </c>
       <c r="E22" s="8" t="s">
-        <v>2109</v>
+        <v>2107</v>
       </c>
       <c r="F22" s="8" t="s">
         <v>149</v>
@@ -26697,7 +26910,7 @@
         <v>890</v>
       </c>
       <c r="J22" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K22" s="8" t="s">
         <v>24</v>
@@ -26714,10 +26927,10 @@
         <v>18</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>2097</v>
+        <v>2108</v>
       </c>
       <c r="E23" s="8" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="F23" s="8" t="s">
         <v>52</v>
@@ -26733,7 +26946,7 @@
         <v>660</v>
       </c>
       <c r="J23" s="8" t="s">
-        <v>2056</v>
+        <v>2077</v>
       </c>
       <c r="K23" s="8" t="s">
         <v>24</v>
@@ -26786,10 +26999,10 @@
         <v>18</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>2098</v>
+        <v>2110</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>2103</v>
+        <v>2111</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>102</v>
@@ -26822,7 +27035,7 @@
         <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>2099</v>
+        <v>2112</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>952</v>
@@ -26852,6 +27065,1078 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1600-000000000000}">
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>2114</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>2115</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>2181</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="8">
+        <v>720</v>
+      </c>
+      <c r="H3" s="8">
+        <v>30</v>
+      </c>
+      <c r="I3" s="8">
+        <f t="shared" ref="I3:I28" si="0">G3-H3</f>
+        <v>690</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>2182</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="8">
+        <v>1165</v>
+      </c>
+      <c r="H4" s="8">
+        <v>25</v>
+      </c>
+      <c r="I4" s="8">
+        <f t="shared" si="0"/>
+        <v>1140</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K4" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="8" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>2120</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>2121</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="G5" s="6">
+        <v>915</v>
+      </c>
+      <c r="H5" s="6">
+        <v>25</v>
+      </c>
+      <c r="I5" s="6">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G6" s="3">
+        <v>900</v>
+      </c>
+      <c r="H6" s="3">
+        <v>20</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>2123</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>2177</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0</v>
+      </c>
+      <c r="H7" s="6">
+        <v>25</v>
+      </c>
+      <c r="I7" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>2127</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1633</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>2129</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="H9" s="6">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>2179</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>2180</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="G10" s="8">
+        <v>0</v>
+      </c>
+      <c r="H10" s="8">
+        <v>25</v>
+      </c>
+      <c r="I10" s="8">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>2172</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="3">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>25</v>
+      </c>
+      <c r="I11" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>2132</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="3">
+        <v>3650</v>
+      </c>
+      <c r="H12" s="3">
+        <v>40</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>3610</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>2136</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>2137</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="G13" s="8">
+        <v>845</v>
+      </c>
+      <c r="H13" s="8">
+        <v>25</v>
+      </c>
+      <c r="I13" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J13" s="8" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>2139</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2174</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="G15" s="3">
+        <v>775</v>
+      </c>
+      <c r="H15" s="3">
+        <v>25</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>2140</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G16" s="8">
+        <v>850</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2141</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>2143</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="3">
+        <v>0</v>
+      </c>
+      <c r="H17" s="3">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>2144</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G18" s="6">
+        <v>595</v>
+      </c>
+      <c r="H18" s="6">
+        <v>25</v>
+      </c>
+      <c r="I18" s="6">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>748</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1775</v>
+      </c>
+      <c r="H19" s="3">
+        <v>25</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>1750</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2166</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
+      </c>
+      <c r="H20" s="3">
+        <v>25</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="3">
+        <v>1120</v>
+      </c>
+      <c r="H21" s="3">
+        <v>30</v>
+      </c>
+      <c r="I21" s="3">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>2150</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>2152</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="G22" s="6">
+        <v>970</v>
+      </c>
+      <c r="H22" s="6">
+        <v>20</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="0"/>
+        <v>950</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>2154</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G23" s="6">
+        <v>845</v>
+      </c>
+      <c r="H23" s="6">
+        <v>25</v>
+      </c>
+      <c r="I23" s="6">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>2155</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>2167</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G24" s="3">
+        <v>1720</v>
+      </c>
+      <c r="H24" s="3">
+        <v>20</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>1700</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>2156</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>2158</v>
+      </c>
+      <c r="F25" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G25" s="8">
+        <v>850</v>
+      </c>
+      <c r="H25" s="8">
+        <v>30</v>
+      </c>
+      <c r="I25" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J25" s="8" t="s">
+        <v>2116</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>20</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>-20</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>2175</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="3">
+        <v>860</v>
+      </c>
+      <c r="H27" s="3">
+        <v>30</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>60</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>-60</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>1889</v>
+      </c>
+      <c r="F29" s="12">
+        <v>4</v>
+      </c>
+      <c r="G29" s="11">
+        <v>845</v>
+      </c>
+      <c r="H29" s="11">
+        <v>25</v>
+      </c>
+      <c r="I29" s="11">
+        <v>820</v>
+      </c>
+      <c r="J29" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="11" t="s">
+        <v>1873</v>
+      </c>
+      <c r="M29" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="N29" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="O29" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="P29" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q29" s="11">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28132,7 +29417,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I55" si="1">G35-H35</f>
         <v>2090</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -35315,7 +36600,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I58" si="1">G35-H35</f>
         <v>-30</v>
       </c>
       <c r="J35" s="8" t="s">

--- a/data/May/Data_May.xlsx
+++ b/data/May/Data_May.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\May\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EFE784-8CA9-4FA5-BC8A-D6340B12189F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1466695-D300-4D95-8388-7E8787C37A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="10" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="01-05" sheetId="4" r:id="rId1"/>
@@ -36,6 +36,8 @@
     <sheet name="26-05" sheetId="25" r:id="rId21"/>
     <sheet name="27-05" sheetId="26" r:id="rId22"/>
     <sheet name="28-05" sheetId="27" r:id="rId23"/>
+    <sheet name="29-05" sheetId="28" r:id="rId24"/>
+    <sheet name="30-05" sheetId="29" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7053" uniqueCount="2183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7503" uniqueCount="2320">
   <si>
     <t>THU 6</t>
   </si>
@@ -6408,6 +6410,9 @@
     <t>HD024168</t>
   </si>
   <si>
+    <t>137/84D âu dương lân - p2</t>
+  </si>
+  <si>
     <t>AT 28-05</t>
   </si>
   <si>
@@ -6420,21 +6425,36 @@
     <t>HD024163</t>
   </si>
   <si>
+    <t>20B Trần Văn Quang, Phường Bảy Hiền</t>
+  </si>
+  <si>
     <t>Thảo My</t>
   </si>
   <si>
     <t>HD024170</t>
   </si>
   <si>
+    <t>91/12 nguyễn thanh tuyền p1</t>
+  </si>
+  <si>
+    <t>khả trinh</t>
+  </si>
+  <si>
     <t>HD024033</t>
   </si>
   <si>
+    <t>82/17/20đinh tiên hoàng p1</t>
+  </si>
+  <si>
     <t>Kelly Phan</t>
   </si>
   <si>
     <t>HD024129</t>
   </si>
   <si>
+    <t>240/6A lê thánh tôn phường bến thành</t>
+  </si>
+  <si>
     <t>Tuệ Nhi</t>
   </si>
   <si>
@@ -6450,12 +6470,24 @@
     <t>24 Lê Thánh Tôn (BIDV), P.Bến Nghé</t>
   </si>
   <si>
+    <t>Thủy Heri</t>
+  </si>
+  <si>
+    <t>HD024145</t>
+  </si>
+  <si>
+    <t>184/17/35 bãi sậy phường bình tiên</t>
+  </si>
+  <si>
     <t>Linh fb Phan Thị Tuyết Nhung</t>
   </si>
   <si>
     <t>HD023982</t>
   </si>
   <si>
+    <t>201 Đường Hoàng Hoa Thám, Phường 13</t>
+  </si>
+  <si>
     <t>Nguyễn Châu Tuệ Lâm</t>
   </si>
   <si>
@@ -6477,9 +6509,15 @@
     <t>HD024142</t>
   </si>
   <si>
+    <t>Nguyễn Trinh</t>
+  </si>
+  <si>
     <t>HD024157</t>
   </si>
   <si>
+    <t>29/10c trần thái tông</t>
+  </si>
+  <si>
     <t>HD023918</t>
   </si>
   <si>
@@ -6501,6 +6539,15 @@
     <t>Bệnh viện Nhi đồng 1: 532 Lý Thái Tổ, P10</t>
   </si>
   <si>
+    <t>HD023972</t>
+  </si>
+  <si>
+    <t>433/11, Lê Đức Thọ, Phường 17</t>
+  </si>
+  <si>
+    <t>chị hương fb Kim Tien Pham</t>
+  </si>
+  <si>
     <t>HD24001</t>
   </si>
   <si>
@@ -6510,6 +6557,9 @@
     <t>HD024017</t>
   </si>
   <si>
+    <t>190 võ văn ngân</t>
+  </si>
+  <si>
     <t>Cô Kiều Hương fb Vân Trần</t>
   </si>
   <si>
@@ -6528,6 +6578,12 @@
     <t>phạm minh phi_F3: Theer To Lao</t>
   </si>
   <si>
+    <t>HD024093</t>
+  </si>
+  <si>
+    <t>33 đường số 6 p26</t>
+  </si>
+  <si>
     <t>Diễm Phúc</t>
   </si>
   <si>
@@ -6549,64 +6605,421 @@
     <t>HD024164</t>
   </si>
   <si>
+    <t>Toà Aster - Urbun Green (đối diện Vạn Phúc)</t>
+  </si>
+  <si>
     <t>Linh Nga Anna</t>
   </si>
   <si>
-    <t>khả trinh</t>
-  </si>
-  <si>
-    <t>82/17/20đinh tiên hoàng p1</t>
-  </si>
-  <si>
-    <t>chị hương fb Kim Tien Pham</t>
-  </si>
-  <si>
-    <t>HD024093</t>
-  </si>
-  <si>
-    <t>33 đường số 6 p26</t>
-  </si>
-  <si>
-    <t>190 võ văn ngân</t>
-  </si>
-  <si>
-    <t>HD023972</t>
-  </si>
-  <si>
-    <t>433/11, Lê Đức Thọ, Phường 17</t>
-  </si>
-  <si>
-    <t>201 Đường Hoàng Hoa Thám, Phường 13</t>
-  </si>
-  <si>
-    <t>Nguyễn Trinh</t>
-  </si>
-  <si>
-    <t>29/10c trần thái tông</t>
-  </si>
-  <si>
-    <t>Toà Aster - Urbun Green (đối diện Vạn Phúc)</t>
-  </si>
-  <si>
-    <t>91/12 nguyễn thanh tuyền p1</t>
-  </si>
-  <si>
-    <t>240/6A lê thánh tôn phường bến thành</t>
-  </si>
-  <si>
-    <t>Thủy Heri</t>
-  </si>
-  <si>
-    <t>HD024145</t>
-  </si>
-  <si>
-    <t>184/17/35 bãi sậy phường bình tiên</t>
-  </si>
-  <si>
-    <t>137/84D âu dương lân - p2</t>
-  </si>
-  <si>
-    <t>20B Trần Văn Quang, Phường Bảy Hiền</t>
+    <t>NGAY 29-5</t>
+  </si>
+  <si>
+    <t>Cẩm Tiên</t>
+  </si>
+  <si>
+    <t>HD024200</t>
+  </si>
+  <si>
+    <t>Chung cư topaz dragon 2A 457-459 tạ quang bửu - phường 4</t>
+  </si>
+  <si>
+    <t>AT 29-05</t>
+  </si>
+  <si>
+    <t>29-05-2026</t>
+  </si>
+  <si>
+    <t>Chan (inst char importshop) -BN2441</t>
+  </si>
+  <si>
+    <t>HD024246</t>
+  </si>
+  <si>
+    <t>163 Trương Thị Hoa phường Tân Thới Hiệp</t>
+  </si>
+  <si>
+    <t>Uyên</t>
+  </si>
+  <si>
+    <t>HD024442</t>
+  </si>
+  <si>
+    <t>98 Vườn Lài, phường An Phú Đông</t>
+  </si>
+  <si>
+    <t>HD024203</t>
+  </si>
+  <si>
+    <t>Nguyễn Huỳnh Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD024247</t>
+  </si>
+  <si>
+    <t>78/63 đường số 11, phường thông tây hội</t>
+  </si>
+  <si>
+    <t>Thùy</t>
+  </si>
+  <si>
+    <t>HD024086</t>
+  </si>
+  <si>
+    <t>175 quốc lộ 1k, linh xuân</t>
+  </si>
+  <si>
+    <t>Minh Hồng Nguyễn</t>
+  </si>
+  <si>
+    <t>HD024438</t>
+  </si>
+  <si>
+    <t>Jasmine 1 Hà đô - 118 Đường 3/2, phường 12</t>
+  </si>
+  <si>
+    <t>Tuyen Nguyen</t>
+  </si>
+  <si>
+    <t>HD024412</t>
+  </si>
+  <si>
+    <t>39/44/6 hoàng bật đạt p15</t>
+  </si>
+  <si>
+    <t>Phương Đoan</t>
+  </si>
+  <si>
+    <t>HD024459</t>
+  </si>
+  <si>
+    <t>số 17 đường số 13 bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Út Nhỏ (thu trần ) (Malaysia)</t>
+  </si>
+  <si>
+    <t>HD024433</t>
+  </si>
+  <si>
+    <t>24/5F, Ấp Đông Lân, Xã Bà Điểm</t>
+  </si>
+  <si>
+    <t>Daisy Le</t>
+  </si>
+  <si>
+    <t>HD024416</t>
+  </si>
+  <si>
+    <t>418 Trường Sa, p2</t>
+  </si>
+  <si>
+    <t>Đào thị thanh tâm</t>
+  </si>
+  <si>
+    <t>HD024429</t>
+  </si>
+  <si>
+    <t>320/16 đường ĐHT 02 Phường đông hưng thuận</t>
+  </si>
+  <si>
+    <t>Ngọc Quyên</t>
+  </si>
+  <si>
+    <t>HD024258</t>
+  </si>
+  <si>
+    <t>148a hòa hưng p13</t>
+  </si>
+  <si>
+    <t>HD024304</t>
+  </si>
+  <si>
+    <t>Block d2, chung cư sài gòn riverside (số 4 đào trí phú thuận)</t>
+  </si>
+  <si>
+    <t>HD024270</t>
+  </si>
+  <si>
+    <t>Kim Anh Phạm</t>
+  </si>
+  <si>
+    <t>HD024302</t>
+  </si>
+  <si>
+    <t>16 cư xá bình minh, dương Bá Trạc, phường 1</t>
+  </si>
+  <si>
+    <t>Tạ Ngọc Mai</t>
+  </si>
+  <si>
+    <t>HD024430</t>
+  </si>
+  <si>
+    <t>Sarimi B1, khu chung cư Sala, P. An Lợi Đông</t>
+  </si>
+  <si>
+    <t>Thúy Duy</t>
+  </si>
+  <si>
+    <t>HD024294</t>
+  </si>
+  <si>
+    <t>539,22 hương lộ 3 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>Kim Tuyền</t>
+  </si>
+  <si>
+    <t>HD024441</t>
+  </si>
+  <si>
+    <t>451/40 phạm thế hiển phường 3</t>
+  </si>
+  <si>
+    <t>HD024290</t>
+  </si>
+  <si>
+    <t>BN1B2 mini chouchou Fb.</t>
+  </si>
+  <si>
+    <t>HD024453</t>
+  </si>
+  <si>
+    <t>410 Quang Trung f10</t>
+  </si>
+  <si>
+    <t>NGAY 30-5</t>
+  </si>
+  <si>
+    <t>ĐỨC - FB MT MI Ngo</t>
+  </si>
+  <si>
+    <t>HD024678</t>
+  </si>
+  <si>
+    <t>30-05-2026</t>
+  </si>
+  <si>
+    <t>Phạm Thị Thanh Hồng</t>
+  </si>
+  <si>
+    <t>HD024697</t>
+  </si>
+  <si>
+    <t>AT 30-05</t>
+  </si>
+  <si>
+    <t>Ngọc Vũ</t>
+  </si>
+  <si>
+    <t>HD024689</t>
+  </si>
+  <si>
+    <t>42 đương so 6 binh trưng đông</t>
+  </si>
+  <si>
+    <t>Nguyễn Cẩm Tú</t>
+  </si>
+  <si>
+    <t>HD024680</t>
+  </si>
+  <si>
+    <t>Ái Linh</t>
+  </si>
+  <si>
+    <t>HD024455</t>
+  </si>
+  <si>
+    <t>Kiều Nhi</t>
+  </si>
+  <si>
+    <t>HD024623</t>
+  </si>
+  <si>
+    <t>Nguyễn Thu Phương</t>
+  </si>
+  <si>
+    <t>HD024563</t>
+  </si>
+  <si>
+    <t>Sunrise riverside tháp H Đường Nguyễn hữu thọ</t>
+  </si>
+  <si>
+    <t>Hoàng Thu Thủy</t>
+  </si>
+  <si>
+    <t>HD024597</t>
+  </si>
+  <si>
+    <t>583 Nguyễn Thị Thập, phường Bình Thuận</t>
+  </si>
+  <si>
+    <t>HD024510</t>
+  </si>
+  <si>
+    <t>235 QL13 Cũ, HBP</t>
+  </si>
+  <si>
+    <t>HD024702</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Thùy Tiên</t>
+  </si>
+  <si>
+    <t>HD024686</t>
+  </si>
+  <si>
+    <t>Trần Thị Mỹ Duyên</t>
+  </si>
+  <si>
+    <t>HD024528</t>
+  </si>
+  <si>
+    <t>HD024599</t>
+  </si>
+  <si>
+    <t>Chị Bảo Châu</t>
+  </si>
+  <si>
+    <t>HD024669</t>
+  </si>
+  <si>
+    <t>W3370</t>
+  </si>
+  <si>
+    <t>HD024406</t>
+  </si>
+  <si>
+    <t>Ngọc Diệu</t>
+  </si>
+  <si>
+    <t>HD024379</t>
+  </si>
+  <si>
+    <t>HD024538</t>
+  </si>
+  <si>
+    <t>Võ Hằng</t>
+  </si>
+  <si>
+    <t>HD024527</t>
+  </si>
+  <si>
+    <t>HD024666</t>
+  </si>
+  <si>
+    <t>11 đường 18 phường 4</t>
+  </si>
+  <si>
+    <t>BN6352</t>
+  </si>
+  <si>
+    <t>HD024138</t>
+  </si>
+  <si>
+    <t>HD024670</t>
+  </si>
+  <si>
+    <t>Phạm Duyên</t>
+  </si>
+  <si>
+    <t>HD024075</t>
+  </si>
+  <si>
+    <t>HD024454</t>
+  </si>
+  <si>
+    <t>Đặng Trung</t>
+  </si>
+  <si>
+    <t>HD023933</t>
+  </si>
+  <si>
+    <t>HD024607</t>
+  </si>
+  <si>
+    <t>17/2 đường số 10 p bình trưng tây</t>
+  </si>
+  <si>
+    <t>84 song hành phường an phú</t>
+  </si>
+  <si>
+    <t>Ngô Hoàng Ánh</t>
+  </si>
+  <si>
+    <t>320/16 đường ĐHT 02 phường đông hưng thuận</t>
+  </si>
+  <si>
+    <t>4/2b đường số 26 phương an khánh</t>
+  </si>
+  <si>
+    <t>39 an nhơn phường 17</t>
+  </si>
+  <si>
+    <t>An Nguyen - fb Nguyễn Hoàng Thúy An</t>
+  </si>
+  <si>
+    <t>105/48 Nguyễn tư giản f12</t>
+  </si>
+  <si>
+    <t>Số 107, Đường Dương Quảng Hàm phường 7 (tiệm rửa xe)</t>
+  </si>
+  <si>
+    <t>Irire Intara (phòng 505)</t>
+  </si>
+  <si>
+    <t>A25 Hotel - 51-53-55 Cách Mạng Tháng 8, Phường Bến Thành</t>
+  </si>
+  <si>
+    <t>Panhaketya (zalo_thiemuyen)</t>
+  </si>
+  <si>
+    <t>Pham Ngu Lao A67 Nguyen Trai</t>
+  </si>
+  <si>
+    <t>HD024659</t>
+  </si>
+  <si>
+    <t>206 khu phố Mỹ Hào, Hà Huy tập, P. Tân Phong</t>
+  </si>
+  <si>
+    <t>Sky garden 2, cổng đông 3, phường tân phong</t>
+  </si>
+  <si>
+    <t>Hẻm 95, nhà 95/5D, đường 15, phường tân hưng</t>
+  </si>
+  <si>
+    <t>Cty leading star, lô C đường số 3, KCN Đồng An, Bình Hoà</t>
+  </si>
+  <si>
+    <t>tinh</t>
+  </si>
+  <si>
+    <t>hàng tỉnh</t>
+  </si>
+  <si>
+    <t>luu tra</t>
+  </si>
+  <si>
+    <t>Nhân (fb Cam Phu)</t>
+  </si>
+  <si>
+    <t>132 Le van quoi p bình hưng hòa a</t>
+  </si>
+  <si>
+    <t>1/10/2 nguyễn văn yến phường phú thạnh</t>
+  </si>
+  <si>
+    <t>Anh Hải nhận hàng (Thảo Trần)</t>
+  </si>
+  <si>
+    <t>HD024613</t>
+  </si>
+  <si>
+    <t>số 17 đường số 13 phường bình hưng hòa</t>
+  </si>
+  <si>
+    <t>HD024704</t>
   </si>
 </sst>
 </file>
@@ -6701,7 +7114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -6723,6 +7136,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8251,7 +8667,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I56" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>30</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -24207,7 +24623,7 @@
         <v>25</v>
       </c>
       <c r="I35" s="3">
-        <f t="shared" ref="I35:I55" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>700</v>
       </c>
       <c r="J35" s="3" t="s">
@@ -27073,10 +27489,12 @@
   <dimension ref="A1:Q29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="35.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="42.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
     <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
@@ -27153,7 +27571,7 @@
         <v>2115</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>2181</v>
+        <v>2116</v>
       </c>
       <c r="F3" s="9" t="s">
         <v>41</v>
@@ -27169,13 +27587,13 @@
         <v>690</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K3" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L3" s="8" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="4" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -27183,13 +27601,13 @@
         <v>18</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>2182</v>
+        <v>2121</v>
       </c>
       <c r="F4" s="9" t="s">
         <v>102</v>
@@ -27205,13 +27623,13 @@
         <v>1140</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K4" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="5" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -27219,13 +27637,13 @@
         <v>18</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>2176</v>
+        <v>2124</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>102</v>
@@ -27247,7 +27665,7 @@
         <v>24</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27255,13 +27673,13 @@
         <v>18</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2164</v>
+        <v>2125</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2122</v>
+        <v>2126</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>2165</v>
+        <v>2127</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>81</v>
@@ -27283,7 +27701,7 @@
         <v>24</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -27291,13 +27709,13 @@
         <v>18</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>2123</v>
+        <v>2128</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>2124</v>
+        <v>2129</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>2177</v>
+        <v>2130</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>63</v>
@@ -27319,7 +27737,7 @@
         <v>24</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -27327,13 +27745,13 @@
         <v>18</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>2126</v>
+        <v>2132</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>2127</v>
+        <v>2133</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>63</v>
@@ -27355,7 +27773,7 @@
         <v>24</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -27366,10 +27784,10 @@
         <v>1633</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>2128</v>
+        <v>2134</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>2129</v>
+        <v>2135</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>63</v>
@@ -27391,7 +27809,7 @@
         <v>24</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="10" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -27399,13 +27817,13 @@
         <v>18</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>2178</v>
+        <v>2136</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>2179</v>
+        <v>2137</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>2180</v>
+        <v>2138</v>
       </c>
       <c r="F10" s="9" t="s">
         <v>127</v>
@@ -27421,13 +27839,13 @@
         <v>-25</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K10" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L10" s="8" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="11" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27435,13 +27853,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>2130</v>
+        <v>2139</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>2131</v>
+        <v>2140</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>2172</v>
+        <v>2141</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>102</v>
@@ -27463,7 +27881,7 @@
         <v>24</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27471,13 +27889,13 @@
         <v>18</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2132</v>
+        <v>2142</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>2133</v>
+        <v>2143</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>2134</v>
+        <v>2144</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>77</v>
@@ -27499,7 +27917,7 @@
         <v>24</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="M12" s="3" t="s">
         <v>145</v>
@@ -27510,13 +27928,13 @@
         <v>18</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>2135</v>
+        <v>2145</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>2136</v>
+        <v>2146</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>2137</v>
+        <v>2147</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>85</v>
@@ -27532,13 +27950,13 @@
         <v>820</v>
       </c>
       <c r="J13" s="8" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K13" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27549,7 +27967,7 @@
         <v>2085</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>2138</v>
+        <v>2148</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>2087</v>
@@ -27574,7 +27992,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27582,13 +28000,13 @@
         <v>18</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>2173</v>
+        <v>2149</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>2139</v>
+        <v>2150</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>2174</v>
+        <v>2151</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>102</v>
@@ -27610,7 +28028,7 @@
         <v>24</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -27621,7 +28039,7 @@
         <v>1930</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>2140</v>
+        <v>2152</v>
       </c>
       <c r="E16" s="8" t="s">
         <v>1932</v>
@@ -27640,13 +28058,13 @@
         <v>820</v>
       </c>
       <c r="J16" s="8" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K16" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L16" s="8" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27654,13 +28072,13 @@
         <v>18</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>2141</v>
+        <v>2153</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>2142</v>
+        <v>2154</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>2143</v>
+        <v>2155</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>29</v>
@@ -27682,7 +28100,7 @@
         <v>24</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -27690,13 +28108,13 @@
         <v>18</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>2144</v>
+        <v>2156</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>2145</v>
+        <v>2157</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>2146</v>
+        <v>2158</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>308</v>
@@ -27718,7 +28136,7 @@
         <v>24</v>
       </c>
       <c r="L18" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27729,10 +28147,10 @@
         <v>748</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>2170</v>
+        <v>2159</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>2171</v>
+        <v>2160</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>70</v>
@@ -27754,7 +28172,7 @@
         <v>24</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27762,10 +28180,10 @@
         <v>18</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>2166</v>
+        <v>2161</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>2147</v>
+        <v>2162</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>242</v>
@@ -27790,7 +28208,7 @@
         <v>24</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27798,13 +28216,13 @@
         <v>18</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>2148</v>
+        <v>2163</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>2149</v>
+        <v>2164</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>2169</v>
+        <v>2165</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>77</v>
@@ -27826,7 +28244,7 @@
         <v>24</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -27834,13 +28252,13 @@
         <v>18</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>2150</v>
+        <v>2166</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2151</v>
+        <v>2167</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>2152</v>
+        <v>2168</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>355</v>
@@ -27862,7 +28280,7 @@
         <v>24</v>
       </c>
       <c r="L22" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -27873,10 +28291,10 @@
         <v>1163</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>2153</v>
+        <v>2169</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>2154</v>
+        <v>2170</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>63</v>
@@ -27898,7 +28316,7 @@
         <v>24</v>
       </c>
       <c r="L23" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27906,13 +28324,13 @@
         <v>18</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>2155</v>
+        <v>2171</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>2167</v>
+        <v>2172</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>2168</v>
+        <v>2173</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>81</v>
@@ -27934,7 +28352,7 @@
         <v>24</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
@@ -27942,13 +28360,13 @@
         <v>18</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>2156</v>
+        <v>2174</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>2157</v>
+        <v>2175</v>
       </c>
       <c r="E25" s="8" t="s">
-        <v>2158</v>
+        <v>2176</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>41</v>
@@ -27964,13 +28382,13 @@
         <v>820</v>
       </c>
       <c r="J25" s="8" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="K25" s="8" t="s">
         <v>24</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -27978,13 +28396,13 @@
         <v>18</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>2159</v>
+        <v>2177</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>2160</v>
+        <v>2178</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>2161</v>
+        <v>2179</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>81</v>
@@ -28006,7 +28424,7 @@
         <v>24</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="M26" s="3" t="s">
         <v>145</v>
@@ -28020,10 +28438,10 @@
         <v>150</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>2162</v>
+        <v>2180</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>2175</v>
+        <v>2181</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>77</v>
@@ -28045,7 +28463,7 @@
         <v>24</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -28056,7 +28474,7 @@
         <v>18</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>2163</v>
+        <v>2182</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>2087</v>
@@ -28081,7 +28499,7 @@
         <v>24</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
@@ -28132,6 +28550,2031 @@
       </c>
       <c r="Q29" s="11">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1700-000000000000}">
+  <dimension ref="A1:P24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="33" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="114.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>2184</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>2185</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>2186</v>
+      </c>
+      <c r="F3" s="9">
+        <v>8</v>
+      </c>
+      <c r="G3" s="8">
+        <v>920</v>
+      </c>
+      <c r="H3" s="8">
+        <v>30</v>
+      </c>
+      <c r="I3" s="8">
+        <f t="shared" ref="I3:I24" si="0">G3-H3</f>
+        <v>890</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>2189</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2190</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2191</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>40</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2193</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2194</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="3">
+        <v>910</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>880</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>2195</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="8">
+        <v>1875</v>
+      </c>
+      <c r="H6" s="8">
+        <v>35</v>
+      </c>
+      <c r="I6" s="8">
+        <f t="shared" si="0"/>
+        <v>1840</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="8" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="3">
+        <v>615</v>
+      </c>
+      <c r="H7" s="3">
+        <v>25</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2199</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>2201</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1120</v>
+      </c>
+      <c r="H8" s="3">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>1090</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>2202</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G9" s="6">
+        <v>795</v>
+      </c>
+      <c r="H9" s="6">
+        <v>25</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="0"/>
+        <v>770</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2205</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>2207</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1145</v>
+      </c>
+      <c r="H10" s="3">
+        <v>25</v>
+      </c>
+      <c r="I10" s="3">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>2208</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>2209</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>2210</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G11" s="8">
+        <v>1770</v>
+      </c>
+      <c r="H11" s="8">
+        <v>30</v>
+      </c>
+      <c r="I11" s="8">
+        <f t="shared" si="0"/>
+        <v>1740</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>2212</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>2213</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>1335</v>
+      </c>
+      <c r="G12" s="8">
+        <v>825</v>
+      </c>
+      <c r="H12" s="8">
+        <v>35</v>
+      </c>
+      <c r="I12" s="8">
+        <f t="shared" si="0"/>
+        <v>790</v>
+      </c>
+      <c r="J12" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>2214</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>2215</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>2216</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="G13" s="6">
+        <v>850</v>
+      </c>
+      <c r="H13" s="6">
+        <v>20</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="0"/>
+        <v>830</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>2218</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>2219</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="3">
+        <v>720</v>
+      </c>
+      <c r="H14" s="3">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3">
+        <f t="shared" si="0"/>
+        <v>690</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>2220</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>2221</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>2222</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="G15" s="6">
+        <v>0</v>
+      </c>
+      <c r="H15" s="6">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>343</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>2223</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>2224</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="G16" s="8">
+        <v>1690</v>
+      </c>
+      <c r="H16" s="8">
+        <v>30</v>
+      </c>
+      <c r="I16" s="8">
+        <f t="shared" si="0"/>
+        <v>1660</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>2225</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>1390</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1290</v>
+      </c>
+      <c r="H17" s="3">
+        <v>30</v>
+      </c>
+      <c r="I17" s="3">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>2226</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>2227</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>2228</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G18" s="8">
+        <v>620</v>
+      </c>
+      <c r="H18" s="8">
+        <v>30</v>
+      </c>
+      <c r="I18" s="8">
+        <f t="shared" si="0"/>
+        <v>590</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>2229</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>2230</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>2231</v>
+      </c>
+      <c r="F19" s="4">
+        <v>2</v>
+      </c>
+      <c r="G19" s="3">
+        <v>1020</v>
+      </c>
+      <c r="H19" s="3">
+        <v>30</v>
+      </c>
+      <c r="I19" s="3">
+        <f t="shared" si="0"/>
+        <v>990</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>2232</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>2233</v>
+      </c>
+      <c r="E20" s="8" t="s">
+        <v>2234</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20" s="8">
+        <v>8559</v>
+      </c>
+      <c r="H20" s="8">
+        <v>65</v>
+      </c>
+      <c r="I20" s="8">
+        <f t="shared" si="0"/>
+        <v>8494</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>2188</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>2235</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>2236</v>
+      </c>
+      <c r="E21" s="8" t="s">
+        <v>2237</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G21" s="8">
+        <v>2620</v>
+      </c>
+      <c r="H21" s="8">
+        <v>35</v>
+      </c>
+      <c r="I21" s="8">
+        <f t="shared" si="0"/>
+        <v>2585</v>
+      </c>
+      <c r="J21" s="8" t="s">
+        <v>2187</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>2188</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>2238</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>1195</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="G22" s="6">
+        <v>915</v>
+      </c>
+      <c r="H22" s="6">
+        <v>25</v>
+      </c>
+      <c r="I22" s="6">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>2239</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2240</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>30</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>2241</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="3">
+        <v>4440</v>
+      </c>
+      <c r="H24" s="3">
+        <v>40</v>
+      </c>
+      <c r="I24" s="3">
+        <f t="shared" si="0"/>
+        <v>4400</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>2188</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1800-000000000000}">
+  <dimension ref="A1:Q31"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="35.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="72.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>721</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2244</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2297</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1825</v>
+      </c>
+      <c r="H3" s="3">
+        <v>25</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" ref="I3:I31" si="0">G3-H3</f>
+        <v>1800</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>2246</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>2247</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>2308</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="6">
+        <v>0</v>
+      </c>
+      <c r="H4" s="6">
+        <v>30</v>
+      </c>
+      <c r="I4" s="6">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2249</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2250</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>2251</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="3">
+        <v>850</v>
+      </c>
+      <c r="H5" s="3">
+        <v>30</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>2253</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>2307</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1730</v>
+      </c>
+      <c r="H6" s="6">
+        <v>30</v>
+      </c>
+      <c r="I6" s="6">
+        <f t="shared" si="0"/>
+        <v>1700</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2254</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>2255</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>2292</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1110</v>
+      </c>
+      <c r="H7" s="3">
+        <v>30</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>2301</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>2291</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>2302</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="6">
+        <v>0</v>
+      </c>
+      <c r="H8" s="6">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2256</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2257</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>2296</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="G9" s="3">
+        <v>1740</v>
+      </c>
+      <c r="H9" s="3">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>1710</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>2258</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>2259</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>2260</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" s="6">
+        <v>525</v>
+      </c>
+      <c r="H10" s="6">
+        <v>35</v>
+      </c>
+      <c r="I10" s="6">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>2261</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>2262</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>2263</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1110</v>
+      </c>
+      <c r="H11" s="6">
+        <v>30</v>
+      </c>
+      <c r="I11" s="6">
+        <f t="shared" si="0"/>
+        <v>1080</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>2264</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>2265</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="3">
+        <v>520</v>
+      </c>
+      <c r="H12" s="3">
+        <v>30</v>
+      </c>
+      <c r="I12" s="3">
+        <f t="shared" si="0"/>
+        <v>490</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>2303</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>2266</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>2304</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0</v>
+      </c>
+      <c r="H13" s="6">
+        <v>25</v>
+      </c>
+      <c r="I13" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>2267</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>2268</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>2315</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="G14" s="8">
+        <v>845</v>
+      </c>
+      <c r="H14" s="8">
+        <v>25</v>
+      </c>
+      <c r="I14" s="8">
+        <f t="shared" si="0"/>
+        <v>820</v>
+      </c>
+      <c r="J14" s="8" t="s">
+        <v>2248</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>2269</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>2270</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>2293</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G15" s="3">
+        <v>550</v>
+      </c>
+      <c r="H15" s="3">
+        <v>30</v>
+      </c>
+      <c r="I15" s="3">
+        <f t="shared" si="0"/>
+        <v>520</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>2271</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="6">
+        <v>0</v>
+      </c>
+      <c r="H16" s="6">
+        <v>25</v>
+      </c>
+      <c r="I16" s="6">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>2273</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="G17" s="8">
+        <v>915</v>
+      </c>
+      <c r="H17" s="8">
+        <v>25</v>
+      </c>
+      <c r="I17" s="8">
+        <f t="shared" si="0"/>
+        <v>890</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>2248</v>
+      </c>
+      <c r="K17" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>2274</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>2275</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G18" s="3">
+        <v>0</v>
+      </c>
+      <c r="H18" s="3">
+        <v>30</v>
+      </c>
+      <c r="I18" s="3">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>2276</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>2277</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>2314</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G19" s="8">
+        <v>1640</v>
+      </c>
+      <c r="H19" s="8">
+        <v>30</v>
+      </c>
+      <c r="I19" s="8">
+        <f t="shared" si="0"/>
+        <v>1610</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>2248</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>2217</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>2295</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G20" s="3">
+        <v>130</v>
+      </c>
+      <c r="H20" s="3">
+        <v>30</v>
+      </c>
+      <c r="I20" s="3">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>2245</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" s="11" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>2279</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>2280</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>2309</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="G21" s="11">
+        <v>570</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0</v>
+      </c>
+      <c r="I21" s="11">
+        <f t="shared" si="0"/>
+        <v>570</v>
+      </c>
+      <c r="J21" s="11" t="s">
+        <v>2312</v>
+      </c>
+      <c r="K21" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="11" t="s">
+        <v>2245</v>
+      </c>
+      <c r="M21" s="21" t="s">
+        <v>2311</v>
+      </c>
+      <c r="N21" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="O21" s="22"/>
+      <c r="P21" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="Q21" s="23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>2313</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>2281</v>
+      </c>
+      <c r="E22" s="8" t="s">
+        <v>2282</v>
+      </c>
+      <c r="F22" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0</v>
+      </c>
+      <c r="H22" s="8">
+        <v>30</v>
+      </c>
+      <c r="I22" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J22" s="8" t="s">
+        <v>2248</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>2284</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G23" s="3">
+        <v>0</v>
+      </c>
+      <c r="H23" s="3">
+        <v>0</v>
+      </c>
+      <c r="I23" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>2245</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>2319</v>
+      </c>
+      <c r="E24" s="8" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F24" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G24" s="8">
+        <v>0</v>
+      </c>
+      <c r="H24" s="8">
+        <v>30</v>
+      </c>
+      <c r="I24" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J24" s="8" t="s">
+        <v>2248</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>2305</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="G25" s="6">
+        <v>1185</v>
+      </c>
+      <c r="H25" s="6">
+        <v>25</v>
+      </c>
+      <c r="I25" s="6">
+        <f t="shared" si="0"/>
+        <v>1160</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>2283</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>2285</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="3">
+        <v>0</v>
+      </c>
+      <c r="H26" s="3">
+        <v>40</v>
+      </c>
+      <c r="I26" s="3">
+        <f t="shared" si="0"/>
+        <v>-40</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>2245</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>2286</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>2287</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>2300</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G27" s="3">
+        <v>775</v>
+      </c>
+      <c r="H27" s="3">
+        <v>25</v>
+      </c>
+      <c r="I27" s="3">
+        <f t="shared" si="0"/>
+        <v>750</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>2298</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>2288</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>2299</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="G28" s="3">
+        <v>0</v>
+      </c>
+      <c r="H28" s="3">
+        <v>25</v>
+      </c>
+      <c r="I28" s="3">
+        <f t="shared" si="0"/>
+        <v>-25</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>2290</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>2306</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="G29" s="6">
+        <v>1600</v>
+      </c>
+      <c r="H29" s="6">
+        <v>30</v>
+      </c>
+      <c r="I29" s="6">
+        <f t="shared" si="0"/>
+        <v>1570</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>2316</v>
+      </c>
+      <c r="D30" s="8" t="s">
+        <v>2317</v>
+      </c>
+      <c r="E30" s="8" t="s">
+        <v>2318</v>
+      </c>
+      <c r="F30" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G30" s="8">
+        <v>0</v>
+      </c>
+      <c r="H30" s="8">
+        <v>30</v>
+      </c>
+      <c r="I30" s="8">
+        <f t="shared" ref="I30" si="1">G30-H30</f>
+        <v>-30</v>
+      </c>
+      <c r="J30" s="8" t="s">
+        <v>2248</v>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L30" s="8" t="s">
+        <v>2245</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E31" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="F31" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="G31" s="8">
+        <v>0</v>
+      </c>
+      <c r="H31" s="8">
+        <v>30</v>
+      </c>
+      <c r="I31" s="8">
+        <f t="shared" si="0"/>
+        <v>-30</v>
+      </c>
+      <c r="J31" s="8" t="s">
+        <v>2248</v>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>2245</v>
       </c>
     </row>
   </sheetData>
@@ -29417,7 +31860,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="6">
-        <f t="shared" ref="I35:I55" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>2090</v>
       </c>
       <c r="J35" s="6" t="s">
@@ -36600,7 +39043,7 @@
         <v>30</v>
       </c>
       <c r="I35" s="8">
-        <f t="shared" ref="I35:I58" si="1">G35-H35</f>
+        <f t="shared" ref="I35:I66" si="1">G35-H35</f>
         <v>-30</v>
       </c>
       <c r="J35" s="8" t="s">
